--- a/NBA/step8_nba1h_direction_clean.xlsx
+++ b/NBA/step8_nba1h_direction_clean.xlsx
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -3264,36 +3264,36 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29 18:00:00-04:00</t>
+          <t>2026-03-29 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -3312,31 +3312,39 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>12.6</v>
+        <v>21.4</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.8838</v>
+        <v>0.8897</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12.6</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>12.6</v>
+        <v>20</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>Above Avg</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
@@ -3349,29 +3357,29 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>PRIMARY</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr"/>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr"/>
       <c r="AD16" s="3" t="inlineStr"/>
       <c r="AE16" s="3" t="n">
-        <v>85.86113229395886</v>
+        <v>29.43920288775949</v>
       </c>
       <c r="AF16" s="3" t="inlineStr"/>
       <c r="AG16" s="3" t="n">
@@ -3380,29 +3388,21 @@
       <c r="AH16" s="3" t="inlineStr"/>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AK16" s="3" t="inlineStr">
         <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AM16" s="3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
       <c r="AN16" s="3" t="inlineStr"/>
       <c r="AO16" s="3" t="inlineStr"/>
       <c r="AP16" s="3" t="inlineStr"/>
@@ -3410,7 +3410,7 @@
       <c r="AR16" s="3" t="inlineStr"/>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr"/>
@@ -3423,12 +3423,12 @@
       <c r="BA16" s="3" t="inlineStr"/>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.829</t>
         </is>
       </c>
       <c r="BC16" s="3" t="inlineStr">
         <is>
-          <t>POR +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>MIL -14.5 pt margin vs LAC, pra: 0.83x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -3618,32 +3618,32 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29 15:30:00-04:00</t>
+          <t>2026-03-29 18:00:00-04:00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -3662,39 +3662,31 @@
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>9.83</v>
+        <v>4.1</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>20.33</v>
+        <v>12.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.8877</v>
+        <v>0.8838</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>19</v>
+        <v>12.6</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>19</v>
+        <v>12.6</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>Above Avg</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" s="3" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
@@ -3707,29 +3699,29 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>PRIMARY</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr"/>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr"/>
       <c r="AD18" s="3" t="inlineStr"/>
       <c r="AE18" s="3" t="n">
-        <v>36.84210526315789</v>
+        <v>85.86113229395886</v>
       </c>
       <c r="AF18" s="3" t="inlineStr"/>
       <c r="AG18" s="3" t="n">
@@ -3738,17 +3730,29 @@
       <c r="AH18" s="3" t="inlineStr"/>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
-      <c r="AM18" s="3" t="inlineStr"/>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
       <c r="AN18" s="3" t="inlineStr"/>
       <c r="AO18" s="3" t="inlineStr"/>
       <c r="AP18" s="3" t="inlineStr"/>
@@ -3756,7 +3760,7 @@
       <c r="AR18" s="3" t="inlineStr"/>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr"/>
@@ -3769,12 +3773,12 @@
       <c r="BA18" s="3" t="inlineStr"/>
       <c r="BB18" s="3" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BC18" s="3" t="inlineStr">
         <is>
-          <t>MIL -14.5 pt margin vs LAC, pra: 0.83x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
+          <t>POR +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3956,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
@@ -4294,7 +4298,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
@@ -4648,16 +4652,16 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -4687,7 +4691,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -4696,22 +4700,22 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>14</v>
+        <v>9.75</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.886</v>
+        <v>0.884</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>0.75</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>3</v>
@@ -4741,29 +4745,29 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr"/>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr"/>
       <c r="AD24" s="3" t="inlineStr"/>
       <c r="AE24" s="3" t="n">
-        <v>26.24453295839119</v>
+        <v>60.84005393694704</v>
       </c>
       <c r="AF24" s="3" t="inlineStr"/>
       <c r="AG24" s="3" t="n">
@@ -4772,22 +4776,22 @@
       <c r="AH24" s="3" t="inlineStr"/>
       <c r="AI24" s="3" t="inlineStr">
         <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="AJ24" s="3" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
       <c r="AK24" s="3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr"/>
@@ -4798,7 +4802,7 @@
       <c r="AR24" s="3" t="inlineStr"/>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr"/>
@@ -4827,7 +4831,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
@@ -4856,7 +4860,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -4866,34 +4870,34 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-2.58</v>
+        <v>3</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>6.42</v>
+        <v>9</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0.8831</v>
+        <v>0.8847</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25" s="5" t="n">
         <v>1</v>
@@ -4926,23 +4930,23 @@
       <c r="Y25" s="5" t="inlineStr"/>
       <c r="Z25" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AA25" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AB25" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AC25" s="5" t="inlineStr"/>
       <c r="AD25" s="5" t="inlineStr"/>
       <c r="AE25" s="5" t="n">
-        <v>0</v>
+        <v>50.51178406291057</v>
       </c>
       <c r="AF25" s="5" t="inlineStr"/>
       <c r="AG25" s="5" t="n">
@@ -4951,11 +4955,19 @@
       <c r="AH25" s="5" t="inlineStr"/>
       <c r="AI25" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AJ25" s="5" t="inlineStr"/>
-      <c r="AK25" s="5" t="inlineStr"/>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AJ25" s="5" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AK25" s="5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
       <c r="AL25" s="5" t="inlineStr"/>
       <c r="AM25" s="5" t="inlineStr"/>
       <c r="AN25" s="5" t="inlineStr"/>
@@ -4965,7 +4977,7 @@
       <c r="AR25" s="5" t="inlineStr"/>
       <c r="AS25" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AT25" s="5" t="inlineStr"/>
@@ -4978,12 +4990,12 @@
       <c r="BA25" s="5" t="inlineStr"/>
       <c r="BB25" s="5" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BC25" s="5" t="inlineStr">
         <is>
-          <t>MIL -14.5 pt margin vs LAC, pra: 0.83x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
+          <t>MIL -14.5 pt margin vs LAC, pts: 0.81x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -4994,16 +5006,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>C-F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -5033,7 +5045,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -5042,25 +5054,25 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.8851</v>
+        <v>0.886</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>1</v>
@@ -5087,29 +5099,29 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr"/>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr"/>
       <c r="AD26" s="3" t="inlineStr"/>
       <c r="AE26" s="3" t="n">
-        <v>64.70588235294117</v>
+        <v>23.47382389307855</v>
       </c>
       <c r="AF26" s="3" t="inlineStr"/>
       <c r="AG26" s="3" t="n">
@@ -5123,12 +5135,24 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AK26" s="3" t="inlineStr"/>
-      <c r="AL26" s="3" t="inlineStr"/>
-      <c r="AM26" s="3" t="inlineStr"/>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="AK26" s="3" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
       <c r="AN26" s="3" t="inlineStr"/>
       <c r="AO26" s="3" t="inlineStr"/>
       <c r="AP26" s="3" t="inlineStr"/>
@@ -5136,7 +5160,7 @@
       <c r="AR26" s="3" t="inlineStr"/>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr"/>
@@ -5165,16 +5189,16 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C-F</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -5194,7 +5218,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -5204,34 +5228,34 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L27" s="5" t="n">
-        <v>2.5</v>
+        <v>-2.58</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>9</v>
+        <v>6.42</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>0.8845</v>
+        <v>0.8831</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S27" s="5" t="n">
         <v>1</v>
@@ -5264,23 +5288,23 @@
       <c r="Y27" s="5" t="inlineStr"/>
       <c r="Z27" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AA27" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AB27" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AC27" s="5" t="inlineStr"/>
       <c r="AD27" s="5" t="inlineStr"/>
       <c r="AE27" s="5" t="n">
-        <v>74.25902835467934</v>
+        <v>0</v>
       </c>
       <c r="AF27" s="5" t="inlineStr"/>
       <c r="AG27" s="5" t="n">
@@ -5289,19 +5313,11 @@
       <c r="AH27" s="5" t="inlineStr"/>
       <c r="AI27" s="5" t="inlineStr">
         <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AJ27" s="5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AK27" s="5" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AJ27" s="5" t="inlineStr"/>
+      <c r="AK27" s="5" t="inlineStr"/>
       <c r="AL27" s="5" t="inlineStr"/>
       <c r="AM27" s="5" t="inlineStr"/>
       <c r="AN27" s="5" t="inlineStr"/>
@@ -5311,7 +5327,7 @@
       <c r="AR27" s="5" t="inlineStr"/>
       <c r="AS27" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AT27" s="5" t="inlineStr"/>
@@ -5324,12 +5340,12 @@
       <c r="BA27" s="5" t="inlineStr"/>
       <c r="BB27" s="5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.829</t>
         </is>
       </c>
       <c r="BC27" s="5" t="inlineStr">
         <is>
-          <t>MIL -14.5 pt margin vs LAC, pts: 0.81x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
+          <t>MIL -14.5 pt margin vs LAC, pra: 0.83x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9206,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -10414,7 +10430,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -11774,7 +11790,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -12302,36 +12318,36 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPP</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29 18:00:00-04:00</t>
+          <t>2026-03-29 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -12341,7 +12357,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
@@ -12350,31 +12366,39 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>12.6</v>
+        <v>21.4</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.8838</v>
+        <v>0.8897</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>12.6</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>12.6</v>
+        <v>20</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>Above Avg</t>
+        </is>
+      </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
@@ -12387,29 +12411,29 @@
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>PRIMARY</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr"/>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AC2" s="3" t="inlineStr"/>
       <c r="AD2" s="3" t="inlineStr"/>
       <c r="AE2" s="3" t="n">
-        <v>85.86113229395886</v>
+        <v>29.43920288775949</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="n">
@@ -12418,29 +12442,21 @@
       <c r="AH2" s="3" t="inlineStr"/>
       <c r="AI2" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AJ2" s="3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AK2" s="3" t="inlineStr">
         <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="AM2" s="3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
       <c r="AO2" s="3" t="inlineStr"/>
       <c r="AP2" s="3" t="inlineStr"/>
@@ -12448,7 +12464,7 @@
       <c r="AR2" s="3" t="inlineStr"/>
       <c r="AS2" s="3" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AT2" s="3" t="inlineStr"/>
@@ -12461,12 +12477,12 @@
       <c r="BA2" s="3" t="inlineStr"/>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.829</t>
         </is>
       </c>
       <c r="BC2" s="3" t="inlineStr">
         <is>
-          <t>POR +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>MIL -14.5 pt margin vs LAC, pra: 0.83x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -12656,32 +12672,32 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>UNKNOWN_OPP</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29 15:30:00-04:00</t>
+          <t>2026-03-29 18:00:00-04:00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -12691,7 +12707,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -12700,39 +12716,31 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>9.83</v>
+        <v>4.1</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>20.33</v>
+        <v>12.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.8877</v>
+        <v>0.8838</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>19</v>
+        <v>12.6</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>19</v>
+        <v>12.6</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>Above Avg</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
@@ -12745,29 +12753,29 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>PRIMARY</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr"/>
       <c r="AD4" s="3" t="inlineStr"/>
       <c r="AE4" s="3" t="n">
-        <v>36.84210526315789</v>
+        <v>85.86113229395886</v>
       </c>
       <c r="AF4" s="3" t="inlineStr"/>
       <c r="AG4" s="3" t="n">
@@ -12776,17 +12784,29 @@
       <c r="AH4" s="3" t="inlineStr"/>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
       <c r="AN4" s="3" t="inlineStr"/>
       <c r="AO4" s="3" t="inlineStr"/>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -12794,7 +12814,7 @@
       <c r="AR4" s="3" t="inlineStr"/>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr"/>
@@ -12807,12 +12827,12 @@
       <c r="BA4" s="3" t="inlineStr"/>
       <c r="BB4" s="3" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BC4" s="3" t="inlineStr">
         <is>
-          <t>MIL -14.5 pt margin vs LAC, pra: 0.83x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
+          <t>POR +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -12990,7 +13010,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -13332,7 +13352,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -14035,16 +14055,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -14074,7 +14094,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
@@ -14083,22 +14103,22 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>14</v>
+        <v>9.75</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.886</v>
+        <v>0.884</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0.75</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>3</v>
@@ -14128,29 +14148,29 @@
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr"/>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AC2" s="3" t="inlineStr"/>
       <c r="AD2" s="3" t="inlineStr"/>
       <c r="AE2" s="3" t="n">
-        <v>26.24453295839119</v>
+        <v>60.84005393694704</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="n">
@@ -14159,22 +14179,22 @@
       <c r="AH2" s="3" t="inlineStr"/>
       <c r="AI2" s="3" t="inlineStr">
         <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="3" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="AJ2" s="3" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
       <c r="AK2" s="3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AL2" s="3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AM2" s="3" t="inlineStr"/>
@@ -14185,7 +14205,7 @@
       <c r="AR2" s="3" t="inlineStr"/>
       <c r="AS2" s="3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AT2" s="3" t="inlineStr"/>
@@ -14214,7 +14234,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
@@ -14243,7 +14263,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -14253,34 +14273,34 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>-2.58</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>6.42</v>
+        <v>9</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.8831</v>
+        <v>0.8847</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R3" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" s="5" t="n">
         <v>1</v>
@@ -14313,23 +14333,23 @@
       <c r="Y3" s="5" t="inlineStr"/>
       <c r="Z3" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AA3" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AB3" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AC3" s="5" t="inlineStr"/>
       <c r="AD3" s="5" t="inlineStr"/>
       <c r="AE3" s="5" t="n">
-        <v>0</v>
+        <v>50.51178406291057</v>
       </c>
       <c r="AF3" s="5" t="inlineStr"/>
       <c r="AG3" s="5" t="n">
@@ -14338,11 +14358,19 @@
       <c r="AH3" s="5" t="inlineStr"/>
       <c r="AI3" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AJ3" s="5" t="inlineStr"/>
-      <c r="AK3" s="5" t="inlineStr"/>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AJ3" s="5" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AK3" s="5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
       <c r="AL3" s="5" t="inlineStr"/>
       <c r="AM3" s="5" t="inlineStr"/>
       <c r="AN3" s="5" t="inlineStr"/>
@@ -14352,7 +14380,7 @@
       <c r="AR3" s="5" t="inlineStr"/>
       <c r="AS3" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AT3" s="5" t="inlineStr"/>
@@ -14365,12 +14393,12 @@
       <c r="BA3" s="5" t="inlineStr"/>
       <c r="BB3" s="5" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BC3" s="5" t="inlineStr">
         <is>
-          <t>MIL -14.5 pt margin vs LAC, pra: 0.83x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
+          <t>MIL -14.5 pt margin vs LAC, pts: 0.81x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -14381,16 +14409,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>C-F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -14420,7 +14448,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -14429,25 +14457,25 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.8851</v>
+        <v>0.886</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>1</v>
@@ -14474,29 +14502,29 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr"/>
       <c r="AD4" s="3" t="inlineStr"/>
       <c r="AE4" s="3" t="n">
-        <v>64.70588235294117</v>
+        <v>23.47382389307855</v>
       </c>
       <c r="AF4" s="3" t="inlineStr"/>
       <c r="AG4" s="3" t="n">
@@ -14510,12 +14538,24 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
       <c r="AN4" s="3" t="inlineStr"/>
       <c r="AO4" s="3" t="inlineStr"/>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -14523,7 +14563,7 @@
       <c r="AR4" s="3" t="inlineStr"/>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr"/>
@@ -14552,16 +14592,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C-F</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -14581,7 +14621,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -14591,34 +14631,34 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>2.5</v>
+        <v>-2.58</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>9</v>
+        <v>6.42</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.8845</v>
+        <v>0.8831</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S5" s="5" t="n">
         <v>1</v>
@@ -14651,23 +14691,23 @@
       <c r="Y5" s="5" t="inlineStr"/>
       <c r="Z5" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AA5" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AB5" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AC5" s="5" t="inlineStr"/>
       <c r="AD5" s="5" t="inlineStr"/>
       <c r="AE5" s="5" t="n">
-        <v>74.25902835467934</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="5" t="inlineStr"/>
       <c r="AG5" s="5" t="n">
@@ -14676,19 +14716,11 @@
       <c r="AH5" s="5" t="inlineStr"/>
       <c r="AI5" s="5" t="inlineStr">
         <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AJ5" s="5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AK5" s="5" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AJ5" s="5" t="inlineStr"/>
+      <c r="AK5" s="5" t="inlineStr"/>
       <c r="AL5" s="5" t="inlineStr"/>
       <c r="AM5" s="5" t="inlineStr"/>
       <c r="AN5" s="5" t="inlineStr"/>
@@ -14698,7 +14730,7 @@
       <c r="AR5" s="5" t="inlineStr"/>
       <c r="AS5" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AT5" s="5" t="inlineStr"/>
@@ -14711,12 +14743,12 @@
       <c r="BA5" s="5" t="inlineStr"/>
       <c r="BB5" s="5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.829</t>
         </is>
       </c>
       <c r="BC5" s="5" t="inlineStr">
         <is>
-          <t>MIL -14.5 pt margin vs LAC, pts: 0.81x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
+          <t>MIL -14.5 pt margin vs LAC, pra: 0.83x game script (dog; spread_risk 0.80, total_risk 1.02)</t>
         </is>
       </c>
     </row>

--- a/NBA/step8_nba1h_direction_clean.xlsx
+++ b/NBA/step8_nba1h_direction_clean.xlsx
@@ -1826,7 +1826,7 @@
       </c>
       <c r="BE6" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="BE7" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="BE12" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="BE16" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BE18" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="BE22" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="BE23" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="BE29" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="BE33" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="BE37" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="BE72" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -14035,7 +14035,7 @@
       </c>
       <c r="BE73" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="BE78" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="BE81" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="BE88" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="BE89" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="BE96" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -17665,7 +17665,7 @@
       </c>
       <c r="BE99" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="BE4" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="BE5" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -20713,7 +20713,7 @@
       </c>
       <c r="BE10" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="BE14" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -22216,7 +22216,7 @@
       </c>
       <c r="BE3" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -22992,7 +22992,7 @@
       </c>
       <c r="BE7" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -23181,7 +23181,7 @@
       </c>
       <c r="BE8" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -24303,7 +24303,7 @@
       </c>
       <c r="BE14" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -25087,7 +25087,7 @@
       </c>
       <c r="BE18" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -25867,7 +25867,7 @@
       </c>
       <c r="BE22" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -31986,7 +31986,7 @@
       </c>
       <c r="BE57" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -32117,7 +32117,7 @@
       </c>
       <c r="BE58" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -32796,7 +32796,7 @@
       </c>
       <c r="BE63" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -33205,7 +33205,7 @@
       </c>
       <c r="BE66" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -34190,7 +34190,7 @@
       </c>
       <c r="BE73" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="BE74" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -35346,7 +35346,7 @@
       </c>
       <c r="BE81" s="5" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -35747,7 +35747,7 @@
       </c>
       <c r="BE84" s="3" t="inlineStr">
         <is>
-          <t>PHI +16.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>PHI +15.5 pt margin vs WSH, pra: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>

--- a/NBA/step8_nba1h_direction_clean.xlsx
+++ b/NBA/step8_nba1h_direction_clean.xlsx
@@ -1878,13 +1878,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-3.96</v>
+        <v>3.96</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>3.96</v>
@@ -1893,13 +1893,13 @@
         <v>6.54</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.5334</v>
+        <v>0.4319</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-0.4478</v>
+        <v>-0.5493</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>0.86</v>
+        <v>0.8296</v>
       </c>
       <c r="R7" s="5" t="n">
         <v>0</v>
@@ -3882,13 +3882,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-4.62</v>
+        <v>4.62</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>4.62</v>
@@ -3897,13 +3897,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.5829</v>
+        <v>0.4929</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-0.4074</v>
+        <v>-0.4973</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>0.6883</v>
+        <v>0.6613</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>0.2</v>
@@ -4286,13 +4286,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-1.51</v>
+        <v>1.51</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>1.51</v>
@@ -4301,13 +4301,13 @@
         <v>4.99</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.5127</v>
+        <v>0.485</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-0.3071</v>
+        <v>-0.3348</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>0.6137</v>
+        <v>0.6054</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0.4</v>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -5099,50 +5099,50 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>-3.04</v>
+        <v>3.61</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>3.04</v>
+        <v>3.61</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>5.46</v>
+        <v>11.11</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0.5987</v>
+        <v>0.9039</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>-0.3556</v>
+        <v>-0.0698</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>0.7221</v>
+        <v>0.7146</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>6.1</v>
+        <v>10.2</v>
       </c>
       <c r="U23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V23" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W23" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X23" s="5" t="inlineStr">
@@ -5162,80 +5162,76 @@
       </c>
       <c r="AA23" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="AB23" s="5" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB23" s="5" t="inlineStr">
+        <is>
+          <t>VOID_LOW_MINUTES_NON_A</t>
+        </is>
+      </c>
       <c r="AC23" s="5" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AD23" s="5" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AE23" s="5" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AF23" s="5" t="inlineStr"/>
       <c r="AG23" s="5" t="inlineStr"/>
       <c r="AH23" s="5" t="n">
-        <v>64.50400256848616</v>
+        <v>47.3143268513502</v>
       </c>
       <c r="AI23" s="5" t="inlineStr"/>
       <c r="AJ23" s="5" t="n">
-        <v>-1.325</v>
+        <v>0.4329999999999998</v>
       </c>
       <c r="AK23" s="5" t="inlineStr"/>
       <c r="AL23" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AM23" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN23" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AO23" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AP23" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ23" s="5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AR23" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AS23" s="5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AR23" s="5" t="inlineStr"/>
+      <c r="AS23" s="5" t="inlineStr"/>
       <c r="AT23" s="5" t="inlineStr"/>
       <c r="AU23" s="5" t="inlineStr"/>
       <c r="AV23" s="5" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AW23" s="5" t="inlineStr"/>
@@ -5248,12 +5244,12 @@
       <c r="BD23" s="5" t="inlineStr"/>
       <c r="BE23" s="5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="BF23" s="5" t="inlineStr">
         <is>
-          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5264,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -5278,22 +5274,22 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -5303,7 +5299,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -5312,41 +5308,41 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>3.61</v>
+        <v>3.04</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>3.61</v>
+        <v>3.04</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.11</v>
+        <v>5.46</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.9039</v>
+        <v>0.5502</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-0.0698</v>
+        <v>-0.404</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.7146</v>
+        <v>0.7076</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>10.6</v>
+        <v>4.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>10.2</v>
+        <v>6.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
@@ -5366,76 +5362,80 @@
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB24" s="3" t="inlineStr">
-        <is>
-          <t>VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr"/>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AD24" s="3" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr"/>
       <c r="AG24" s="3" t="inlineStr"/>
       <c r="AH24" s="3" t="n">
-        <v>47.3143268513502</v>
+        <v>64.50400256848616</v>
       </c>
       <c r="AI24" s="3" t="inlineStr"/>
       <c r="AJ24" s="3" t="n">
-        <v>0.4329999999999998</v>
+        <v>-1.325</v>
       </c>
       <c r="AK24" s="3" t="inlineStr"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AM24" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AO24" s="3" t="inlineStr">
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ24" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AR24" s="3" t="inlineStr"/>
-      <c r="AS24" s="3" t="inlineStr"/>
       <c r="AT24" s="3" t="inlineStr"/>
       <c r="AU24" s="3" t="inlineStr"/>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AW24" s="3" t="inlineStr"/>
@@ -5448,12 +5448,12 @@
       <c r="BD24" s="3" t="inlineStr"/>
       <c r="BE24" s="3" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BF24" s="3" t="inlineStr">
         <is>
-          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -5922,13 +5922,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L27" s="5" t="n">
-        <v>-1.96</v>
+        <v>1.96</v>
       </c>
       <c r="M27" s="5" t="n">
         <v>1.96</v>
@@ -5937,13 +5937,13 @@
         <v>8.039999999999999</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0.4745</v>
+        <v>0.463</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>-0.4015</v>
+        <v>-0.4131</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>0.6247</v>
+        <v>0.6212</v>
       </c>
       <c r="R27" s="5" t="n">
         <v>0.4</v>
@@ -6464,22 +6464,22 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Taylor Hendricks</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -6499,55 +6499,55 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-2.04</v>
+        <v>5.41</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>2.04</v>
+        <v>5.41</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>4.46</v>
+        <v>15.41</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.5717</v>
+        <v>0.9096</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-0.3136</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0.7014</v>
+        <v>0.6929</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>4.7</v>
+        <v>14.4</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -6562,76 +6562,72 @@
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="AB30" s="3" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>VOID_LOW_MINUTES_NON_A</t>
+        </is>
+      </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AD30" s="3" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr"/>
       <c r="AG30" s="3" t="inlineStr"/>
       <c r="AH30" s="3" t="n">
-        <v>43.4930305891131</v>
+        <v>45.77015848134467</v>
       </c>
       <c r="AI30" s="3" t="inlineStr"/>
       <c r="AJ30" s="3" t="n">
-        <v>-0.5140000000000002</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="3" t="inlineStr"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AQ30" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AR30" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr"/>
       <c r="AS30" s="3" t="inlineStr"/>
       <c r="AT30" s="3" t="inlineStr"/>
       <c r="AU30" s="3" t="inlineStr"/>
       <c r="AV30" s="3" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AW30" s="3" t="inlineStr"/>
@@ -6644,12 +6640,12 @@
       <c r="BD30" s="3" t="inlineStr"/>
       <c r="BE30" s="3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.045</t>
         </is>
       </c>
       <c r="BF30" s="3" t="inlineStr">
         <is>
-          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>BOS +9.5 pt margin vs TOR, pra: 1.04x game script (fav; spread_risk 1.05, total_risk 1.00)</t>
         </is>
       </c>
     </row>
@@ -6664,22 +6660,22 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Taylor Hendricks</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -6689,7 +6685,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -6699,7 +6695,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -6708,46 +6704,46 @@
         </is>
       </c>
       <c r="L31" s="5" t="n">
-        <v>5.41</v>
+        <v>2.04</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>5.41</v>
+        <v>2.04</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>15.41</v>
+        <v>4.46</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>0.9096</v>
+        <v>0.497</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.3882</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>0.6929</v>
+        <v>0.679</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>14.4</v>
+        <v>4.7</v>
       </c>
       <c r="U31" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V31" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W31" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="X31" s="5" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Y31" s="5" t="inlineStr">
@@ -6762,72 +6758,76 @@
       </c>
       <c r="AA31" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB31" s="5" t="inlineStr">
-        <is>
-          <t>VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AB31" s="5" t="inlineStr"/>
       <c r="AC31" s="5" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AD31" s="5" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AE31" s="5" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AF31" s="5" t="inlineStr"/>
       <c r="AG31" s="5" t="inlineStr"/>
       <c r="AH31" s="5" t="n">
-        <v>45.77015848134467</v>
+        <v>43.4930305891131</v>
       </c>
       <c r="AI31" s="5" t="inlineStr"/>
       <c r="AJ31" s="5" t="n">
-        <v>0</v>
+        <v>-0.5140000000000002</v>
       </c>
       <c r="AK31" s="5" t="inlineStr"/>
       <c r="AL31" s="5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM31" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN31" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO31" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AP31" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ31" s="5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AN31" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AO31" s="5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AP31" s="5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AQ31" s="5" t="inlineStr"/>
-      <c r="AR31" s="5" t="inlineStr"/>
+      <c r="AR31" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AS31" s="5" t="inlineStr"/>
       <c r="AT31" s="5" t="inlineStr"/>
       <c r="AU31" s="5" t="inlineStr"/>
       <c r="AV31" s="5" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AW31" s="5" t="inlineStr"/>
@@ -6840,12 +6840,12 @@
       <c r="BD31" s="5" t="inlineStr"/>
       <c r="BE31" s="5" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BF31" s="5" t="inlineStr">
         <is>
-          <t>BOS +9.5 pt margin vs TOR, pra: 1.04x game script (fav; spread_risk 1.05, total_risk 1.00)</t>
+          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -6898,13 +6898,13 @@
           <t>8</t>
         </is>
       </c>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>-0.92</v>
+        <v>0.92</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>0.92</v>
@@ -6913,13 +6913,13 @@
         <v>7.08</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>0.5419</v>
+        <v>0.5175</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>-0.1741</v>
+        <v>-0.1986</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>0.746</v>
+        <v>0.7387</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>0</v>
@@ -7102,13 +7102,13 @@
           <t>11</t>
         </is>
       </c>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L33" s="5" t="n">
-        <v>-5.65</v>
+        <v>5.65</v>
       </c>
       <c r="M33" s="5" t="n">
         <v>5.65</v>
@@ -7117,13 +7117,13 @@
         <v>5.35</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>0.6911</v>
+        <v>0.6272</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>-0.3054</v>
+        <v>-0.3693</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>0.9073</v>
+        <v>0.8881</v>
       </c>
       <c r="R33" s="5" t="n">
         <v>0</v>
@@ -7282,13 +7282,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>-3.02</v>
+        <v>3.02</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>3.02</v>
@@ -7297,13 +7297,13 @@
         <v>11.48</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0.6384</v>
+        <v>0.5231</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>-0.3149</v>
+        <v>-0.4302</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0.7631</v>
+        <v>0.7285</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>0.2</v>
@@ -7686,13 +7686,13 @@
           <t>9.5</t>
         </is>
       </c>
-      <c r="K36" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>1.5</v>
@@ -7701,13 +7701,13 @@
         <v>8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.522</v>
+        <v>0.5165</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.2955</v>
+        <v>-0.3011</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.6816</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>0.2</v>
@@ -7898,13 +7898,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K37" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-2.26</v>
+        <v>2.26</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>2.26</v>
@@ -7913,13 +7913,13 @@
         <v>4.24</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>0.6422</v>
+        <v>0.5964</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>-0.263</v>
+        <v>-0.3088</v>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>0.7226</v>
+        <v>0.7088</v>
       </c>
       <c r="R37" s="5" t="n">
         <v>0.2</v>
@@ -8694,13 +8694,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K41" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.75</v>
+        <v>0.75</v>
       </c>
       <c r="M41" s="5" t="n">
         <v>0.75</v>
@@ -8709,13 +8709,13 @@
         <v>6.75</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.445</v>
+        <v>0.4351</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>-0.2342</v>
+        <v>-0.2441</v>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>0.5769</v>
+        <v>0.574</v>
       </c>
       <c r="R41" s="5" t="n">
         <v>0.4</v>
@@ -9074,13 +9074,13 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="K43" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L43" s="5" t="n">
-        <v>-4.65</v>
+        <v>4.65</v>
       </c>
       <c r="M43" s="5" t="n">
         <v>4.65</v>
@@ -9089,13 +9089,13 @@
         <v>7.85</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>0.493</v>
+        <v>0.5157</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>-0.4976</v>
+        <v>-0.4749</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>0.8479</v>
+        <v>0.8547</v>
       </c>
       <c r="R43" s="5" t="n">
         <v>0</v>
@@ -9258,13 +9258,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K44" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L44" s="3" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>0.3</v>
@@ -9273,13 +9273,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>0.4635</v>
+        <v>0.4735</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>-0.1109</v>
+        <v>-0.1009</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>0.6291</v>
+        <v>0.6321</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>0.2</v>
@@ -9470,13 +9470,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L45" s="5" t="n">
-        <v>-1.91</v>
+        <v>1.91</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>1.91</v>
@@ -9485,13 +9485,13 @@
         <v>6.59</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.4482</v>
+        <v>0.4415</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>-0.4233</v>
+        <v>-0.43</v>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>0.5443</v>
+        <v>0.5423</v>
       </c>
       <c r="R45" s="5" t="n">
         <v>0.4</v>
@@ -9870,13 +9870,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K47" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-1.74</v>
+        <v>1.74</v>
       </c>
       <c r="M47" s="5" t="n">
         <v>1.74</v>
@@ -9885,13 +9885,13 @@
         <v>9.76</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>0.4266</v>
+        <v>0.4807</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>-0.4238</v>
+        <v>-0.3697</v>
       </c>
       <c r="Q47" s="5" t="n">
-        <v>0.6705</v>
+        <v>0.6867</v>
       </c>
       <c r="R47" s="5" t="n">
         <v>0.2</v>
@@ -11034,13 +11034,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K53" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.61</v>
+        <v>0.61</v>
       </c>
       <c r="M53" s="5" t="n">
         <v>0.61</v>
@@ -11049,13 +11049,13 @@
         <v>7.89</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.3754</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>-0.1193</v>
+        <v>-0.2735</v>
       </c>
       <c r="Q53" s="5" t="n">
-        <v>0.6188</v>
+        <v>0.5725</v>
       </c>
       <c r="R53" s="5" t="n">
         <v>0.4</v>
@@ -11422,13 +11422,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K55" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L55" s="5" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="M55" s="5" t="n">
         <v>1.5</v>
@@ -11437,13 +11437,13 @@
         <v>5</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>0.5584</v>
+        <v>0.5625</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>-0.2592</v>
+        <v>-0.2551</v>
       </c>
       <c r="Q55" s="5" t="n">
-        <v>0.6343</v>
+        <v>0.6355</v>
       </c>
       <c r="R55" s="5" t="n">
         <v>0.33</v>
@@ -11606,13 +11606,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K56" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-1.75</v>
+        <v>1.75</v>
       </c>
       <c r="M56" s="3" t="n">
         <v>1.75</v>
@@ -11621,13 +11621,13 @@
         <v>4.75</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0.5866</v>
+        <v>0.5292</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.2654</v>
+        <v>-0.3228</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0.631</v>
+        <v>0.6137</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>0.4</v>
@@ -13046,13 +13046,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K63" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-1.18</v>
+        <v>1.18</v>
       </c>
       <c r="M63" s="5" t="n">
         <v>1.18</v>
@@ -13061,13 +13061,13 @@
         <v>9.32</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>0.4668</v>
+        <v>0.5016</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>-0.2978</v>
+        <v>-0.263</v>
       </c>
       <c r="Q63" s="5" t="n">
-        <v>0.6535</v>
+        <v>0.6639</v>
       </c>
       <c r="R63" s="5" t="n">
         <v>0.2</v>
@@ -13462,13 +13462,13 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="K65" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-1.06</v>
+        <v>1.06</v>
       </c>
       <c r="M65" s="5" t="n">
         <v>1.06</v>
@@ -13477,13 +13477,13 @@
         <v>11.44</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>0.4915</v>
+        <v>0.5179</v>
       </c>
       <c r="P65" s="5" t="n">
-        <v>-0.2517</v>
+        <v>-0.2253</v>
       </c>
       <c r="Q65" s="5" t="n">
-        <v>0.5324</v>
+        <v>0.5404</v>
       </c>
       <c r="R65" s="5" t="n">
         <v>0.4</v>
@@ -13862,13 +13862,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K67" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-1.23</v>
+        <v>1.23</v>
       </c>
       <c r="M67" s="5" t="n">
         <v>1.23</v>
@@ -13877,13 +13877,13 @@
         <v>9.27</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>0.4065</v>
+        <v>0.4211</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>-0.3667</v>
+        <v>-0.3521</v>
       </c>
       <c r="Q67" s="5" t="n">
-        <v>0.5887</v>
+        <v>0.5931</v>
       </c>
       <c r="R67" s="5" t="n">
         <v>0.33</v>
@@ -14046,13 +14046,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K68" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="M68" s="3" t="n">
         <v>0.02</v>
@@ -14061,13 +14061,13 @@
         <v>7.48</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.5265</v>
+        <v>0.4714</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.021</v>
+        <v>-0.0341</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.4533</v>
+        <v>0.4368</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.6</v>
@@ -14254,13 +14254,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K69" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-1.9</v>
+        <v>1.9</v>
       </c>
       <c r="M69" s="5" t="n">
         <v>1.9</v>
@@ -14269,13 +14269,13 @@
         <v>8.6</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>0.5023</v>
+        <v>0.5128</v>
       </c>
       <c r="P69" s="5" t="n">
-        <v>-0.3676</v>
+        <v>-0.3571</v>
       </c>
       <c r="Q69" s="5" t="n">
-        <v>0.6757</v>
+        <v>0.6788</v>
       </c>
       <c r="R69" s="5" t="n">
         <v>0.2</v>
@@ -14466,13 +14466,13 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K70" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-2.58</v>
+        <v>2.58</v>
       </c>
       <c r="M70" s="3" t="n">
         <v>2.58</v>
@@ -14481,13 +14481,13 @@
         <v>10.42</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.5708</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>-0.3242</v>
+        <v>-0.3587</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0.6639</v>
+        <v>0.6535</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.4</v>
@@ -15910,13 +15910,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K77" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-1.83</v>
+        <v>1.83</v>
       </c>
       <c r="M77" s="5" t="n">
         <v>1.83</v>
@@ -15925,13 +15925,13 @@
         <v>6.67</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>0.54</v>
+        <v>0.4979</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>-0.3221</v>
+        <v>-0.3642</v>
       </c>
       <c r="Q77" s="5" t="n">
-        <v>0.6288</v>
+        <v>0.6162</v>
       </c>
       <c r="R77" s="5" t="n">
         <v>0.33</v>
@@ -16094,13 +16094,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="M78" s="3" t="n">
         <v>0.05</v>
@@ -16109,13 +16109,13 @@
         <v>10.05</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0.4748</v>
+        <v>0.5149</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>-0.0377</v>
+        <v>0.0024</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0.5603</v>
+        <v>0.5724</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>0.2</v>
@@ -16306,13 +16306,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K79" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L79" s="5" t="n">
-        <v>-3.28</v>
+        <v>3.28</v>
       </c>
       <c r="M79" s="5" t="n">
         <v>3.28</v>
@@ -16321,13 +16321,13 @@
         <v>7.22</v>
       </c>
       <c r="O79" s="5" t="n">
-        <v>0.6572</v>
+        <v>0.4877</v>
       </c>
       <c r="P79" s="5" t="n">
-        <v>-0.3064</v>
+        <v>-0.476</v>
       </c>
       <c r="Q79" s="5" t="n">
-        <v>0.8972</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="R79" s="5" t="n">
         <v>0</v>
@@ -16494,13 +16494,13 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="K80" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L80" s="3" t="n">
-        <v>-0.98</v>
+        <v>0.98</v>
       </c>
       <c r="M80" s="3" t="n">
         <v>0.98</v>
@@ -16509,13 +16509,13 @@
         <v>14.52</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.3768</v>
+        <v>0.412</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>-0.3511</v>
+        <v>-0.3159</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.6059</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>0.4</v>
@@ -18130,13 +18130,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K88" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L88" s="3" t="n">
-        <v>-0.42</v>
+        <v>0.42</v>
       </c>
       <c r="M88" s="3" t="n">
         <v>0.42</v>
@@ -18145,13 +18145,13 @@
         <v>7.08</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>0.4945</v>
+        <v>0.4653</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>-0.1094</v>
+        <v>-0.1387</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>0.7007</v>
+        <v>0.6919</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>0.2</v>
@@ -18338,13 +18338,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K89" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.75</v>
+        <v>0.75</v>
       </c>
       <c r="M89" s="5" t="n">
         <v>0.75</v>
@@ -18353,13 +18353,13 @@
         <v>10.75</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>0.4565</v>
+        <v>0.5041</v>
       </c>
       <c r="P89" s="5" t="n">
-        <v>-0.2227</v>
+        <v>-0.175</v>
       </c>
       <c r="Q89" s="5" t="n">
-        <v>0.6269</v>
+        <v>0.6412</v>
       </c>
       <c r="R89" s="5" t="n">
         <v>0.2</v>
@@ -18550,13 +18550,13 @@
           <t>18.5</t>
         </is>
       </c>
-      <c r="K90" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-1.21</v>
+        <v>1.21</v>
       </c>
       <c r="M90" s="3" t="n">
         <v>1.21</v>
@@ -18565,13 +18565,13 @@
         <v>17.29</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>0.3772</v>
+        <v>0.4787</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-0.3935</v>
+        <v>-0.2919</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>0.523</v>
+        <v>0.5535</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>0.4</v>
@@ -19750,13 +19750,13 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="K96" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L96" s="3" t="n">
-        <v>-0.79</v>
+        <v>0.79</v>
       </c>
       <c r="M96" s="3" t="n">
         <v>0.79</v>
@@ -19765,13 +19765,13 @@
         <v>14.71</v>
       </c>
       <c r="O96" s="3" t="n">
-        <v>0.3512</v>
+        <v>0.429</v>
       </c>
       <c r="P96" s="3" t="n">
-        <v>-0.3361</v>
+        <v>-0.2583</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>0.5341</v>
+        <v>0.5574</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>0.4</v>
@@ -20554,13 +20554,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K100" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>-0.38</v>
+        <v>0.38</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>0.38</v>
@@ -20569,13 +20569,13 @@
         <v>14.12</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0.4592</v>
+        <v>0.4578</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>-0.1337</v>
+        <v>-0.1351</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0.5578</v>
+        <v>0.5574</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>0.4</v>
@@ -21146,13 +21146,13 @@
           <t>21.5</t>
         </is>
       </c>
-      <c r="K103" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L103" s="5" t="n">
-        <v>-2.54</v>
+        <v>2.54</v>
       </c>
       <c r="M103" s="5" t="n">
         <v>2.54</v>
@@ -21161,13 +21161,13 @@
         <v>18.96</v>
       </c>
       <c r="O103" s="5" t="n">
-        <v>0.3767</v>
+        <v>0.5342</v>
       </c>
       <c r="P103" s="5" t="n">
-        <v>-0.55</v>
+        <v>-0.3925</v>
       </c>
       <c r="Q103" s="5" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="R103" s="5" t="n">
         <v>0.4</v>
@@ -21570,13 +21570,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K105" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L105" s="5" t="n">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
       <c r="M105" s="5" t="n">
         <v>0.8</v>
@@ -21585,13 +21585,13 @@
         <v>10.7</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>0.443</v>
+        <v>0.5122</v>
       </c>
       <c r="P105" s="5" t="n">
-        <v>-0.247</v>
+        <v>-0.1778</v>
       </c>
       <c r="Q105" s="5" t="n">
-        <v>0.8329</v>
+        <v>0.8537</v>
       </c>
       <c r="R105" s="5" t="n">
         <v>0</v>
@@ -21706,32 +21706,32 @@
       <c r="B106" s="3" t="inlineStr"/>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G-F</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
@@ -21741,7 +21741,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
@@ -21750,31 +21750,31 @@
         </is>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>11.35</v>
+        <v>14.25</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.5359</v>
+        <v>0.4076</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.0015</v>
+        <v>-0.2708</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.6742</v>
+        <v>0.6522</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="S106" s="3" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="T106" s="3" t="n">
-        <v>11.5</v>
+        <v>14.4</v>
       </c>
       <c r="U106" s="3" t="n">
         <v>1</v>
@@ -21784,12 +21784,12 @@
       </c>
       <c r="W106" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X106" s="3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Y106" s="3" t="inlineStr">
@@ -21810,66 +21810,70 @@
       <c r="AB106" s="3" t="inlineStr"/>
       <c r="AC106" s="3" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AD106" s="3" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AE106" s="3" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AF106" s="3" t="inlineStr"/>
       <c r="AG106" s="3" t="inlineStr"/>
       <c r="AH106" s="3" t="n">
-        <v>25.47593598731441</v>
+        <v>43.02091283643649</v>
       </c>
       <c r="AI106" s="3" t="inlineStr"/>
       <c r="AJ106" s="3" t="n">
-        <v>-0.3000000000000007</v>
+        <v>-2.229000000000001</v>
       </c>
       <c r="AK106" s="3" t="inlineStr"/>
       <c r="AL106" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM106" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AN106" s="3" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AO106" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AP106" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AQ106" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AR106" s="3" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AO106" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AP106" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AQ106" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR106" s="3" t="inlineStr"/>
       <c r="AS106" s="3" t="inlineStr"/>
       <c r="AT106" s="3" t="inlineStr"/>
       <c r="AU106" s="3" t="inlineStr"/>
       <c r="AV106" s="3" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AW106" s="3" t="inlineStr"/>
@@ -21882,12 +21886,12 @@
       <c r="BD106" s="3" t="inlineStr"/>
       <c r="BE106" s="3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="BF106" s="3" t="inlineStr">
         <is>
-          <t>MIL +6.5 pt margin vs MEM, pts: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
+          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -21900,32 +21904,32 @@
       <c r="B107" s="5" t="inlineStr"/>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
@@ -21935,7 +21939,7 @@
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -21944,31 +21948,31 @@
         </is>
       </c>
       <c r="L107" s="5" t="n">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>14.25</v>
+        <v>11.35</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>0.4077</v>
+        <v>0.4537</v>
       </c>
       <c r="P107" s="5" t="n">
-        <v>-0.2708</v>
+        <v>-0.0837</v>
       </c>
       <c r="Q107" s="5" t="n">
-        <v>0.6522</v>
+        <v>0.6496</v>
       </c>
       <c r="R107" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="S107" s="5" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="T107" s="5" t="n">
-        <v>14.4</v>
+        <v>11.5</v>
       </c>
       <c r="U107" s="5" t="n">
         <v>1</v>
@@ -21978,12 +21982,12 @@
       </c>
       <c r="W107" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="X107" s="5" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y107" s="5" t="inlineStr">
@@ -22004,70 +22008,66 @@
       <c r="AB107" s="5" t="inlineStr"/>
       <c r="AC107" s="5" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AD107" s="5" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AE107" s="5" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AF107" s="5" t="inlineStr"/>
       <c r="AG107" s="5" t="inlineStr"/>
       <c r="AH107" s="5" t="n">
-        <v>43.02091283643649</v>
+        <v>25.47593598731441</v>
       </c>
       <c r="AI107" s="5" t="inlineStr"/>
       <c r="AJ107" s="5" t="n">
-        <v>-2.229000000000001</v>
+        <v>-0.3000000000000007</v>
       </c>
       <c r="AK107" s="5" t="inlineStr"/>
       <c r="AL107" s="5" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AM107" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AN107" s="5" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM107" s="5" t="inlineStr">
+      <c r="AO107" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AP107" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ107" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AN107" s="5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AO107" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AP107" s="5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AQ107" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AR107" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="AR107" s="5" t="inlineStr"/>
       <c r="AS107" s="5" t="inlineStr"/>
       <c r="AT107" s="5" t="inlineStr"/>
       <c r="AU107" s="5" t="inlineStr"/>
       <c r="AV107" s="5" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AW107" s="5" t="inlineStr"/>
@@ -22080,12 +22080,12 @@
       <c r="BD107" s="5" t="inlineStr"/>
       <c r="BE107" s="5" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BF107" s="5" t="inlineStr">
         <is>
-          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>MIL +6.5 pt margin vs MEM, pts: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -22098,32 +22098,32 @@
       <c r="B108" s="3" t="inlineStr"/>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
@@ -22133,7 +22133,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
@@ -22142,46 +22142,46 @@
         </is>
       </c>
       <c r="L108" s="3" t="n">
-        <v>-0.06</v>
+        <v>-1.42</v>
       </c>
       <c r="M108" s="3" t="n">
-        <v>0.06</v>
+        <v>1.42</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>3.94</v>
+        <v>17.92</v>
       </c>
       <c r="O108" s="3" t="n">
-        <v>0.6328</v>
+        <v>0.3537</v>
       </c>
       <c r="P108" s="3" t="n">
-        <v>0.1171</v>
+        <v>-0.452</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>0.6332</v>
+        <v>0.6311</v>
       </c>
       <c r="R108" s="3" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="S108" s="3" t="n">
-        <v>4</v>
+        <v>16.8</v>
       </c>
       <c r="T108" s="3" t="n">
-        <v>3.9</v>
+        <v>16.8</v>
       </c>
       <c r="U108" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V108" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W108" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X108" s="3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Y108" s="3" t="inlineStr">
@@ -22196,80 +22196,64 @@
       </c>
       <c r="AA108" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AB108" s="3" t="inlineStr"/>
       <c r="AC108" s="3" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AD108" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AE108" s="3" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AF108" s="3" t="inlineStr"/>
       <c r="AG108" s="3" t="inlineStr"/>
       <c r="AH108" s="3" t="n">
-        <v>55.4050452816699</v>
+        <v>51.42218858791706</v>
       </c>
       <c r="AI108" s="3" t="inlineStr"/>
       <c r="AJ108" s="3" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AK108" s="3" t="inlineStr"/>
       <c r="AL108" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AM108" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AN108" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AO108" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AP108" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ108" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AR108" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AS108" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AP108" s="3" t="inlineStr"/>
+      <c r="AQ108" s="3" t="inlineStr"/>
+      <c r="AR108" s="3" t="inlineStr"/>
+      <c r="AS108" s="3" t="inlineStr"/>
       <c r="AT108" s="3" t="inlineStr"/>
       <c r="AU108" s="3" t="inlineStr"/>
       <c r="AV108" s="3" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AW108" s="3" t="inlineStr"/>
@@ -22282,12 +22266,12 @@
       <c r="BD108" s="3" t="inlineStr"/>
       <c r="BE108" s="3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.991</t>
         </is>
       </c>
       <c r="BF108" s="3" t="inlineStr">
         <is>
-          <t>PHX +10.5 pt margin vs ?, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>MIN -2.5 pt margin vs CHA, pra: 0.99x game script (pick; spread_risk 0.98, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -22300,32 +22284,32 @@
       <c r="B109" s="5" t="inlineStr"/>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
@@ -22335,7 +22319,7 @@
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
@@ -22344,46 +22328,46 @@
         </is>
       </c>
       <c r="L109" s="5" t="n">
-        <v>1.42</v>
+        <v>0.06</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>1.42</v>
+        <v>0.06</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>17.92</v>
+        <v>3.94</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>0.3528</v>
+        <v>0.6019</v>
       </c>
       <c r="P109" s="5" t="n">
-        <v>-0.453</v>
+        <v>0.0863</v>
       </c>
       <c r="Q109" s="5" t="n">
-        <v>0.6308</v>
+        <v>0.6239</v>
       </c>
       <c r="R109" s="5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="S109" s="5" t="n">
-        <v>16.8</v>
+        <v>4</v>
       </c>
       <c r="T109" s="5" t="n">
-        <v>16.8</v>
+        <v>3.9</v>
       </c>
       <c r="U109" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V109" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W109" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>28</t>
         </is>
       </c>
       <c r="X109" s="5" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y109" s="5" t="inlineStr">
@@ -22398,64 +22382,80 @@
       </c>
       <c r="AA109" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AB109" s="5" t="inlineStr"/>
       <c r="AC109" s="5" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AD109" s="5" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE109" s="5" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AF109" s="5" t="inlineStr"/>
       <c r="AG109" s="5" t="inlineStr"/>
       <c r="AH109" s="5" t="n">
-        <v>51.42218858791706</v>
+        <v>55.4050452816699</v>
       </c>
       <c r="AI109" s="5" t="inlineStr"/>
       <c r="AJ109" s="5" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK109" s="5" t="inlineStr"/>
       <c r="AL109" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM109" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN109" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AO109" s="5" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AP109" s="5" t="inlineStr"/>
-      <c r="AQ109" s="5" t="inlineStr"/>
-      <c r="AR109" s="5" t="inlineStr"/>
-      <c r="AS109" s="5" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP109" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ109" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AR109" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS109" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AT109" s="5" t="inlineStr"/>
       <c r="AU109" s="5" t="inlineStr"/>
       <c r="AV109" s="5" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AW109" s="5" t="inlineStr"/>
@@ -22468,12 +22468,12 @@
       <c r="BD109" s="5" t="inlineStr"/>
       <c r="BE109" s="5" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BF109" s="5" t="inlineStr">
         <is>
-          <t>MIN -2.5 pt margin vs CHA, pra: 0.99x game script (pick; spread_risk 0.98, total_risk 1.02)</t>
+          <t>PHX +10.5 pt margin vs ?, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -22906,22 +22906,22 @@
       <c r="B113" s="5" t="inlineStr"/>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -22931,7 +22931,7 @@
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
@@ -22949,47 +22949,33 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="L113" s="5" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="M113" s="5" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="L113" s="5" t="inlineStr"/>
+      <c r="M113" s="5" t="inlineStr"/>
       <c r="N113" s="5" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>0.6364</v>
+        <v>0.703</v>
       </c>
       <c r="P113" s="5" t="n">
-        <v>0.1114</v>
+        <v>0.203</v>
       </c>
       <c r="Q113" s="5" t="n">
-        <v>0.5658</v>
-      </c>
-      <c r="R113" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S113" s="5" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="T113" s="5" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U113" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V113" s="5" t="n">
-        <v>2</v>
-      </c>
+        <v>0.5609</v>
+      </c>
+      <c r="R113" s="5" t="inlineStr"/>
+      <c r="S113" s="5" t="inlineStr"/>
+      <c r="T113" s="5" t="inlineStr"/>
+      <c r="U113" s="5" t="inlineStr"/>
+      <c r="V113" s="5" t="inlineStr"/>
       <c r="W113" s="5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="X113" s="5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Y113" s="5" t="inlineStr">
@@ -23004,82 +22990,34 @@
       </c>
       <c r="AA113" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB113" s="5" t="inlineStr"/>
-      <c r="AC113" s="5" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="AD113" s="5" t="inlineStr">
-        <is>
-          <t>13.6</t>
-        </is>
-      </c>
-      <c r="AE113" s="5" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AB113" s="5" t="inlineStr">
+        <is>
+          <t>NO_PROJECTION_OR_LINE</t>
+        </is>
+      </c>
+      <c r="AC113" s="5" t="inlineStr"/>
+      <c r="AD113" s="5" t="inlineStr"/>
+      <c r="AE113" s="5" t="inlineStr"/>
       <c r="AF113" s="5" t="inlineStr"/>
       <c r="AG113" s="5" t="inlineStr"/>
-      <c r="AH113" s="5" t="n">
-        <v>30.33616923822909</v>
-      </c>
+      <c r="AH113" s="5" t="inlineStr"/>
       <c r="AI113" s="5" t="inlineStr"/>
-      <c r="AJ113" s="5" t="n">
-        <v>-0.6500000000000004</v>
-      </c>
+      <c r="AJ113" s="5" t="inlineStr"/>
       <c r="AK113" s="5" t="inlineStr"/>
-      <c r="AL113" s="5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AM113" s="5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AN113" s="5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AO113" s="5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AP113" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ113" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR113" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AS113" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="AL113" s="5" t="inlineStr"/>
+      <c r="AM113" s="5" t="inlineStr"/>
+      <c r="AN113" s="5" t="inlineStr"/>
+      <c r="AO113" s="5" t="inlineStr"/>
+      <c r="AP113" s="5" t="inlineStr"/>
+      <c r="AQ113" s="5" t="inlineStr"/>
+      <c r="AR113" s="5" t="inlineStr"/>
+      <c r="AS113" s="5" t="inlineStr"/>
       <c r="AT113" s="5" t="inlineStr"/>
       <c r="AU113" s="5" t="inlineStr"/>
-      <c r="AV113" s="5" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
+      <c r="AV113" s="5" t="inlineStr"/>
       <c r="AW113" s="5" t="inlineStr"/>
       <c r="AX113" s="5" t="inlineStr"/>
       <c r="AY113" s="5" t="inlineStr"/>
@@ -23090,12 +23028,12 @@
       <c r="BD113" s="5" t="inlineStr"/>
       <c r="BE113" s="5" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BF113" s="5" t="inlineStr">
         <is>
-          <t>ORL +4.5 pt margin vs NO, pra: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
+          <t>CHA +2.5 pt margin vs MIN, pts: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -23108,32 +23046,32 @@
       <c r="B114" s="3" t="inlineStr"/>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Fantasy Score</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
@@ -23143,7 +23081,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
@@ -23157,13 +23095,13 @@
         <v>0</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0.703</v>
+        <v>0.6866</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>0.203</v>
+        <v>0.1866</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0.5609</v>
+        <v>0.556</v>
       </c>
       <c r="R114" s="3" t="inlineStr"/>
       <c r="S114" s="3" t="inlineStr"/>
@@ -23172,12 +23110,12 @@
       <c r="V114" s="3" t="inlineStr"/>
       <c r="W114" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>28</t>
         </is>
       </c>
       <c r="X114" s="3" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y114" s="3" t="inlineStr">
@@ -23230,12 +23168,12 @@
       <c r="BD114" s="3" t="inlineStr"/>
       <c r="BE114" s="3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.054</t>
         </is>
       </c>
       <c r="BF114" s="3" t="inlineStr">
         <is>
-          <t>CHA +2.5 pt margin vs MIN, pts: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
+          <t>PHX +10.5 pt margin vs ?, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -23248,27 +23186,27 @@
       <c r="B115" s="5" t="inlineStr"/>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:30:00-04:00</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -23312,7 +23250,7 @@
       <c r="V115" s="5" t="inlineStr"/>
       <c r="W115" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="X115" s="5" t="inlineStr">
@@ -23370,12 +23308,12 @@
       <c r="BD115" s="5" t="inlineStr"/>
       <c r="BE115" s="5" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>1.009</t>
         </is>
       </c>
       <c r="BF115" s="5" t="inlineStr">
         <is>
-          <t>PHX +10.5 pt margin vs ?, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>LAL +1.5 pt margin vs DAL, fantasy: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -23388,32 +23326,32 @@
       <c r="B116" s="3" t="inlineStr"/>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 19:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>Fantasy Score</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
@@ -23423,36 +23361,50 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K116" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="L116" s="3" t="inlineStr"/>
-      <c r="M116" s="3" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M116" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0.6866</v>
+        <v>0.6018</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0.1866</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="R116" s="3" t="inlineStr"/>
-      <c r="S116" s="3" t="inlineStr"/>
-      <c r="T116" s="3" t="inlineStr"/>
-      <c r="U116" s="3" t="inlineStr"/>
-      <c r="V116" s="3" t="inlineStr"/>
+        <v>0.5554</v>
+      </c>
+      <c r="R116" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S116" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="T116" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="U116" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V116" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="W116" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="X116" s="3" t="inlineStr">
@@ -23472,34 +23424,82 @@
       </c>
       <c r="AA116" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="AB116" s="3" t="inlineStr">
-        <is>
-          <t>NO_PROJECTION_OR_LINE</t>
-        </is>
-      </c>
-      <c r="AC116" s="3" t="inlineStr"/>
-      <c r="AD116" s="3" t="inlineStr"/>
-      <c r="AE116" s="3" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB116" s="3" t="inlineStr"/>
+      <c r="AC116" s="3" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="AD116" s="3" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="AE116" s="3" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
       <c r="AF116" s="3" t="inlineStr"/>
       <c r="AG116" s="3" t="inlineStr"/>
-      <c r="AH116" s="3" t="inlineStr"/>
+      <c r="AH116" s="3" t="n">
+        <v>30.33616923822909</v>
+      </c>
       <c r="AI116" s="3" t="inlineStr"/>
-      <c r="AJ116" s="3" t="inlineStr"/>
+      <c r="AJ116" s="3" t="n">
+        <v>-0.6500000000000004</v>
+      </c>
       <c r="AK116" s="3" t="inlineStr"/>
-      <c r="AL116" s="3" t="inlineStr"/>
-      <c r="AM116" s="3" t="inlineStr"/>
-      <c r="AN116" s="3" t="inlineStr"/>
-      <c r="AO116" s="3" t="inlineStr"/>
-      <c r="AP116" s="3" t="inlineStr"/>
-      <c r="AQ116" s="3" t="inlineStr"/>
-      <c r="AR116" s="3" t="inlineStr"/>
-      <c r="AS116" s="3" t="inlineStr"/>
+      <c r="AL116" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AM116" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AN116" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AO116" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AP116" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ116" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AR116" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AS116" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="AT116" s="3" t="inlineStr"/>
       <c r="AU116" s="3" t="inlineStr"/>
-      <c r="AV116" s="3" t="inlineStr"/>
+      <c r="AV116" s="3" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
       <c r="AW116" s="3" t="inlineStr"/>
       <c r="AX116" s="3" t="inlineStr"/>
       <c r="AY116" s="3" t="inlineStr"/>
@@ -23510,12 +23510,12 @@
       <c r="BD116" s="3" t="inlineStr"/>
       <c r="BE116" s="3" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>1.027</t>
         </is>
       </c>
       <c r="BF116" s="3" t="inlineStr">
         <is>
-          <t>LAL +1.5 pt margin vs DAL, fantasy: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
+          <t>ORL +4.5 pt margin vs NO, pra: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -34338,13 +34338,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-3.96</v>
+        <v>3.96</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>3.96</v>
@@ -34353,13 +34353,13 @@
         <v>6.54</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.5334</v>
+        <v>0.4319</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-0.4478</v>
+        <v>-0.5493</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>0.86</v>
+        <v>0.8296</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -36709,13 +36709,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-4.62</v>
+        <v>4.62</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>4.62</v>
@@ -36724,13 +36724,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.5829</v>
+        <v>0.4929</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-0.4074</v>
+        <v>-0.4973</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>0.6883</v>
+        <v>0.6613</v>
       </c>
       <c r="R7" s="5" t="n">
         <v>0.2</v>
@@ -37113,13 +37113,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-1.51</v>
+        <v>1.51</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>1.51</v>
@@ -37128,13 +37128,13 @@
         <v>4.99</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.5127</v>
+        <v>0.485</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>-0.3071</v>
+        <v>-0.3348</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>0.6137</v>
+        <v>0.6054</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>0.4</v>
@@ -37891,7 +37891,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -37901,22 +37901,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -37926,50 +37926,50 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-3.04</v>
+        <v>3.61</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>3.04</v>
+        <v>3.61</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>5.46</v>
+        <v>11.11</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>0.5987</v>
+        <v>0.9039</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-0.3556</v>
+        <v>-0.0698</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>0.7221</v>
+        <v>0.7146</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>6.1</v>
+        <v>10.2</v>
       </c>
       <c r="U13" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W13" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X13" s="5" t="inlineStr">
@@ -37989,80 +37989,76 @@
       </c>
       <c r="AA13" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="AB13" s="5" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB13" s="5" t="inlineStr">
+        <is>
+          <t>VOID_LOW_MINUTES_NON_A</t>
+        </is>
+      </c>
       <c r="AC13" s="5" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AD13" s="5" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AE13" s="5" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AF13" s="5" t="inlineStr"/>
       <c r="AG13" s="5" t="inlineStr"/>
       <c r="AH13" s="5" t="n">
-        <v>64.50400256848616</v>
+        <v>47.3143268513502</v>
       </c>
       <c r="AI13" s="5" t="inlineStr"/>
       <c r="AJ13" s="5" t="n">
-        <v>-1.325</v>
+        <v>0.4329999999999998</v>
       </c>
       <c r="AK13" s="5" t="inlineStr"/>
       <c r="AL13" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AM13" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN13" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AO13" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AP13" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ13" s="5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AR13" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AS13" s="5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AR13" s="5" t="inlineStr"/>
+      <c r="AS13" s="5" t="inlineStr"/>
       <c r="AT13" s="5" t="inlineStr"/>
       <c r="AU13" s="5" t="inlineStr"/>
       <c r="AV13" s="5" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AW13" s="5" t="inlineStr"/>
@@ -38075,12 +38071,12 @@
       <c r="BD13" s="5" t="inlineStr"/>
       <c r="BE13" s="5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="BF13" s="5" t="inlineStr">
         <is>
-          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -38095,7 +38091,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -38105,22 +38101,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -38130,7 +38126,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -38139,41 +38135,41 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>3.61</v>
+        <v>3.04</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>3.61</v>
+        <v>3.04</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>11.11</v>
+        <v>5.46</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.9039</v>
+        <v>0.5502</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-0.0698</v>
+        <v>-0.404</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.7146</v>
+        <v>0.7076</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>10.6</v>
+        <v>4.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>10.2</v>
+        <v>6.1</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
@@ -38193,76 +38189,80 @@
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB14" s="3" t="inlineStr">
-        <is>
-          <t>VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr"/>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AD14" s="3" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr"/>
       <c r="AG14" s="3" t="inlineStr"/>
       <c r="AH14" s="3" t="n">
-        <v>47.3143268513502</v>
+        <v>64.50400256848616</v>
       </c>
       <c r="AI14" s="3" t="inlineStr"/>
       <c r="AJ14" s="3" t="n">
-        <v>0.4329999999999998</v>
+        <v>-1.325</v>
       </c>
       <c r="AK14" s="3" t="inlineStr"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AO14" s="3" t="inlineStr">
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ14" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
       <c r="AT14" s="3" t="inlineStr"/>
       <c r="AU14" s="3" t="inlineStr"/>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr"/>
@@ -38275,12 +38275,12 @@
       <c r="BD14" s="3" t="inlineStr"/>
       <c r="BE14" s="3" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BF14" s="3" t="inlineStr">
         <is>
-          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -38749,13 +38749,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-1.96</v>
+        <v>1.96</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>1.96</v>
@@ -38764,13 +38764,13 @@
         <v>8.039999999999999</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.4745</v>
+        <v>0.463</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-0.4015</v>
+        <v>-0.4131</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>0.6247</v>
+        <v>0.6212</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>0.4</v>
@@ -39291,22 +39291,22 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Taylor Hendricks</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -39316,7 +39316,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -39326,55 +39326,55 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-2.04</v>
+        <v>5.41</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.04</v>
+        <v>5.41</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>4.46</v>
+        <v>15.41</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.5717</v>
+        <v>0.9096</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-0.3136</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.7014</v>
+        <v>0.6929</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>4.7</v>
+        <v>14.4</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -39389,76 +39389,72 @@
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="AB20" s="3" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>VOID_LOW_MINUTES_NON_A</t>
+        </is>
+      </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr"/>
       <c r="AG20" s="3" t="inlineStr"/>
       <c r="AH20" s="3" t="n">
-        <v>43.4930305891131</v>
+        <v>45.77015848134467</v>
       </c>
       <c r="AI20" s="3" t="inlineStr"/>
       <c r="AJ20" s="3" t="n">
-        <v>-0.5140000000000002</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3" t="inlineStr"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AQ20" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AR20" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr"/>
       <c r="AS20" s="3" t="inlineStr"/>
       <c r="AT20" s="3" t="inlineStr"/>
       <c r="AU20" s="3" t="inlineStr"/>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AW20" s="3" t="inlineStr"/>
@@ -39471,12 +39467,12 @@
       <c r="BD20" s="3" t="inlineStr"/>
       <c r="BE20" s="3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.045</t>
         </is>
       </c>
       <c r="BF20" s="3" t="inlineStr">
         <is>
-          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>BOS +9.5 pt margin vs TOR, pra: 1.04x game script (fav; spread_risk 1.05, total_risk 1.00)</t>
         </is>
       </c>
     </row>
@@ -39491,22 +39487,22 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Taylor Hendricks</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -39516,7 +39512,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -39526,7 +39522,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -39535,46 +39531,46 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>5.41</v>
+        <v>2.04</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>5.41</v>
+        <v>2.04</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>15.41</v>
+        <v>4.46</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.9096</v>
+        <v>0.497</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.3882</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>0.6929</v>
+        <v>0.679</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>14.4</v>
+        <v>4.7</v>
       </c>
       <c r="U21" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V21" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W21" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="X21" s="5" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Y21" s="5" t="inlineStr">
@@ -39589,72 +39585,76 @@
       </c>
       <c r="AA21" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB21" s="5" t="inlineStr">
-        <is>
-          <t>VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AB21" s="5" t="inlineStr"/>
       <c r="AC21" s="5" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AD21" s="5" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AE21" s="5" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AF21" s="5" t="inlineStr"/>
       <c r="AG21" s="5" t="inlineStr"/>
       <c r="AH21" s="5" t="n">
-        <v>45.77015848134467</v>
+        <v>43.4930305891131</v>
       </c>
       <c r="AI21" s="5" t="inlineStr"/>
       <c r="AJ21" s="5" t="n">
-        <v>0</v>
+        <v>-0.5140000000000002</v>
       </c>
       <c r="AK21" s="5" t="inlineStr"/>
       <c r="AL21" s="5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM21" s="5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN21" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO21" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AP21" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ21" s="5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AN21" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AO21" s="5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AP21" s="5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AQ21" s="5" t="inlineStr"/>
-      <c r="AR21" s="5" t="inlineStr"/>
+      <c r="AR21" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AS21" s="5" t="inlineStr"/>
       <c r="AT21" s="5" t="inlineStr"/>
       <c r="AU21" s="5" t="inlineStr"/>
       <c r="AV21" s="5" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AW21" s="5" t="inlineStr"/>
@@ -39667,12 +39667,12 @@
       <c r="BD21" s="5" t="inlineStr"/>
       <c r="BE21" s="5" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BF21" s="5" t="inlineStr">
         <is>
-          <t>BOS +9.5 pt margin vs TOR, pra: 1.04x game script (fav; spread_risk 1.05, total_risk 1.00)</t>
+          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -39725,13 +39725,13 @@
           <t>8</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.92</v>
+        <v>0.92</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0.92</v>
@@ -39740,13 +39740,13 @@
         <v>7.08</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.5419</v>
+        <v>0.5175</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>-0.1741</v>
+        <v>-0.1986</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.746</v>
+        <v>0.7387</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0</v>
@@ -39929,13 +39929,13 @@
           <t>11</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>-5.65</v>
+        <v>5.65</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>5.65</v>
@@ -39944,13 +39944,13 @@
         <v>5.35</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0.6911</v>
+        <v>0.6272</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>-0.3054</v>
+        <v>-0.3693</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>0.9073</v>
+        <v>0.8881</v>
       </c>
       <c r="R23" s="5" t="n">
         <v>0</v>
@@ -40109,13 +40109,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-3.02</v>
+        <v>3.02</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>3.02</v>
@@ -40124,13 +40124,13 @@
         <v>11.48</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.6384</v>
+        <v>0.5231</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-0.3149</v>
+        <v>-0.4302</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.7631</v>
+        <v>0.7285</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>0.2</v>
@@ -40513,13 +40513,13 @@
           <t>9.5</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>1.5</v>
@@ -40528,13 +40528,13 @@
         <v>8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>0.522</v>
+        <v>0.5165</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.2955</v>
+        <v>-0.3011</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>0.6816</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>0.2</v>
@@ -40725,13 +40725,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L27" s="5" t="n">
-        <v>-2.26</v>
+        <v>2.26</v>
       </c>
       <c r="M27" s="5" t="n">
         <v>2.26</v>
@@ -40740,13 +40740,13 @@
         <v>4.24</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0.6422</v>
+        <v>0.5964</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>-0.263</v>
+        <v>-0.3088</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>0.7226</v>
+        <v>0.7088</v>
       </c>
       <c r="R27" s="5" t="n">
         <v>0.2</v>
@@ -41888,13 +41888,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>-0.75</v>
+        <v>0.75</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>0.75</v>
@@ -41903,13 +41903,13 @@
         <v>6.75</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.445</v>
+        <v>0.4351</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>-0.2342</v>
+        <v>-0.2441</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.5769</v>
+        <v>0.574</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0.4</v>
@@ -42268,13 +42268,13 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>-4.65</v>
+        <v>4.65</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>4.65</v>
@@ -42283,13 +42283,13 @@
         <v>7.85</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.493</v>
+        <v>0.5157</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-0.4976</v>
+        <v>-0.4749</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.8479</v>
+        <v>0.8547</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
@@ -42452,13 +42452,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>0.3</v>
@@ -42467,13 +42467,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.4635</v>
+        <v>0.4735</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-0.1109</v>
+        <v>-0.1009</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>0.6291</v>
+        <v>0.6321</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0.2</v>
@@ -42664,13 +42664,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-1.91</v>
+        <v>1.91</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>1.91</v>
@@ -42679,13 +42679,13 @@
         <v>6.59</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.4482</v>
+        <v>0.4415</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.4233</v>
+        <v>-0.43</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.5443</v>
+        <v>0.5423</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0.4</v>
@@ -43064,13 +43064,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-1.74</v>
+        <v>1.74</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>1.74</v>
@@ -43079,13 +43079,13 @@
         <v>9.76</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.4266</v>
+        <v>0.4807</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-0.4238</v>
+        <v>-0.3697</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.6705</v>
+        <v>0.6867</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0.2</v>
@@ -44228,13 +44228,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>-0.61</v>
+        <v>0.61</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0.61</v>
@@ -44243,13 +44243,13 @@
         <v>7.89</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.3754</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-0.1193</v>
+        <v>-0.2735</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.6188</v>
+        <v>0.5725</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>0.4</v>
@@ -44616,13 +44616,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>1.5</v>
@@ -44631,13 +44631,13 @@
         <v>5</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.5584</v>
+        <v>0.5625</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.2592</v>
+        <v>-0.2551</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.6343</v>
+        <v>0.6355</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>0.33</v>
@@ -44800,13 +44800,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-1.75</v>
+        <v>1.75</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>1.75</v>
@@ -44815,13 +44815,13 @@
         <v>4.75</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.5866</v>
+        <v>0.5292</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-0.2654</v>
+        <v>-0.3228</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>0.631</v>
+        <v>0.6137</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>0.4</v>
@@ -46240,13 +46240,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-1.18</v>
+        <v>1.18</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>1.18</v>
@@ -46255,13 +46255,13 @@
         <v>9.32</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.4668</v>
+        <v>0.5016</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-0.2978</v>
+        <v>-0.263</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.6535</v>
+        <v>0.6639</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>0.2</v>
@@ -46656,13 +46656,13 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-1.06</v>
+        <v>1.06</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>1.06</v>
@@ -46671,13 +46671,13 @@
         <v>11.44</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>0.4915</v>
+        <v>0.5179</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.2517</v>
+        <v>-0.2253</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>0.5324</v>
+        <v>0.5404</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>0.4</v>
@@ -47056,13 +47056,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>-1.23</v>
+        <v>1.23</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>1.23</v>
@@ -47071,13 +47071,13 @@
         <v>9.27</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.4065</v>
+        <v>0.4211</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>-0.3667</v>
+        <v>-0.3521</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.5887</v>
+        <v>0.5931</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0.33</v>
@@ -47240,13 +47240,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="M29" s="5" t="n">
         <v>0.02</v>
@@ -47255,13 +47255,13 @@
         <v>7.48</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>0.5265</v>
+        <v>0.4714</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>0.021</v>
+        <v>-0.0341</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>0.4533</v>
+        <v>0.4368</v>
       </c>
       <c r="R29" s="5" t="n">
         <v>0.6</v>
@@ -47448,13 +47448,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-1.9</v>
+        <v>1.9</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>1.9</v>
@@ -47463,13 +47463,13 @@
         <v>8.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.5023</v>
+        <v>0.5128</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-0.3676</v>
+        <v>-0.3571</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0.6757</v>
+        <v>0.6788</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>0.2</v>
@@ -47660,13 +47660,13 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L31" s="5" t="n">
-        <v>-2.58</v>
+        <v>2.58</v>
       </c>
       <c r="M31" s="5" t="n">
         <v>2.58</v>
@@ -47675,13 +47675,13 @@
         <v>10.42</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.5708</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>-0.3242</v>
+        <v>-0.3587</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>0.6639</v>
+        <v>0.6535</v>
       </c>
       <c r="R31" s="5" t="n">
         <v>0.4</v>
@@ -49104,13 +49104,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K38" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-1.83</v>
+        <v>1.83</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>1.83</v>
@@ -49119,13 +49119,13 @@
         <v>6.67</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>0.54</v>
+        <v>0.4979</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>-0.3221</v>
+        <v>-0.3642</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>0.6288</v>
+        <v>0.6162</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>0.33</v>
@@ -49288,13 +49288,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="M39" s="5" t="n">
         <v>0.05</v>
@@ -49303,13 +49303,13 @@
         <v>10.05</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>0.4748</v>
+        <v>0.5149</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>-0.0377</v>
+        <v>0.0024</v>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>0.5603</v>
+        <v>0.5724</v>
       </c>
       <c r="R39" s="5" t="n">
         <v>0.2</v>
@@ -49500,13 +49500,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K40" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-3.28</v>
+        <v>3.28</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>3.28</v>
@@ -49515,13 +49515,13 @@
         <v>7.22</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0.6572</v>
+        <v>0.4877</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-0.3064</v>
+        <v>-0.476</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0.8972</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>0</v>
@@ -49688,13 +49688,13 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="K41" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.98</v>
+        <v>0.98</v>
       </c>
       <c r="M41" s="5" t="n">
         <v>0.98</v>
@@ -49703,13 +49703,13 @@
         <v>14.52</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.3768</v>
+        <v>0.412</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>-0.3511</v>
+        <v>-0.3159</v>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.6059</v>
       </c>
       <c r="R41" s="5" t="n">
         <v>0.4</v>
@@ -51324,13 +51324,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.42</v>
+        <v>0.42</v>
       </c>
       <c r="M49" s="5" t="n">
         <v>0.42</v>
@@ -51339,13 +51339,13 @@
         <v>7.08</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>0.4945</v>
+        <v>0.4653</v>
       </c>
       <c r="P49" s="5" t="n">
-        <v>-0.1094</v>
+        <v>-0.1387</v>
       </c>
       <c r="Q49" s="5" t="n">
-        <v>0.7007</v>
+        <v>0.6919</v>
       </c>
       <c r="R49" s="5" t="n">
         <v>0.2</v>
@@ -51532,13 +51532,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K50" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L50" s="3" t="n">
-        <v>-0.75</v>
+        <v>0.75</v>
       </c>
       <c r="M50" s="3" t="n">
         <v>0.75</v>
@@ -51547,13 +51547,13 @@
         <v>10.75</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>0.4565</v>
+        <v>0.5041</v>
       </c>
       <c r="P50" s="3" t="n">
-        <v>-0.2227</v>
+        <v>-0.175</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>0.6269</v>
+        <v>0.6412</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>0.2</v>
@@ -51744,13 +51744,13 @@
           <t>18.5</t>
         </is>
       </c>
-      <c r="K51" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L51" s="5" t="n">
-        <v>-1.21</v>
+        <v>1.21</v>
       </c>
       <c r="M51" s="5" t="n">
         <v>1.21</v>
@@ -51759,13 +51759,13 @@
         <v>17.29</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>0.3772</v>
+        <v>0.4787</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>-0.3935</v>
+        <v>-0.2919</v>
       </c>
       <c r="Q51" s="5" t="n">
-        <v>0.523</v>
+        <v>0.5535</v>
       </c>
       <c r="R51" s="5" t="n">
         <v>0.4</v>
@@ -52944,13 +52944,13 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="K57" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.79</v>
+        <v>0.79</v>
       </c>
       <c r="M57" s="5" t="n">
         <v>0.79</v>
@@ -52959,13 +52959,13 @@
         <v>14.71</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>0.3512</v>
+        <v>0.429</v>
       </c>
       <c r="P57" s="5" t="n">
-        <v>-0.3361</v>
+        <v>-0.2583</v>
       </c>
       <c r="Q57" s="5" t="n">
-        <v>0.5341</v>
+        <v>0.5574</v>
       </c>
       <c r="R57" s="5" t="n">
         <v>0.4</v>
@@ -53748,13 +53748,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K61" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.38</v>
+        <v>0.38</v>
       </c>
       <c r="M61" s="5" t="n">
         <v>0.38</v>
@@ -53763,13 +53763,13 @@
         <v>14.12</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>0.4592</v>
+        <v>0.4578</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>-0.1337</v>
+        <v>-0.1351</v>
       </c>
       <c r="Q61" s="5" t="n">
-        <v>0.5578</v>
+        <v>0.5574</v>
       </c>
       <c r="R61" s="5" t="n">
         <v>0.4</v>
@@ -54340,13 +54340,13 @@
           <t>21.5</t>
         </is>
       </c>
-      <c r="K64" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-2.54</v>
+        <v>2.54</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>2.54</v>
@@ -54355,13 +54355,13 @@
         <v>18.96</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0.3767</v>
+        <v>0.5342</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.3925</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>0.4</v>
@@ -54764,13 +54764,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K66" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
       <c r="M66" s="3" t="n">
         <v>0.8</v>
@@ -54779,13 +54779,13 @@
         <v>10.7</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>0.443</v>
+        <v>0.5122</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>-0.247</v>
+        <v>-0.1778</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0.8329</v>
+        <v>0.8537</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>0</v>
@@ -54900,32 +54900,32 @@
       <c r="B67" s="5" t="inlineStr"/>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G-F</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
@@ -54935,7 +54935,7 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
@@ -54944,31 +54944,31 @@
         </is>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>11.35</v>
+        <v>14.25</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>0.5359</v>
+        <v>0.4076</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.2708</v>
       </c>
       <c r="Q67" s="5" t="n">
-        <v>0.6742</v>
+        <v>0.6522</v>
       </c>
       <c r="R67" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="S67" s="5" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="T67" s="5" t="n">
-        <v>11.5</v>
+        <v>14.4</v>
       </c>
       <c r="U67" s="5" t="n">
         <v>1</v>
@@ -54978,12 +54978,12 @@
       </c>
       <c r="W67" s="5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X67" s="5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Y67" s="5" t="inlineStr">
@@ -55004,66 +55004,70 @@
       <c r="AB67" s="5" t="inlineStr"/>
       <c r="AC67" s="5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AD67" s="5" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AE67" s="5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AF67" s="5" t="inlineStr"/>
       <c r="AG67" s="5" t="inlineStr"/>
       <c r="AH67" s="5" t="n">
-        <v>25.47593598731441</v>
+        <v>43.02091283643649</v>
       </c>
       <c r="AI67" s="5" t="inlineStr"/>
       <c r="AJ67" s="5" t="n">
-        <v>-0.3000000000000007</v>
+        <v>-2.229000000000001</v>
       </c>
       <c r="AK67" s="5" t="inlineStr"/>
       <c r="AL67" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM67" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AN67" s="5" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AO67" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AP67" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AQ67" s="5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AR67" s="5" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AO67" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AP67" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AQ67" s="5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR67" s="5" t="inlineStr"/>
       <c r="AS67" s="5" t="inlineStr"/>
       <c r="AT67" s="5" t="inlineStr"/>
       <c r="AU67" s="5" t="inlineStr"/>
       <c r="AV67" s="5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AW67" s="5" t="inlineStr"/>
@@ -55076,12 +55080,12 @@
       <c r="BD67" s="5" t="inlineStr"/>
       <c r="BE67" s="5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="BF67" s="5" t="inlineStr">
         <is>
-          <t>MIL +6.5 pt margin vs MEM, pts: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
+          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -55094,32 +55098,32 @@
       <c r="B68" s="3" t="inlineStr"/>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -55129,7 +55133,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -55138,31 +55142,31 @@
         </is>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>14.25</v>
+        <v>11.35</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.4077</v>
+        <v>0.4537</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>-0.2708</v>
+        <v>-0.0837</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.6522</v>
+        <v>0.6496</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>14.4</v>
+        <v>11.5</v>
       </c>
       <c r="U68" s="3" t="n">
         <v>1</v>
@@ -55172,12 +55176,12 @@
       </c>
       <c r="W68" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
@@ -55198,70 +55202,66 @@
       <c r="AB68" s="3" t="inlineStr"/>
       <c r="AC68" s="3" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AD68" s="3" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AE68" s="3" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AF68" s="3" t="inlineStr"/>
       <c r="AG68" s="3" t="inlineStr"/>
       <c r="AH68" s="3" t="n">
-        <v>43.02091283643649</v>
+        <v>25.47593598731441</v>
       </c>
       <c r="AI68" s="3" t="inlineStr"/>
       <c r="AJ68" s="3" t="n">
-        <v>-2.229000000000001</v>
+        <v>-0.3000000000000007</v>
       </c>
       <c r="AK68" s="3" t="inlineStr"/>
       <c r="AL68" s="3" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM68" s="3" t="inlineStr">
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AP68" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ68" s="3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AN68" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AO68" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AP68" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AQ68" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AR68" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="AR68" s="3" t="inlineStr"/>
       <c r="AS68" s="3" t="inlineStr"/>
       <c r="AT68" s="3" t="inlineStr"/>
       <c r="AU68" s="3" t="inlineStr"/>
       <c r="AV68" s="3" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AW68" s="3" t="inlineStr"/>
@@ -55274,12 +55274,12 @@
       <c r="BD68" s="3" t="inlineStr"/>
       <c r="BE68" s="3" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BF68" s="3" t="inlineStr">
         <is>
-          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>MIL +6.5 pt margin vs MEM, pts: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -55292,32 +55292,32 @@
       <c r="B69" s="5" t="inlineStr"/>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
@@ -55327,7 +55327,7 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
@@ -55336,46 +55336,46 @@
         </is>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.06</v>
+        <v>-1.42</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>0.06</v>
+        <v>1.42</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>3.94</v>
+        <v>17.92</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>0.6328</v>
+        <v>0.3537</v>
       </c>
       <c r="P69" s="5" t="n">
-        <v>0.1171</v>
+        <v>-0.452</v>
       </c>
       <c r="Q69" s="5" t="n">
-        <v>0.6332</v>
+        <v>0.6311</v>
       </c>
       <c r="R69" s="5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="S69" s="5" t="n">
-        <v>4</v>
+        <v>16.8</v>
       </c>
       <c r="T69" s="5" t="n">
-        <v>3.9</v>
+        <v>16.8</v>
       </c>
       <c r="U69" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V69" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W69" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X69" s="5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Y69" s="5" t="inlineStr">
@@ -55390,80 +55390,64 @@
       </c>
       <c r="AA69" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AB69" s="5" t="inlineStr"/>
       <c r="AC69" s="5" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AD69" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AE69" s="5" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AF69" s="5" t="inlineStr"/>
       <c r="AG69" s="5" t="inlineStr"/>
       <c r="AH69" s="5" t="n">
-        <v>55.4050452816699</v>
+        <v>51.42218858791706</v>
       </c>
       <c r="AI69" s="5" t="inlineStr"/>
       <c r="AJ69" s="5" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AK69" s="5" t="inlineStr"/>
       <c r="AL69" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AM69" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AN69" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AO69" s="5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AP69" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ69" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AR69" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AS69" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AP69" s="5" t="inlineStr"/>
+      <c r="AQ69" s="5" t="inlineStr"/>
+      <c r="AR69" s="5" t="inlineStr"/>
+      <c r="AS69" s="5" t="inlineStr"/>
       <c r="AT69" s="5" t="inlineStr"/>
       <c r="AU69" s="5" t="inlineStr"/>
       <c r="AV69" s="5" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AW69" s="5" t="inlineStr"/>
@@ -55476,12 +55460,12 @@
       <c r="BD69" s="5" t="inlineStr"/>
       <c r="BE69" s="5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.991</t>
         </is>
       </c>
       <c r="BF69" s="5" t="inlineStr">
         <is>
-          <t>PHX +10.5 pt margin vs ?, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>MIN -2.5 pt margin vs CHA, pra: 0.99x game script (pick; spread_risk 0.98, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -55494,32 +55478,32 @@
       <c r="B70" s="3" t="inlineStr"/>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -55529,7 +55513,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -55538,46 +55522,46 @@
         </is>
       </c>
       <c r="L70" s="3" t="n">
-        <v>1.42</v>
+        <v>0.06</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>1.42</v>
+        <v>0.06</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>17.92</v>
+        <v>3.94</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0.3528</v>
+        <v>0.6019</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>-0.453</v>
+        <v>0.0863</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0.6308</v>
+        <v>0.6239</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>16.8</v>
+        <v>4</v>
       </c>
       <c r="T70" s="3" t="n">
-        <v>16.8</v>
+        <v>3.9</v>
       </c>
       <c r="U70" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V70" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>28</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
@@ -55592,64 +55576,80 @@
       </c>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr"/>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AD70" s="3" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE70" s="3" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AF70" s="3" t="inlineStr"/>
       <c r="AG70" s="3" t="inlineStr"/>
       <c r="AH70" s="3" t="n">
-        <v>51.42218858791706</v>
+        <v>55.4050452816699</v>
       </c>
       <c r="AI70" s="3" t="inlineStr"/>
       <c r="AJ70" s="3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK70" s="3" t="inlineStr"/>
       <c r="AL70" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM70" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN70" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AP70" s="3" t="inlineStr"/>
-      <c r="AQ70" s="3" t="inlineStr"/>
-      <c r="AR70" s="3" t="inlineStr"/>
-      <c r="AS70" s="3" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP70" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ70" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AR70" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AT70" s="3" t="inlineStr"/>
       <c r="AU70" s="3" t="inlineStr"/>
       <c r="AV70" s="3" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AW70" s="3" t="inlineStr"/>
@@ -55662,12 +55662,12 @@
       <c r="BD70" s="3" t="inlineStr"/>
       <c r="BE70" s="3" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BF70" s="3" t="inlineStr">
         <is>
-          <t>MIN -2.5 pt margin vs CHA, pra: 0.99x game script (pick; spread_risk 0.98, total_risk 1.02)</t>
+          <t>PHX +10.5 pt margin vs ?, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -56100,22 +56100,22 @@
       <c r="B74" s="3" t="inlineStr"/>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -56125,7 +56125,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -56135,7 +56135,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -56143,47 +56143,33 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="L74" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="M74" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="L74" s="3" t="inlineStr"/>
+      <c r="M74" s="3" t="inlineStr"/>
       <c r="N74" s="3" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>0.6364</v>
+        <v>0.703</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>0.1114</v>
+        <v>0.203</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>0.5658</v>
-      </c>
-      <c r="R74" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S74" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="T74" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U74" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V74" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>0.5609</v>
+      </c>
+      <c r="R74" s="3" t="inlineStr"/>
+      <c r="S74" s="3" t="inlineStr"/>
+      <c r="T74" s="3" t="inlineStr"/>
+      <c r="U74" s="3" t="inlineStr"/>
+      <c r="V74" s="3" t="inlineStr"/>
       <c r="W74" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
@@ -56198,82 +56184,34 @@
       </c>
       <c r="AA74" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB74" s="3" t="inlineStr"/>
-      <c r="AC74" s="3" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="AD74" s="3" t="inlineStr">
-        <is>
-          <t>13.6</t>
-        </is>
-      </c>
-      <c r="AE74" s="3" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AB74" s="3" t="inlineStr">
+        <is>
+          <t>NO_PROJECTION_OR_LINE</t>
+        </is>
+      </c>
+      <c r="AC74" s="3" t="inlineStr"/>
+      <c r="AD74" s="3" t="inlineStr"/>
+      <c r="AE74" s="3" t="inlineStr"/>
       <c r="AF74" s="3" t="inlineStr"/>
       <c r="AG74" s="3" t="inlineStr"/>
-      <c r="AH74" s="3" t="n">
-        <v>30.33616923822909</v>
-      </c>
+      <c r="AH74" s="3" t="inlineStr"/>
       <c r="AI74" s="3" t="inlineStr"/>
-      <c r="AJ74" s="3" t="n">
-        <v>-0.6500000000000004</v>
-      </c>
+      <c r="AJ74" s="3" t="inlineStr"/>
       <c r="AK74" s="3" t="inlineStr"/>
-      <c r="AL74" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AM74" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AN74" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AO74" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AP74" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ74" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR74" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AS74" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="AL74" s="3" t="inlineStr"/>
+      <c r="AM74" s="3" t="inlineStr"/>
+      <c r="AN74" s="3" t="inlineStr"/>
+      <c r="AO74" s="3" t="inlineStr"/>
+      <c r="AP74" s="3" t="inlineStr"/>
+      <c r="AQ74" s="3" t="inlineStr"/>
+      <c r="AR74" s="3" t="inlineStr"/>
+      <c r="AS74" s="3" t="inlineStr"/>
       <c r="AT74" s="3" t="inlineStr"/>
       <c r="AU74" s="3" t="inlineStr"/>
-      <c r="AV74" s="3" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
+      <c r="AV74" s="3" t="inlineStr"/>
       <c r="AW74" s="3" t="inlineStr"/>
       <c r="AX74" s="3" t="inlineStr"/>
       <c r="AY74" s="3" t="inlineStr"/>
@@ -56284,12 +56222,12 @@
       <c r="BD74" s="3" t="inlineStr"/>
       <c r="BE74" s="3" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BF74" s="3" t="inlineStr">
         <is>
-          <t>ORL +4.5 pt margin vs NO, pra: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
+          <t>CHA +2.5 pt margin vs MIN, pts: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -56302,32 +56240,32 @@
       <c r="B75" s="5" t="inlineStr"/>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Fantasy Score</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
@@ -56337,7 +56275,7 @@
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
@@ -56351,13 +56289,13 @@
         <v>0</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>0.703</v>
+        <v>0.6866</v>
       </c>
       <c r="P75" s="5" t="n">
-        <v>0.203</v>
+        <v>0.1866</v>
       </c>
       <c r="Q75" s="5" t="n">
-        <v>0.5609</v>
+        <v>0.556</v>
       </c>
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="5" t="inlineStr"/>
@@ -56366,12 +56304,12 @@
       <c r="V75" s="5" t="inlineStr"/>
       <c r="W75" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>28</t>
         </is>
       </c>
       <c r="X75" s="5" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y75" s="5" t="inlineStr">
@@ -56424,12 +56362,12 @@
       <c r="BD75" s="5" t="inlineStr"/>
       <c r="BE75" s="5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.054</t>
         </is>
       </c>
       <c r="BF75" s="5" t="inlineStr">
         <is>
-          <t>CHA +2.5 pt margin vs MIN, pts: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
+          <t>PHX +10.5 pt margin vs ?, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -56442,27 +56380,27 @@
       <c r="B76" s="3" t="inlineStr"/>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:30:00-04:00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -56506,7 +56444,7 @@
       <c r="V76" s="3" t="inlineStr"/>
       <c r="W76" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="X76" s="3" t="inlineStr">
@@ -56564,12 +56502,12 @@
       <c r="BD76" s="3" t="inlineStr"/>
       <c r="BE76" s="3" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>1.009</t>
         </is>
       </c>
       <c r="BF76" s="3" t="inlineStr">
         <is>
-          <t>PHX +10.5 pt margin vs ?, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>LAL +1.5 pt margin vs DAL, fantasy: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -56582,32 +56520,32 @@
       <c r="B77" s="5" t="inlineStr"/>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 19:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>Fantasy Score</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -56617,36 +56555,50 @@
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K77" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="inlineStr"/>
-      <c r="M77" s="5" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>0.1</v>
+      </c>
       <c r="N77" s="5" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>0.6866</v>
+        <v>0.6018</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>0.1866</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="Q77" s="5" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="R77" s="5" t="inlineStr"/>
-      <c r="S77" s="5" t="inlineStr"/>
-      <c r="T77" s="5" t="inlineStr"/>
-      <c r="U77" s="5" t="inlineStr"/>
-      <c r="V77" s="5" t="inlineStr"/>
+        <v>0.5554</v>
+      </c>
+      <c r="R77" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S77" s="5" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="T77" s="5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="U77" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V77" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="W77" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="X77" s="5" t="inlineStr">
@@ -56666,34 +56618,82 @@
       </c>
       <c r="AA77" s="5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="AB77" s="5" t="inlineStr">
-        <is>
-          <t>NO_PROJECTION_OR_LINE</t>
-        </is>
-      </c>
-      <c r="AC77" s="5" t="inlineStr"/>
-      <c r="AD77" s="5" t="inlineStr"/>
-      <c r="AE77" s="5" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB77" s="5" t="inlineStr"/>
+      <c r="AC77" s="5" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="AD77" s="5" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="AE77" s="5" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
       <c r="AF77" s="5" t="inlineStr"/>
       <c r="AG77" s="5" t="inlineStr"/>
-      <c r="AH77" s="5" t="inlineStr"/>
+      <c r="AH77" s="5" t="n">
+        <v>30.33616923822909</v>
+      </c>
       <c r="AI77" s="5" t="inlineStr"/>
-      <c r="AJ77" s="5" t="inlineStr"/>
+      <c r="AJ77" s="5" t="n">
+        <v>-0.6500000000000004</v>
+      </c>
       <c r="AK77" s="5" t="inlineStr"/>
-      <c r="AL77" s="5" t="inlineStr"/>
-      <c r="AM77" s="5" t="inlineStr"/>
-      <c r="AN77" s="5" t="inlineStr"/>
-      <c r="AO77" s="5" t="inlineStr"/>
-      <c r="AP77" s="5" t="inlineStr"/>
-      <c r="AQ77" s="5" t="inlineStr"/>
-      <c r="AR77" s="5" t="inlineStr"/>
-      <c r="AS77" s="5" t="inlineStr"/>
+      <c r="AL77" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AM77" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AN77" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AO77" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AP77" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ77" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AR77" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AS77" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="AT77" s="5" t="inlineStr"/>
       <c r="AU77" s="5" t="inlineStr"/>
-      <c r="AV77" s="5" t="inlineStr"/>
+      <c r="AV77" s="5" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
       <c r="AW77" s="5" t="inlineStr"/>
       <c r="AX77" s="5" t="inlineStr"/>
       <c r="AY77" s="5" t="inlineStr"/>
@@ -56704,12 +56704,12 @@
       <c r="BD77" s="5" t="inlineStr"/>
       <c r="BE77" s="5" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>1.027</t>
         </is>
       </c>
       <c r="BF77" s="5" t="inlineStr">
         <is>
-          <t>LAL +1.5 pt margin vs DAL, fantasy: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
+          <t>ORL +4.5 pt margin vs NO, pra: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
         </is>
       </c>
     </row>

--- a/NBA/step8_nba1h_direction_clean.xlsx
+++ b/NBA/step8_nba1h_direction_clean.xlsx
@@ -1878,13 +1878,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>3.96</v>
+        <v>-3.96</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>3.96</v>
@@ -1893,13 +1893,13 @@
         <v>6.54</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.4319</v>
+        <v>0.5334</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-0.5493</v>
+        <v>-0.4478</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>0.8296</v>
+        <v>0.86</v>
       </c>
       <c r="R7" s="5" t="n">
         <v>0</v>
@@ -3882,13 +3882,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>4.62</v>
+        <v>-4.62</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>4.62</v>
@@ -3897,13 +3897,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.4929</v>
+        <v>0.5829</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-0.4973</v>
+        <v>-0.4074</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>0.6613</v>
+        <v>0.6883</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>0.2</v>
@@ -4286,13 +4286,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>1.51</v>
+        <v>-1.51</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>1.51</v>
@@ -4301,13 +4301,13 @@
         <v>4.99</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.485</v>
+        <v>0.5127</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-0.3348</v>
+        <v>-0.3071</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>0.6054</v>
+        <v>0.6137</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0.4</v>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -5074,22 +5074,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -5099,50 +5099,50 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>3.61</v>
+        <v>-3.04</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>3.61</v>
+        <v>3.04</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>11.11</v>
+        <v>5.46</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0.9039</v>
+        <v>0.5987</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>-0.0698</v>
+        <v>-0.3556</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>0.7146</v>
+        <v>0.7221</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>10.6</v>
+        <v>4.8</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>10.2</v>
+        <v>6.1</v>
       </c>
       <c r="U23" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V23" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W23" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="X23" s="5" t="inlineStr">
@@ -5162,76 +5162,80 @@
       </c>
       <c r="AA23" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB23" s="5" t="inlineStr">
-        <is>
-          <t>VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AB23" s="5" t="inlineStr"/>
       <c r="AC23" s="5" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AD23" s="5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AE23" s="5" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AF23" s="5" t="inlineStr"/>
       <c r="AG23" s="5" t="inlineStr"/>
       <c r="AH23" s="5" t="n">
-        <v>47.3143268513502</v>
+        <v>64.50400256848616</v>
       </c>
       <c r="AI23" s="5" t="inlineStr"/>
       <c r="AJ23" s="5" t="n">
-        <v>0.4329999999999998</v>
+        <v>-1.325</v>
       </c>
       <c r="AK23" s="5" t="inlineStr"/>
       <c r="AL23" s="5" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM23" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN23" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AO23" s="5" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AM23" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AN23" s="5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AO23" s="5" t="inlineStr">
+      <c r="AP23" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ23" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AR23" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AS23" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AP23" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ23" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AR23" s="5" t="inlineStr"/>
-      <c r="AS23" s="5" t="inlineStr"/>
       <c r="AT23" s="5" t="inlineStr"/>
       <c r="AU23" s="5" t="inlineStr"/>
       <c r="AV23" s="5" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AW23" s="5" t="inlineStr"/>
@@ -5244,12 +5248,12 @@
       <c r="BD23" s="5" t="inlineStr"/>
       <c r="BE23" s="5" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BF23" s="5" t="inlineStr">
         <is>
-          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5268,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -5274,22 +5278,22 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -5299,7 +5303,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -5308,41 +5312,41 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>3.04</v>
+        <v>3.61</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>3.04</v>
+        <v>3.61</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>5.46</v>
+        <v>11.11</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.5502</v>
+        <v>0.9039</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-0.404</v>
+        <v>-0.0698</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.7076</v>
+        <v>0.7146</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>6.1</v>
+        <v>10.2</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
@@ -5362,80 +5366,76 @@
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="AB24" s="3" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>VOID_LOW_MINUTES_NON_A</t>
+        </is>
+      </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AD24" s="3" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr"/>
       <c r="AG24" s="3" t="inlineStr"/>
       <c r="AH24" s="3" t="n">
-        <v>64.50400256848616</v>
+        <v>47.3143268513502</v>
       </c>
       <c r="AI24" s="3" t="inlineStr"/>
       <c r="AJ24" s="3" t="n">
-        <v>-1.325</v>
+        <v>0.4329999999999998</v>
       </c>
       <c r="AK24" s="3" t="inlineStr"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AR24" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AS24" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AR24" s="3" t="inlineStr"/>
+      <c r="AS24" s="3" t="inlineStr"/>
       <c r="AT24" s="3" t="inlineStr"/>
       <c r="AU24" s="3" t="inlineStr"/>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AW24" s="3" t="inlineStr"/>
@@ -5448,12 +5448,12 @@
       <c r="BD24" s="3" t="inlineStr"/>
       <c r="BE24" s="3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="BF24" s="3" t="inlineStr">
         <is>
-          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -5922,13 +5922,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L27" s="5" t="n">
-        <v>1.96</v>
+        <v>-1.96</v>
       </c>
       <c r="M27" s="5" t="n">
         <v>1.96</v>
@@ -5937,13 +5937,13 @@
         <v>8.039999999999999</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0.463</v>
+        <v>0.4745</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>-0.4131</v>
+        <v>-0.4015</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>0.6212</v>
+        <v>0.6247</v>
       </c>
       <c r="R27" s="5" t="n">
         <v>0.4</v>
@@ -6464,22 +6464,22 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Taylor Hendricks</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -6499,55 +6499,55 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>5.41</v>
+        <v>-2.04</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>5.41</v>
+        <v>2.04</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>15.41</v>
+        <v>4.46</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.9096</v>
+        <v>0.5717</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.3136</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0.6929</v>
+        <v>0.7014</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>14.4</v>
+        <v>4.7</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -6562,72 +6562,76 @@
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB30" s="3" t="inlineStr">
-        <is>
-          <t>VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr"/>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AD30" s="3" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr"/>
       <c r="AG30" s="3" t="inlineStr"/>
       <c r="AH30" s="3" t="n">
-        <v>45.77015848134467</v>
+        <v>43.4930305891131</v>
       </c>
       <c r="AI30" s="3" t="inlineStr"/>
       <c r="AJ30" s="3" t="n">
-        <v>0</v>
+        <v>-0.5140000000000002</v>
       </c>
       <c r="AK30" s="3" t="inlineStr"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AO30" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AQ30" s="3" t="inlineStr"/>
-      <c r="AR30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AS30" s="3" t="inlineStr"/>
       <c r="AT30" s="3" t="inlineStr"/>
       <c r="AU30" s="3" t="inlineStr"/>
       <c r="AV30" s="3" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AW30" s="3" t="inlineStr"/>
@@ -6640,12 +6644,12 @@
       <c r="BD30" s="3" t="inlineStr"/>
       <c r="BE30" s="3" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BF30" s="3" t="inlineStr">
         <is>
-          <t>BOS +9.5 pt margin vs TOR, pra: 1.04x game script (fav; spread_risk 1.05, total_risk 1.00)</t>
+          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -6660,22 +6664,22 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Taylor Hendricks</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -6685,7 +6689,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -6695,7 +6699,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -6704,46 +6708,46 @@
         </is>
       </c>
       <c r="L31" s="5" t="n">
-        <v>2.04</v>
+        <v>5.41</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>2.04</v>
+        <v>5.41</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>4.46</v>
+        <v>15.41</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>0.497</v>
+        <v>0.9096</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>-0.3882</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>0.679</v>
+        <v>0.6929</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>4.7</v>
+        <v>14.4</v>
       </c>
       <c r="U31" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V31" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W31" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X31" s="5" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Y31" s="5" t="inlineStr">
@@ -6758,76 +6762,72 @@
       </c>
       <c r="AA31" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="AB31" s="5" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB31" s="5" t="inlineStr">
+        <is>
+          <t>VOID_LOW_MINUTES_NON_A</t>
+        </is>
+      </c>
       <c r="AC31" s="5" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AD31" s="5" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AE31" s="5" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AF31" s="5" t="inlineStr"/>
       <c r="AG31" s="5" t="inlineStr"/>
       <c r="AH31" s="5" t="n">
-        <v>43.4930305891131</v>
+        <v>45.77015848134467</v>
       </c>
       <c r="AI31" s="5" t="inlineStr"/>
       <c r="AJ31" s="5" t="n">
-        <v>-0.5140000000000002</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="5" t="inlineStr"/>
       <c r="AL31" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AM31" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AN31" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AO31" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AP31" s="5" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AQ31" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AR31" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AQ31" s="5" t="inlineStr"/>
+      <c r="AR31" s="5" t="inlineStr"/>
       <c r="AS31" s="5" t="inlineStr"/>
       <c r="AT31" s="5" t="inlineStr"/>
       <c r="AU31" s="5" t="inlineStr"/>
       <c r="AV31" s="5" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AW31" s="5" t="inlineStr"/>
@@ -6840,12 +6840,12 @@
       <c r="BD31" s="5" t="inlineStr"/>
       <c r="BE31" s="5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.045</t>
         </is>
       </c>
       <c r="BF31" s="5" t="inlineStr">
         <is>
-          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>BOS +9.5 pt margin vs TOR, pra: 1.04x game script (fav; spread_risk 1.05, total_risk 1.00)</t>
         </is>
       </c>
     </row>
@@ -6898,13 +6898,13 @@
           <t>8</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.92</v>
+        <v>-0.92</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>0.92</v>
@@ -6913,13 +6913,13 @@
         <v>7.08</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>0.5175</v>
+        <v>0.5419</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>-0.1986</v>
+        <v>-0.1741</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>0.7387</v>
+        <v>0.746</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>0</v>
@@ -7102,13 +7102,13 @@
           <t>11</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L33" s="5" t="n">
-        <v>5.65</v>
+        <v>-5.65</v>
       </c>
       <c r="M33" s="5" t="n">
         <v>5.65</v>
@@ -7117,13 +7117,13 @@
         <v>5.35</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>0.6272</v>
+        <v>0.6911</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>-0.3693</v>
+        <v>-0.3054</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>0.8881</v>
+        <v>0.9073</v>
       </c>
       <c r="R33" s="5" t="n">
         <v>0</v>
@@ -7282,13 +7282,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3.02</v>
+        <v>-3.02</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>3.02</v>
@@ -7297,13 +7297,13 @@
         <v>11.48</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0.5231</v>
+        <v>0.6384</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>-0.4302</v>
+        <v>-0.3149</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0.7285</v>
+        <v>0.7631</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>0.2</v>
@@ -7686,13 +7686,13 @@
           <t>9.5</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>1.5</v>
@@ -7701,13 +7701,13 @@
         <v>8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.5165</v>
+        <v>0.522</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.3011</v>
+        <v>-0.2955</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6816</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>0.2</v>
@@ -7898,13 +7898,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L37" s="5" t="n">
-        <v>2.26</v>
+        <v>-2.26</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>2.26</v>
@@ -7913,13 +7913,13 @@
         <v>4.24</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>0.5964</v>
+        <v>0.6422</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>-0.3088</v>
+        <v>-0.263</v>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>0.7088</v>
+        <v>0.7226</v>
       </c>
       <c r="R37" s="5" t="n">
         <v>0.2</v>
@@ -8694,13 +8694,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.75</v>
+        <v>-0.75</v>
       </c>
       <c r="M41" s="5" t="n">
         <v>0.75</v>
@@ -8709,13 +8709,13 @@
         <v>6.75</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.4351</v>
+        <v>0.445</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>-0.2441</v>
+        <v>-0.2342</v>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>0.574</v>
+        <v>0.5769</v>
       </c>
       <c r="R41" s="5" t="n">
         <v>0.4</v>
@@ -9074,13 +9074,13 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L43" s="5" t="n">
-        <v>4.65</v>
+        <v>-4.65</v>
       </c>
       <c r="M43" s="5" t="n">
         <v>4.65</v>
@@ -9089,13 +9089,13 @@
         <v>7.85</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>0.5157</v>
+        <v>0.493</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>-0.4749</v>
+        <v>-0.4976</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>0.8547</v>
+        <v>0.8479</v>
       </c>
       <c r="R43" s="5" t="n">
         <v>0</v>
@@ -9258,13 +9258,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>0.3</v>
@@ -9273,13 +9273,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>0.4735</v>
+        <v>0.4635</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>-0.1009</v>
+        <v>-0.1109</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>0.6321</v>
+        <v>0.6291</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>0.2</v>
@@ -9470,13 +9470,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L45" s="5" t="n">
-        <v>1.91</v>
+        <v>-1.91</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>1.91</v>
@@ -9485,13 +9485,13 @@
         <v>6.59</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.4415</v>
+        <v>0.4482</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>-0.43</v>
+        <v>-0.4233</v>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>0.5423</v>
+        <v>0.5443</v>
       </c>
       <c r="R45" s="5" t="n">
         <v>0.4</v>
@@ -9870,13 +9870,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L47" s="5" t="n">
-        <v>1.74</v>
+        <v>-1.74</v>
       </c>
       <c r="M47" s="5" t="n">
         <v>1.74</v>
@@ -9885,13 +9885,13 @@
         <v>9.76</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>0.4807</v>
+        <v>0.4266</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>-0.3697</v>
+        <v>-0.4238</v>
       </c>
       <c r="Q47" s="5" t="n">
-        <v>0.6867</v>
+        <v>0.6705</v>
       </c>
       <c r="R47" s="5" t="n">
         <v>0.2</v>
@@ -11034,13 +11034,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0.61</v>
+        <v>-0.61</v>
       </c>
       <c r="M53" s="5" t="n">
         <v>0.61</v>
@@ -11049,13 +11049,13 @@
         <v>7.89</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0.3754</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>-0.2735</v>
+        <v>-0.1193</v>
       </c>
       <c r="Q53" s="5" t="n">
-        <v>0.5725</v>
+        <v>0.6188</v>
       </c>
       <c r="R53" s="5" t="n">
         <v>0.4</v>
@@ -11422,13 +11422,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L55" s="5" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="M55" s="5" t="n">
         <v>1.5</v>
@@ -11437,13 +11437,13 @@
         <v>5</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>0.5625</v>
+        <v>0.5584</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>-0.2551</v>
+        <v>-0.2592</v>
       </c>
       <c r="Q55" s="5" t="n">
-        <v>0.6355</v>
+        <v>0.6343</v>
       </c>
       <c r="R55" s="5" t="n">
         <v>0.33</v>
@@ -11606,13 +11606,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>1.75</v>
+        <v>-1.75</v>
       </c>
       <c r="M56" s="3" t="n">
         <v>1.75</v>
@@ -11621,13 +11621,13 @@
         <v>4.75</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0.5292</v>
+        <v>0.5866</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.3228</v>
+        <v>-0.2654</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0.6137</v>
+        <v>0.631</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>0.4</v>
@@ -13046,13 +13046,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L63" s="5" t="n">
-        <v>1.18</v>
+        <v>-1.18</v>
       </c>
       <c r="M63" s="5" t="n">
         <v>1.18</v>
@@ -13061,13 +13061,13 @@
         <v>9.32</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>0.5016</v>
+        <v>0.4668</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>-0.263</v>
+        <v>-0.2978</v>
       </c>
       <c r="Q63" s="5" t="n">
-        <v>0.6639</v>
+        <v>0.6535</v>
       </c>
       <c r="R63" s="5" t="n">
         <v>0.2</v>
@@ -13462,13 +13462,13 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L65" s="5" t="n">
-        <v>1.06</v>
+        <v>-1.06</v>
       </c>
       <c r="M65" s="5" t="n">
         <v>1.06</v>
@@ -13477,13 +13477,13 @@
         <v>11.44</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>0.5179</v>
+        <v>0.4915</v>
       </c>
       <c r="P65" s="5" t="n">
-        <v>-0.2253</v>
+        <v>-0.2517</v>
       </c>
       <c r="Q65" s="5" t="n">
-        <v>0.5404</v>
+        <v>0.5324</v>
       </c>
       <c r="R65" s="5" t="n">
         <v>0.4</v>
@@ -13862,13 +13862,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L67" s="5" t="n">
-        <v>1.23</v>
+        <v>-1.23</v>
       </c>
       <c r="M67" s="5" t="n">
         <v>1.23</v>
@@ -13877,13 +13877,13 @@
         <v>9.27</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>0.4211</v>
+        <v>0.4065</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>-0.3521</v>
+        <v>-0.3667</v>
       </c>
       <c r="Q67" s="5" t="n">
-        <v>0.5931</v>
+        <v>0.5887</v>
       </c>
       <c r="R67" s="5" t="n">
         <v>0.33</v>
@@ -14046,13 +14046,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="M68" s="3" t="n">
         <v>0.02</v>
@@ -14061,13 +14061,13 @@
         <v>7.48</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.4714</v>
+        <v>0.5265</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>-0.0341</v>
+        <v>0.021</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.4368</v>
+        <v>0.4533</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.6</v>
@@ -14254,13 +14254,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L69" s="5" t="n">
-        <v>1.9</v>
+        <v>-1.9</v>
       </c>
       <c r="M69" s="5" t="n">
         <v>1.9</v>
@@ -14269,13 +14269,13 @@
         <v>8.6</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>0.5128</v>
+        <v>0.5023</v>
       </c>
       <c r="P69" s="5" t="n">
-        <v>-0.3571</v>
+        <v>-0.3676</v>
       </c>
       <c r="Q69" s="5" t="n">
-        <v>0.6788</v>
+        <v>0.6757</v>
       </c>
       <c r="R69" s="5" t="n">
         <v>0.2</v>
@@ -14466,13 +14466,13 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L70" s="3" t="n">
-        <v>2.58</v>
+        <v>-2.58</v>
       </c>
       <c r="M70" s="3" t="n">
         <v>2.58</v>
@@ -14481,13 +14481,13 @@
         <v>10.42</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0.5708</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>-0.3587</v>
+        <v>-0.3242</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0.6535</v>
+        <v>0.6639</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0.4</v>
@@ -15910,13 +15910,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L77" s="5" t="n">
-        <v>1.83</v>
+        <v>-1.83</v>
       </c>
       <c r="M77" s="5" t="n">
         <v>1.83</v>
@@ -15925,13 +15925,13 @@
         <v>6.67</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>0.4979</v>
+        <v>0.54</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>-0.3642</v>
+        <v>-0.3221</v>
       </c>
       <c r="Q77" s="5" t="n">
-        <v>0.6162</v>
+        <v>0.6288</v>
       </c>
       <c r="R77" s="5" t="n">
         <v>0.33</v>
@@ -16094,13 +16094,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K78" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L78" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="M78" s="3" t="n">
         <v>0.05</v>
@@ -16109,13 +16109,13 @@
         <v>10.05</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0.5149</v>
+        <v>0.4748</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0.0024</v>
+        <v>-0.0377</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0.5724</v>
+        <v>0.5603</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>0.2</v>
@@ -16306,13 +16306,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L79" s="5" t="n">
-        <v>3.28</v>
+        <v>-3.28</v>
       </c>
       <c r="M79" s="5" t="n">
         <v>3.28</v>
@@ -16321,13 +16321,13 @@
         <v>7.22</v>
       </c>
       <c r="O79" s="5" t="n">
-        <v>0.4877</v>
+        <v>0.6572</v>
       </c>
       <c r="P79" s="5" t="n">
-        <v>-0.476</v>
+        <v>-0.3064</v>
       </c>
       <c r="Q79" s="5" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8972</v>
       </c>
       <c r="R79" s="5" t="n">
         <v>0</v>
@@ -16494,13 +16494,13 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.98</v>
+        <v>-0.98</v>
       </c>
       <c r="M80" s="3" t="n">
         <v>0.98</v>
@@ -16509,13 +16509,13 @@
         <v>14.52</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.412</v>
+        <v>0.3768</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>-0.3159</v>
+        <v>-0.3511</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.6059</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>0.4</v>
@@ -18130,13 +18130,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K88" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.42</v>
+        <v>-0.42</v>
       </c>
       <c r="M88" s="3" t="n">
         <v>0.42</v>
@@ -18145,13 +18145,13 @@
         <v>7.08</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>0.4653</v>
+        <v>0.4945</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>-0.1387</v>
+        <v>-0.1094</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>0.6919</v>
+        <v>0.7007</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>0.2</v>
@@ -18338,13 +18338,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K89" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L89" s="5" t="n">
-        <v>0.75</v>
+        <v>-0.75</v>
       </c>
       <c r="M89" s="5" t="n">
         <v>0.75</v>
@@ -18353,13 +18353,13 @@
         <v>10.75</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>0.5041</v>
+        <v>0.4565</v>
       </c>
       <c r="P89" s="5" t="n">
-        <v>-0.175</v>
+        <v>-0.2227</v>
       </c>
       <c r="Q89" s="5" t="n">
-        <v>0.6412</v>
+        <v>0.6269</v>
       </c>
       <c r="R89" s="5" t="n">
         <v>0.2</v>
@@ -18550,13 +18550,13 @@
           <t>18.5</t>
         </is>
       </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L90" s="3" t="n">
-        <v>1.21</v>
+        <v>-1.21</v>
       </c>
       <c r="M90" s="3" t="n">
         <v>1.21</v>
@@ -18565,13 +18565,13 @@
         <v>17.29</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>0.4787</v>
+        <v>0.3772</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-0.2919</v>
+        <v>-0.3935</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>0.5535</v>
+        <v>0.523</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>0.4</v>
@@ -19750,13 +19750,13 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="K96" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L96" s="3" t="n">
-        <v>0.79</v>
+        <v>-0.79</v>
       </c>
       <c r="M96" s="3" t="n">
         <v>0.79</v>
@@ -19765,13 +19765,13 @@
         <v>14.71</v>
       </c>
       <c r="O96" s="3" t="n">
-        <v>0.429</v>
+        <v>0.3512</v>
       </c>
       <c r="P96" s="3" t="n">
-        <v>-0.2583</v>
+        <v>-0.3361</v>
       </c>
       <c r="Q96" s="3" t="n">
-        <v>0.5574</v>
+        <v>0.5341</v>
       </c>
       <c r="R96" s="3" t="n">
         <v>0.4</v>
@@ -20554,13 +20554,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K100" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0.38</v>
+        <v>-0.38</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>0.38</v>
@@ -20569,13 +20569,13 @@
         <v>14.12</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0.4578</v>
+        <v>0.4592</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>-0.1351</v>
+        <v>-0.1337</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0.5574</v>
+        <v>0.5578</v>
       </c>
       <c r="R100" s="3" t="n">
         <v>0.4</v>
@@ -21146,13 +21146,13 @@
           <t>21.5</t>
         </is>
       </c>
-      <c r="K103" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L103" s="5" t="n">
-        <v>2.54</v>
+        <v>-2.54</v>
       </c>
       <c r="M103" s="5" t="n">
         <v>2.54</v>
@@ -21161,13 +21161,13 @@
         <v>18.96</v>
       </c>
       <c r="O103" s="5" t="n">
-        <v>0.5342</v>
+        <v>0.3767</v>
       </c>
       <c r="P103" s="5" t="n">
-        <v>-0.3925</v>
+        <v>-0.55</v>
       </c>
       <c r="Q103" s="5" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="R103" s="5" t="n">
         <v>0.4</v>
@@ -21570,13 +21570,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K105" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L105" s="5" t="n">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
       <c r="M105" s="5" t="n">
         <v>0.8</v>
@@ -21585,13 +21585,13 @@
         <v>10.7</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>0.5122</v>
+        <v>0.443</v>
       </c>
       <c r="P105" s="5" t="n">
-        <v>-0.1778</v>
+        <v>-0.247</v>
       </c>
       <c r="Q105" s="5" t="n">
-        <v>0.8537</v>
+        <v>0.8329</v>
       </c>
       <c r="R105" s="5" t="n">
         <v>0</v>
@@ -21706,32 +21706,32 @@
       <c r="B106" s="3" t="inlineStr"/>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
@@ -21741,7 +21741,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
@@ -21750,31 +21750,31 @@
         </is>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>14.25</v>
+        <v>11.35</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.4076</v>
+        <v>0.5359</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.2708</v>
+        <v>-0.0015</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.6522</v>
+        <v>0.6742</v>
       </c>
       <c r="R106" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="S106" s="3" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="T106" s="3" t="n">
-        <v>14.4</v>
+        <v>11.5</v>
       </c>
       <c r="U106" s="3" t="n">
         <v>1</v>
@@ -21784,12 +21784,12 @@
       </c>
       <c r="W106" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="X106" s="3" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y106" s="3" t="inlineStr">
@@ -21810,70 +21810,66 @@
       <c r="AB106" s="3" t="inlineStr"/>
       <c r="AC106" s="3" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AD106" s="3" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AE106" s="3" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AF106" s="3" t="inlineStr"/>
       <c r="AG106" s="3" t="inlineStr"/>
       <c r="AH106" s="3" t="n">
-        <v>43.02091283643649</v>
+        <v>25.47593598731441</v>
       </c>
       <c r="AI106" s="3" t="inlineStr"/>
       <c r="AJ106" s="3" t="n">
-        <v>-2.229000000000001</v>
+        <v>-0.3000000000000007</v>
       </c>
       <c r="AK106" s="3" t="inlineStr"/>
       <c r="AL106" s="3" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AM106" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AN106" s="3" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM106" s="3" t="inlineStr">
+      <c r="AO106" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AP106" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ106" s="3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AN106" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AO106" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AP106" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AQ106" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AR106" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="AR106" s="3" t="inlineStr"/>
       <c r="AS106" s="3" t="inlineStr"/>
       <c r="AT106" s="3" t="inlineStr"/>
       <c r="AU106" s="3" t="inlineStr"/>
       <c r="AV106" s="3" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AW106" s="3" t="inlineStr"/>
@@ -21886,12 +21882,12 @@
       <c r="BD106" s="3" t="inlineStr"/>
       <c r="BE106" s="3" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BF106" s="3" t="inlineStr">
         <is>
-          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>MIL +6.5 pt margin vs MEM, pts: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -21904,32 +21900,32 @@
       <c r="B107" s="5" t="inlineStr"/>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G-F</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
@@ -21939,7 +21935,7 @@
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -21948,31 +21944,31 @@
         </is>
       </c>
       <c r="L107" s="5" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>11.35</v>
+        <v>14.25</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>0.4537</v>
+        <v>0.4077</v>
       </c>
       <c r="P107" s="5" t="n">
-        <v>-0.0837</v>
+        <v>-0.2708</v>
       </c>
       <c r="Q107" s="5" t="n">
-        <v>0.6496</v>
+        <v>0.6522</v>
       </c>
       <c r="R107" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="S107" s="5" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="T107" s="5" t="n">
-        <v>11.5</v>
+        <v>14.4</v>
       </c>
       <c r="U107" s="5" t="n">
         <v>1</v>
@@ -21982,12 +21978,12 @@
       </c>
       <c r="W107" s="5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X107" s="5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Y107" s="5" t="inlineStr">
@@ -22008,66 +22004,70 @@
       <c r="AB107" s="5" t="inlineStr"/>
       <c r="AC107" s="5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AD107" s="5" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AE107" s="5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AF107" s="5" t="inlineStr"/>
       <c r="AG107" s="5" t="inlineStr"/>
       <c r="AH107" s="5" t="n">
-        <v>25.47593598731441</v>
+        <v>43.02091283643649</v>
       </c>
       <c r="AI107" s="5" t="inlineStr"/>
       <c r="AJ107" s="5" t="n">
-        <v>-0.3000000000000007</v>
+        <v>-2.229000000000001</v>
       </c>
       <c r="AK107" s="5" t="inlineStr"/>
       <c r="AL107" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM107" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AN107" s="5" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AO107" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AP107" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AQ107" s="5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AR107" s="5" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AO107" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AP107" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AQ107" s="5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR107" s="5" t="inlineStr"/>
       <c r="AS107" s="5" t="inlineStr"/>
       <c r="AT107" s="5" t="inlineStr"/>
       <c r="AU107" s="5" t="inlineStr"/>
       <c r="AV107" s="5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AW107" s="5" t="inlineStr"/>
@@ -22080,12 +22080,12 @@
       <c r="BD107" s="5" t="inlineStr"/>
       <c r="BE107" s="5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="BF107" s="5" t="inlineStr">
         <is>
-          <t>MIL +6.5 pt margin vs MEM, pts: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
+          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -22098,32 +22098,32 @@
       <c r="B108" s="3" t="inlineStr"/>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
@@ -22133,7 +22133,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
@@ -22142,46 +22142,46 @@
         </is>
       </c>
       <c r="L108" s="3" t="n">
-        <v>-1.42</v>
+        <v>-0.06</v>
       </c>
       <c r="M108" s="3" t="n">
-        <v>1.42</v>
+        <v>0.06</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>17.92</v>
+        <v>3.94</v>
       </c>
       <c r="O108" s="3" t="n">
-        <v>0.3537</v>
+        <v>0.6328</v>
       </c>
       <c r="P108" s="3" t="n">
-        <v>-0.452</v>
+        <v>0.1171</v>
       </c>
       <c r="Q108" s="3" t="n">
-        <v>0.6311</v>
+        <v>0.6332</v>
       </c>
       <c r="R108" s="3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="S108" s="3" t="n">
-        <v>16.8</v>
+        <v>4</v>
       </c>
       <c r="T108" s="3" t="n">
-        <v>16.8</v>
+        <v>3.9</v>
       </c>
       <c r="U108" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V108" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W108" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>28</t>
         </is>
       </c>
       <c r="X108" s="3" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y108" s="3" t="inlineStr">
@@ -22196,64 +22196,80 @@
       </c>
       <c r="AA108" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AB108" s="3" t="inlineStr"/>
       <c r="AC108" s="3" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AD108" s="3" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE108" s="3" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AF108" s="3" t="inlineStr"/>
       <c r="AG108" s="3" t="inlineStr"/>
       <c r="AH108" s="3" t="n">
-        <v>51.42218858791706</v>
+        <v>55.4050452816699</v>
       </c>
       <c r="AI108" s="3" t="inlineStr"/>
       <c r="AJ108" s="3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK108" s="3" t="inlineStr"/>
       <c r="AL108" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM108" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN108" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AO108" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AP108" s="3" t="inlineStr"/>
-      <c r="AQ108" s="3" t="inlineStr"/>
-      <c r="AR108" s="3" t="inlineStr"/>
-      <c r="AS108" s="3" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP108" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ108" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AR108" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS108" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AT108" s="3" t="inlineStr"/>
       <c r="AU108" s="3" t="inlineStr"/>
       <c r="AV108" s="3" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AW108" s="3" t="inlineStr"/>
@@ -22266,12 +22282,12 @@
       <c r="BD108" s="3" t="inlineStr"/>
       <c r="BE108" s="3" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BF108" s="3" t="inlineStr">
         <is>
-          <t>MIN -2.5 pt margin vs CHA, pra: 0.99x game script (pick; spread_risk 0.98, total_risk 1.02)</t>
+          <t>PHX +10.5 pt margin vs ?, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -22284,32 +22300,32 @@
       <c r="B109" s="5" t="inlineStr"/>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
@@ -22319,7 +22335,7 @@
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
@@ -22328,46 +22344,46 @@
         </is>
       </c>
       <c r="L109" s="5" t="n">
-        <v>0.06</v>
+        <v>1.42</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>0.06</v>
+        <v>1.42</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>3.94</v>
+        <v>17.92</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>0.6019</v>
+        <v>0.3528</v>
       </c>
       <c r="P109" s="5" t="n">
-        <v>0.0863</v>
+        <v>-0.453</v>
       </c>
       <c r="Q109" s="5" t="n">
-        <v>0.6239</v>
+        <v>0.6308</v>
       </c>
       <c r="R109" s="5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="S109" s="5" t="n">
-        <v>4</v>
+        <v>16.8</v>
       </c>
       <c r="T109" s="5" t="n">
-        <v>3.9</v>
+        <v>16.8</v>
       </c>
       <c r="U109" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V109" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W109" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X109" s="5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Y109" s="5" t="inlineStr">
@@ -22382,80 +22398,64 @@
       </c>
       <c r="AA109" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AB109" s="5" t="inlineStr"/>
       <c r="AC109" s="5" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AD109" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AE109" s="5" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AF109" s="5" t="inlineStr"/>
       <c r="AG109" s="5" t="inlineStr"/>
       <c r="AH109" s="5" t="n">
-        <v>55.4050452816699</v>
+        <v>51.42218858791706</v>
       </c>
       <c r="AI109" s="5" t="inlineStr"/>
       <c r="AJ109" s="5" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AK109" s="5" t="inlineStr"/>
       <c r="AL109" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AM109" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AN109" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AO109" s="5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AP109" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ109" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AR109" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AS109" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AP109" s="5" t="inlineStr"/>
+      <c r="AQ109" s="5" t="inlineStr"/>
+      <c r="AR109" s="5" t="inlineStr"/>
+      <c r="AS109" s="5" t="inlineStr"/>
       <c r="AT109" s="5" t="inlineStr"/>
       <c r="AU109" s="5" t="inlineStr"/>
       <c r="AV109" s="5" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AW109" s="5" t="inlineStr"/>
@@ -22468,12 +22468,12 @@
       <c r="BD109" s="5" t="inlineStr"/>
       <c r="BE109" s="5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.991</t>
         </is>
       </c>
       <c r="BF109" s="5" t="inlineStr">
         <is>
-          <t>PHX +10.5 pt margin vs ?, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>MIN -2.5 pt margin vs CHA, pra: 0.99x game script (pick; spread_risk 0.98, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -22906,22 +22906,22 @@
       <c r="B113" s="5" t="inlineStr"/>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -22931,7 +22931,7 @@
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
@@ -22949,33 +22949,47 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="L113" s="5" t="inlineStr"/>
-      <c r="M113" s="5" t="inlineStr"/>
+      <c r="L113" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M113" s="5" t="n">
+        <v>0.1</v>
+      </c>
       <c r="N113" s="5" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>0.703</v>
+        <v>0.6364</v>
       </c>
       <c r="P113" s="5" t="n">
-        <v>0.203</v>
+        <v>0.1114</v>
       </c>
       <c r="Q113" s="5" t="n">
-        <v>0.5609</v>
-      </c>
-      <c r="R113" s="5" t="inlineStr"/>
-      <c r="S113" s="5" t="inlineStr"/>
-      <c r="T113" s="5" t="inlineStr"/>
-      <c r="U113" s="5" t="inlineStr"/>
-      <c r="V113" s="5" t="inlineStr"/>
+        <v>0.5658</v>
+      </c>
+      <c r="R113" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S113" s="5" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="T113" s="5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="U113" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V113" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="W113" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="X113" s="5" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y113" s="5" t="inlineStr">
@@ -22990,34 +23004,82 @@
       </c>
       <c r="AA113" s="5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="AB113" s="5" t="inlineStr">
-        <is>
-          <t>NO_PROJECTION_OR_LINE</t>
-        </is>
-      </c>
-      <c r="AC113" s="5" t="inlineStr"/>
-      <c r="AD113" s="5" t="inlineStr"/>
-      <c r="AE113" s="5" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB113" s="5" t="inlineStr"/>
+      <c r="AC113" s="5" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="AD113" s="5" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="AE113" s="5" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
       <c r="AF113" s="5" t="inlineStr"/>
       <c r="AG113" s="5" t="inlineStr"/>
-      <c r="AH113" s="5" t="inlineStr"/>
+      <c r="AH113" s="5" t="n">
+        <v>30.33616923822909</v>
+      </c>
       <c r="AI113" s="5" t="inlineStr"/>
-      <c r="AJ113" s="5" t="inlineStr"/>
+      <c r="AJ113" s="5" t="n">
+        <v>-0.6500000000000004</v>
+      </c>
       <c r="AK113" s="5" t="inlineStr"/>
-      <c r="AL113" s="5" t="inlineStr"/>
-      <c r="AM113" s="5" t="inlineStr"/>
-      <c r="AN113" s="5" t="inlineStr"/>
-      <c r="AO113" s="5" t="inlineStr"/>
-      <c r="AP113" s="5" t="inlineStr"/>
-      <c r="AQ113" s="5" t="inlineStr"/>
-      <c r="AR113" s="5" t="inlineStr"/>
-      <c r="AS113" s="5" t="inlineStr"/>
+      <c r="AL113" s="5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AM113" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AN113" s="5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AO113" s="5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AP113" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ113" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AR113" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AS113" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="AT113" s="5" t="inlineStr"/>
       <c r="AU113" s="5" t="inlineStr"/>
-      <c r="AV113" s="5" t="inlineStr"/>
+      <c r="AV113" s="5" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
       <c r="AW113" s="5" t="inlineStr"/>
       <c r="AX113" s="5" t="inlineStr"/>
       <c r="AY113" s="5" t="inlineStr"/>
@@ -23028,12 +23090,12 @@
       <c r="BD113" s="5" t="inlineStr"/>
       <c r="BE113" s="5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.027</t>
         </is>
       </c>
       <c r="BF113" s="5" t="inlineStr">
         <is>
-          <t>CHA +2.5 pt margin vs MIN, pts: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
+          <t>ORL +4.5 pt margin vs NO, pra: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -23046,32 +23108,32 @@
       <c r="B114" s="3" t="inlineStr"/>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>Fantasy Score</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
@@ -23081,7 +23143,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
@@ -23095,13 +23157,13 @@
         <v>0</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0.6866</v>
+        <v>0.703</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>0.1866</v>
+        <v>0.203</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0.556</v>
+        <v>0.5609</v>
       </c>
       <c r="R114" s="3" t="inlineStr"/>
       <c r="S114" s="3" t="inlineStr"/>
@@ -23110,12 +23172,12 @@
       <c r="V114" s="3" t="inlineStr"/>
       <c r="W114" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>11</t>
         </is>
       </c>
       <c r="X114" s="3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Y114" s="3" t="inlineStr">
@@ -23168,12 +23230,12 @@
       <c r="BD114" s="3" t="inlineStr"/>
       <c r="BE114" s="3" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BF114" s="3" t="inlineStr">
         <is>
-          <t>PHX +10.5 pt margin vs ?, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>CHA +2.5 pt margin vs MIN, pts: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -23186,27 +23248,27 @@
       <c r="B115" s="5" t="inlineStr"/>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 19:30:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H115" s="5" t="inlineStr">
@@ -23250,7 +23312,7 @@
       <c r="V115" s="5" t="inlineStr"/>
       <c r="W115" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="X115" s="5" t="inlineStr">
@@ -23308,12 +23370,12 @@
       <c r="BD115" s="5" t="inlineStr"/>
       <c r="BE115" s="5" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>1.054</t>
         </is>
       </c>
       <c r="BF115" s="5" t="inlineStr">
         <is>
-          <t>LAL +1.5 pt margin vs DAL, fantasy: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
+          <t>PHX +10.5 pt margin vs ?, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -23326,32 +23388,32 @@
       <c r="B116" s="3" t="inlineStr"/>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 19:30:00-04:00</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Fantasy Score</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
@@ -23361,50 +23423,36 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K116" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="L116" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M116" s="3" t="n">
-        <v>0.1</v>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr"/>
+      <c r="M116" s="3" t="inlineStr"/>
       <c r="N116" s="3" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0.6018</v>
+        <v>0.6866</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.1866</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0.5554</v>
-      </c>
-      <c r="R116" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S116" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="T116" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U116" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V116" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>0.556</v>
+      </c>
+      <c r="R116" s="3" t="inlineStr"/>
+      <c r="S116" s="3" t="inlineStr"/>
+      <c r="T116" s="3" t="inlineStr"/>
+      <c r="U116" s="3" t="inlineStr"/>
+      <c r="V116" s="3" t="inlineStr"/>
       <c r="W116" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="X116" s="3" t="inlineStr">
@@ -23424,82 +23472,34 @@
       </c>
       <c r="AA116" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB116" s="3" t="inlineStr"/>
-      <c r="AC116" s="3" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="AD116" s="3" t="inlineStr">
-        <is>
-          <t>13.6</t>
-        </is>
-      </c>
-      <c r="AE116" s="3" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AB116" s="3" t="inlineStr">
+        <is>
+          <t>NO_PROJECTION_OR_LINE</t>
+        </is>
+      </c>
+      <c r="AC116" s="3" t="inlineStr"/>
+      <c r="AD116" s="3" t="inlineStr"/>
+      <c r="AE116" s="3" t="inlineStr"/>
       <c r="AF116" s="3" t="inlineStr"/>
       <c r="AG116" s="3" t="inlineStr"/>
-      <c r="AH116" s="3" t="n">
-        <v>30.33616923822909</v>
-      </c>
+      <c r="AH116" s="3" t="inlineStr"/>
       <c r="AI116" s="3" t="inlineStr"/>
-      <c r="AJ116" s="3" t="n">
-        <v>-0.6500000000000004</v>
-      </c>
+      <c r="AJ116" s="3" t="inlineStr"/>
       <c r="AK116" s="3" t="inlineStr"/>
-      <c r="AL116" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AM116" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AN116" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AO116" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AP116" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ116" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR116" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AS116" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="AL116" s="3" t="inlineStr"/>
+      <c r="AM116" s="3" t="inlineStr"/>
+      <c r="AN116" s="3" t="inlineStr"/>
+      <c r="AO116" s="3" t="inlineStr"/>
+      <c r="AP116" s="3" t="inlineStr"/>
+      <c r="AQ116" s="3" t="inlineStr"/>
+      <c r="AR116" s="3" t="inlineStr"/>
+      <c r="AS116" s="3" t="inlineStr"/>
       <c r="AT116" s="3" t="inlineStr"/>
       <c r="AU116" s="3" t="inlineStr"/>
-      <c r="AV116" s="3" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
+      <c r="AV116" s="3" t="inlineStr"/>
       <c r="AW116" s="3" t="inlineStr"/>
       <c r="AX116" s="3" t="inlineStr"/>
       <c r="AY116" s="3" t="inlineStr"/>
@@ -23510,12 +23510,12 @@
       <c r="BD116" s="3" t="inlineStr"/>
       <c r="BE116" s="3" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1.009</t>
         </is>
       </c>
       <c r="BF116" s="3" t="inlineStr">
         <is>
-          <t>ORL +4.5 pt margin vs NO, pra: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
+          <t>LAL +1.5 pt margin vs DAL, fantasy: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -34338,13 +34338,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3.96</v>
+        <v>-3.96</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>3.96</v>
@@ -34353,13 +34353,13 @@
         <v>6.54</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.4319</v>
+        <v>0.5334</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-0.5493</v>
+        <v>-0.4478</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>0.8296</v>
+        <v>0.86</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -36709,13 +36709,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>4.62</v>
+        <v>-4.62</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>4.62</v>
@@ -36724,13 +36724,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.4929</v>
+        <v>0.5829</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-0.4973</v>
+        <v>-0.4074</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>0.6613</v>
+        <v>0.6883</v>
       </c>
       <c r="R7" s="5" t="n">
         <v>0.2</v>
@@ -37113,13 +37113,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>1.51</v>
+        <v>-1.51</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>1.51</v>
@@ -37128,13 +37128,13 @@
         <v>4.99</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.485</v>
+        <v>0.5127</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>-0.3348</v>
+        <v>-0.3071</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>0.6054</v>
+        <v>0.6137</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>0.4</v>
@@ -37891,7 +37891,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -37901,22 +37901,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -37926,50 +37926,50 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>3.61</v>
+        <v>-3.04</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>3.61</v>
+        <v>3.04</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>11.11</v>
+        <v>5.46</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>0.9039</v>
+        <v>0.5987</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-0.0698</v>
+        <v>-0.3556</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>0.7146</v>
+        <v>0.7221</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>10.6</v>
+        <v>4.8</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>10.2</v>
+        <v>6.1</v>
       </c>
       <c r="U13" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W13" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="X13" s="5" t="inlineStr">
@@ -37989,76 +37989,80 @@
       </c>
       <c r="AA13" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB13" s="5" t="inlineStr">
-        <is>
-          <t>VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AB13" s="5" t="inlineStr"/>
       <c r="AC13" s="5" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AD13" s="5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AE13" s="5" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AF13" s="5" t="inlineStr"/>
       <c r="AG13" s="5" t="inlineStr"/>
       <c r="AH13" s="5" t="n">
-        <v>47.3143268513502</v>
+        <v>64.50400256848616</v>
       </c>
       <c r="AI13" s="5" t="inlineStr"/>
       <c r="AJ13" s="5" t="n">
-        <v>0.4329999999999998</v>
+        <v>-1.325</v>
       </c>
       <c r="AK13" s="5" t="inlineStr"/>
       <c r="AL13" s="5" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM13" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN13" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AO13" s="5" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AM13" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AN13" s="5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AO13" s="5" t="inlineStr">
+      <c r="AP13" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ13" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AR13" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AS13" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AP13" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ13" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AR13" s="5" t="inlineStr"/>
-      <c r="AS13" s="5" t="inlineStr"/>
       <c r="AT13" s="5" t="inlineStr"/>
       <c r="AU13" s="5" t="inlineStr"/>
       <c r="AV13" s="5" t="inlineStr">
         <is>
-          <t>10.167</t>
+          <t>6.125</t>
         </is>
       </c>
       <c r="AW13" s="5" t="inlineStr"/>
@@ -38071,12 +38075,12 @@
       <c r="BD13" s="5" t="inlineStr"/>
       <c r="BE13" s="5" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BF13" s="5" t="inlineStr">
         <is>
-          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -38091,7 +38095,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Olivier-Maxence Prosper</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -38101,22 +38105,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -38126,7 +38130,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -38135,41 +38139,41 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>3.04</v>
+        <v>3.61</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>3.04</v>
+        <v>3.61</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>5.46</v>
+        <v>11.11</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.5502</v>
+        <v>0.9039</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-0.404</v>
+        <v>-0.0698</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.7076</v>
+        <v>0.7146</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>4.8</v>
+        <v>10.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>6.1</v>
+        <v>10.2</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
@@ -38189,80 +38193,76 @@
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="AB14" s="3" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>VOID_LOW_MINUTES_NON_A</t>
+        </is>
+      </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AD14" s="3" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr"/>
       <c r="AG14" s="3" t="inlineStr"/>
       <c r="AH14" s="3" t="n">
-        <v>64.50400256848616</v>
+        <v>47.3143268513502</v>
       </c>
       <c r="AI14" s="3" t="inlineStr"/>
       <c r="AJ14" s="3" t="n">
-        <v>-1.325</v>
+        <v>0.4329999999999998</v>
       </c>
       <c r="AK14" s="3" t="inlineStr"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AR14" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr"/>
+      <c r="AS14" s="3" t="inlineStr"/>
       <c r="AT14" s="3" t="inlineStr"/>
       <c r="AU14" s="3" t="inlineStr"/>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>6.125</t>
+          <t>10.167</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr"/>
@@ -38275,12 +38275,12 @@
       <c r="BD14" s="3" t="inlineStr"/>
       <c r="BE14" s="3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="BF14" s="3" t="inlineStr">
         <is>
-          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -38749,13 +38749,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>1.96</v>
+        <v>-1.96</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>1.96</v>
@@ -38764,13 +38764,13 @@
         <v>8.039999999999999</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.463</v>
+        <v>0.4745</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-0.4131</v>
+        <v>-0.4015</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>0.6212</v>
+        <v>0.6247</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>0.4</v>
@@ -39291,22 +39291,22 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Taylor Hendricks</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -39316,7 +39316,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -39326,55 +39326,55 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5.41</v>
+        <v>-2.04</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>5.41</v>
+        <v>2.04</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>15.41</v>
+        <v>4.46</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.9096</v>
+        <v>0.5717</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.3136</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.6929</v>
+        <v>0.7014</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>14.4</v>
+        <v>4.2</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>14.4</v>
+        <v>4.7</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -39389,72 +39389,76 @@
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB20" s="3" t="inlineStr">
-        <is>
-          <t>VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr"/>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr"/>
       <c r="AG20" s="3" t="inlineStr"/>
       <c r="AH20" s="3" t="n">
-        <v>45.77015848134467</v>
+        <v>43.4930305891131</v>
       </c>
       <c r="AI20" s="3" t="inlineStr"/>
       <c r="AJ20" s="3" t="n">
-        <v>0</v>
+        <v>-0.5140000000000002</v>
       </c>
       <c r="AK20" s="3" t="inlineStr"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AO20" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AQ20" s="3" t="inlineStr"/>
-      <c r="AR20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AS20" s="3" t="inlineStr"/>
       <c r="AT20" s="3" t="inlineStr"/>
       <c r="AU20" s="3" t="inlineStr"/>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>4.714</t>
         </is>
       </c>
       <c r="AW20" s="3" t="inlineStr"/>
@@ -39467,12 +39471,12 @@
       <c r="BD20" s="3" t="inlineStr"/>
       <c r="BE20" s="3" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BF20" s="3" t="inlineStr">
         <is>
-          <t>BOS +9.5 pt margin vs TOR, pra: 1.04x game script (fav; spread_risk 1.05, total_risk 1.00)</t>
+          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -39487,22 +39491,22 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Taylor Hendricks</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -39512,7 +39516,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -39522,7 +39526,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -39531,46 +39535,46 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>2.04</v>
+        <v>5.41</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>2.04</v>
+        <v>5.41</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>4.46</v>
+        <v>15.41</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.497</v>
+        <v>0.9096</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-0.3882</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>0.679</v>
+        <v>0.6929</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>4.2</v>
+        <v>14.4</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>4.7</v>
+        <v>14.4</v>
       </c>
       <c r="U21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V21" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W21" s="5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X21" s="5" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Y21" s="5" t="inlineStr">
@@ -39585,76 +39589,72 @@
       </c>
       <c r="AA21" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="AB21" s="5" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB21" s="5" t="inlineStr">
+        <is>
+          <t>VOID_LOW_MINUTES_NON_A</t>
+        </is>
+      </c>
       <c r="AC21" s="5" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AD21" s="5" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AE21" s="5" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AF21" s="5" t="inlineStr"/>
       <c r="AG21" s="5" t="inlineStr"/>
       <c r="AH21" s="5" t="n">
-        <v>43.4930305891131</v>
+        <v>45.77015848134467</v>
       </c>
       <c r="AI21" s="5" t="inlineStr"/>
       <c r="AJ21" s="5" t="n">
-        <v>-0.5140000000000002</v>
+        <v>0</v>
       </c>
       <c r="AK21" s="5" t="inlineStr"/>
       <c r="AL21" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AM21" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AN21" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AO21" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AP21" s="5" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AQ21" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AR21" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AQ21" s="5" t="inlineStr"/>
+      <c r="AR21" s="5" t="inlineStr"/>
       <c r="AS21" s="5" t="inlineStr"/>
       <c r="AT21" s="5" t="inlineStr"/>
       <c r="AU21" s="5" t="inlineStr"/>
       <c r="AV21" s="5" t="inlineStr">
         <is>
-          <t>4.714</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AW21" s="5" t="inlineStr"/>
@@ -39667,12 +39667,12 @@
       <c r="BD21" s="5" t="inlineStr"/>
       <c r="BE21" s="5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.045</t>
         </is>
       </c>
       <c r="BF21" s="5" t="inlineStr">
         <is>
-          <t>MEM -6.5 pt margin vs MIL, pts: 0.94x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>BOS +9.5 pt margin vs TOR, pra: 1.04x game script (fav; spread_risk 1.05, total_risk 1.00)</t>
         </is>
       </c>
     </row>
@@ -39725,13 +39725,13 @@
           <t>8</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.92</v>
+        <v>-0.92</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0.92</v>
@@ -39740,13 +39740,13 @@
         <v>7.08</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.5175</v>
+        <v>0.5419</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>-0.1986</v>
+        <v>-0.1741</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.7387</v>
+        <v>0.746</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0</v>
@@ -39929,13 +39929,13 @@
           <t>11</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L23" s="5" t="n">
-        <v>5.65</v>
+        <v>-5.65</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>5.65</v>
@@ -39944,13 +39944,13 @@
         <v>5.35</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0.6272</v>
+        <v>0.6911</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>-0.3693</v>
+        <v>-0.3054</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>0.8881</v>
+        <v>0.9073</v>
       </c>
       <c r="R23" s="5" t="n">
         <v>0</v>
@@ -40109,13 +40109,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>3.02</v>
+        <v>-3.02</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>3.02</v>
@@ -40124,13 +40124,13 @@
         <v>11.48</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.5231</v>
+        <v>0.6384</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-0.4302</v>
+        <v>-0.3149</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.7285</v>
+        <v>0.7631</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>0.2</v>
@@ -40513,13 +40513,13 @@
           <t>9.5</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>1.5</v>
@@ -40528,13 +40528,13 @@
         <v>8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>0.5165</v>
+        <v>0.522</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.3011</v>
+        <v>-0.2955</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6816</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>0.2</v>
@@ -40725,13 +40725,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L27" s="5" t="n">
-        <v>2.26</v>
+        <v>-2.26</v>
       </c>
       <c r="M27" s="5" t="n">
         <v>2.26</v>
@@ -40740,13 +40740,13 @@
         <v>4.24</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0.5964</v>
+        <v>0.6422</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>-0.3088</v>
+        <v>-0.263</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>0.7088</v>
+        <v>0.7226</v>
       </c>
       <c r="R27" s="5" t="n">
         <v>0.2</v>
@@ -41888,13 +41888,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.75</v>
+        <v>-0.75</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>0.75</v>
@@ -41903,13 +41903,13 @@
         <v>6.75</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.4351</v>
+        <v>0.445</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>-0.2441</v>
+        <v>-0.2342</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.574</v>
+        <v>0.5769</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0.4</v>
@@ -42268,13 +42268,13 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>4.65</v>
+        <v>-4.65</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>4.65</v>
@@ -42283,13 +42283,13 @@
         <v>7.85</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.5157</v>
+        <v>0.493</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-0.4749</v>
+        <v>-0.4976</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.8547</v>
+        <v>0.8479</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
@@ -42452,13 +42452,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>0.3</v>
@@ -42467,13 +42467,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.4735</v>
+        <v>0.4635</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-0.1009</v>
+        <v>-0.1109</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>0.6321</v>
+        <v>0.6291</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0.2</v>
@@ -42664,13 +42664,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1.91</v>
+        <v>-1.91</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>1.91</v>
@@ -42679,13 +42679,13 @@
         <v>6.59</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.4415</v>
+        <v>0.4482</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.4233</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.5423</v>
+        <v>0.5443</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0.4</v>
@@ -43064,13 +43064,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.74</v>
+        <v>-1.74</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>1.74</v>
@@ -43079,13 +43079,13 @@
         <v>9.76</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.4807</v>
+        <v>0.4266</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-0.3697</v>
+        <v>-0.4238</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.6867</v>
+        <v>0.6705</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0.2</v>
@@ -44228,13 +44228,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.61</v>
+        <v>-0.61</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0.61</v>
@@ -44243,13 +44243,13 @@
         <v>7.89</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.3754</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-0.2735</v>
+        <v>-0.1193</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>0.5725</v>
+        <v>0.6188</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>0.4</v>
@@ -44616,13 +44616,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.5</v>
+        <v>-1.5</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>1.5</v>
@@ -44631,13 +44631,13 @@
         <v>5</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.5625</v>
+        <v>0.5584</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.2551</v>
+        <v>-0.2592</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.6355</v>
+        <v>0.6343</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>0.33</v>
@@ -44800,13 +44800,13 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>1.75</v>
+        <v>-1.75</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>1.75</v>
@@ -44815,13 +44815,13 @@
         <v>4.75</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.5292</v>
+        <v>0.5866</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-0.3228</v>
+        <v>-0.2654</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>0.6137</v>
+        <v>0.631</v>
       </c>
       <c r="R17" s="5" t="n">
         <v>0.4</v>
@@ -46240,13 +46240,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1.18</v>
+        <v>-1.18</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>1.18</v>
@@ -46255,13 +46255,13 @@
         <v>9.32</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.5016</v>
+        <v>0.4668</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-0.263</v>
+        <v>-0.2978</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0.6639</v>
+        <v>0.6535</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>0.2</v>
@@ -46656,13 +46656,13 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>1.06</v>
+        <v>-1.06</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>1.06</v>
@@ -46671,13 +46671,13 @@
         <v>11.44</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>0.5179</v>
+        <v>0.4915</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-0.2253</v>
+        <v>-0.2517</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>0.5404</v>
+        <v>0.5324</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>0.4</v>
@@ -47056,13 +47056,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1.23</v>
+        <v>-1.23</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>1.23</v>
@@ -47071,13 +47071,13 @@
         <v>9.27</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.4211</v>
+        <v>0.4065</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>-0.3521</v>
+        <v>-0.3667</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.5931</v>
+        <v>0.5887</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0.33</v>
@@ -47240,13 +47240,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="M29" s="5" t="n">
         <v>0.02</v>
@@ -47255,13 +47255,13 @@
         <v>7.48</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>0.4714</v>
+        <v>0.5265</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>-0.0341</v>
+        <v>0.021</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>0.4368</v>
+        <v>0.4533</v>
       </c>
       <c r="R29" s="5" t="n">
         <v>0.6</v>
@@ -47448,13 +47448,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>1.9</v>
+        <v>-1.9</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>1.9</v>
@@ -47463,13 +47463,13 @@
         <v>8.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.5128</v>
+        <v>0.5023</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-0.3571</v>
+        <v>-0.3676</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0.6788</v>
+        <v>0.6757</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>0.2</v>
@@ -47660,13 +47660,13 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L31" s="5" t="n">
-        <v>2.58</v>
+        <v>-2.58</v>
       </c>
       <c r="M31" s="5" t="n">
         <v>2.58</v>
@@ -47675,13 +47675,13 @@
         <v>10.42</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>0.5708</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>-0.3587</v>
+        <v>-0.3242</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>0.6535</v>
+        <v>0.6639</v>
       </c>
       <c r="R31" s="5" t="n">
         <v>0.4</v>
@@ -49104,13 +49104,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L38" s="3" t="n">
-        <v>1.83</v>
+        <v>-1.83</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>1.83</v>
@@ -49119,13 +49119,13 @@
         <v>6.67</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>0.4979</v>
+        <v>0.54</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>-0.3642</v>
+        <v>-0.3221</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>0.6162</v>
+        <v>0.6288</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>0.33</v>
@@ -49288,13 +49288,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K39" s="6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>OVER</t>
         </is>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.05</v>
+        <v>0.05</v>
       </c>
       <c r="M39" s="5" t="n">
         <v>0.05</v>
@@ -49303,13 +49303,13 @@
         <v>10.05</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>0.5149</v>
+        <v>0.4748</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0377</v>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>0.5724</v>
+        <v>0.5603</v>
       </c>
       <c r="R39" s="5" t="n">
         <v>0.2</v>
@@ -49500,13 +49500,13 @@
           <t>10.5</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>3.28</v>
+        <v>-3.28</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>3.28</v>
@@ -49515,13 +49515,13 @@
         <v>7.22</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0.4877</v>
+        <v>0.6572</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-0.476</v>
+        <v>-0.3064</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.8972</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>0</v>
@@ -49688,13 +49688,13 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.98</v>
+        <v>-0.98</v>
       </c>
       <c r="M41" s="5" t="n">
         <v>0.98</v>
@@ -49703,13 +49703,13 @@
         <v>14.52</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.412</v>
+        <v>0.3768</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>-0.3159</v>
+        <v>-0.3511</v>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>0.6059</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="R41" s="5" t="n">
         <v>0.4</v>
@@ -51324,13 +51324,13 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.42</v>
+        <v>-0.42</v>
       </c>
       <c r="M49" s="5" t="n">
         <v>0.42</v>
@@ -51339,13 +51339,13 @@
         <v>7.08</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>0.4653</v>
+        <v>0.4945</v>
       </c>
       <c r="P49" s="5" t="n">
-        <v>-0.1387</v>
+        <v>-0.1094</v>
       </c>
       <c r="Q49" s="5" t="n">
-        <v>0.6919</v>
+        <v>0.7007</v>
       </c>
       <c r="R49" s="5" t="n">
         <v>0.2</v>
@@ -51532,13 +51532,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.75</v>
+        <v>-0.75</v>
       </c>
       <c r="M50" s="3" t="n">
         <v>0.75</v>
@@ -51547,13 +51547,13 @@
         <v>10.75</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>0.5041</v>
+        <v>0.4565</v>
       </c>
       <c r="P50" s="3" t="n">
-        <v>-0.175</v>
+        <v>-0.2227</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>0.6412</v>
+        <v>0.6269</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>0.2</v>
@@ -51744,13 +51744,13 @@
           <t>18.5</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L51" s="5" t="n">
-        <v>1.21</v>
+        <v>-1.21</v>
       </c>
       <c r="M51" s="5" t="n">
         <v>1.21</v>
@@ -51759,13 +51759,13 @@
         <v>17.29</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>0.4787</v>
+        <v>0.3772</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>-0.2919</v>
+        <v>-0.3935</v>
       </c>
       <c r="Q51" s="5" t="n">
-        <v>0.5535</v>
+        <v>0.523</v>
       </c>
       <c r="R51" s="5" t="n">
         <v>0.4</v>
@@ -52944,13 +52944,13 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L57" s="5" t="n">
-        <v>0.79</v>
+        <v>-0.79</v>
       </c>
       <c r="M57" s="5" t="n">
         <v>0.79</v>
@@ -52959,13 +52959,13 @@
         <v>14.71</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>0.429</v>
+        <v>0.3512</v>
       </c>
       <c r="P57" s="5" t="n">
-        <v>-0.2583</v>
+        <v>-0.3361</v>
       </c>
       <c r="Q57" s="5" t="n">
-        <v>0.5574</v>
+        <v>0.5341</v>
       </c>
       <c r="R57" s="5" t="n">
         <v>0.4</v>
@@ -53748,13 +53748,13 @@
           <t>14.5</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L61" s="5" t="n">
-        <v>0.38</v>
+        <v>-0.38</v>
       </c>
       <c r="M61" s="5" t="n">
         <v>0.38</v>
@@ -53763,13 +53763,13 @@
         <v>14.12</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>0.4578</v>
+        <v>0.4592</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>-0.1351</v>
+        <v>-0.1337</v>
       </c>
       <c r="Q61" s="5" t="n">
-        <v>0.5574</v>
+        <v>0.5578</v>
       </c>
       <c r="R61" s="5" t="n">
         <v>0.4</v>
@@ -54340,13 +54340,13 @@
           <t>21.5</t>
         </is>
       </c>
-      <c r="K64" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L64" s="3" t="n">
-        <v>2.54</v>
+        <v>-2.54</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>2.54</v>
@@ -54355,13 +54355,13 @@
         <v>18.96</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0.5342</v>
+        <v>0.3767</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>-0.3925</v>
+        <v>-0.55</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>0.4</v>
@@ -54764,13 +54764,13 @@
           <t>11.5</t>
         </is>
       </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
       <c r="M66" s="3" t="n">
         <v>0.8</v>
@@ -54779,13 +54779,13 @@
         <v>10.7</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>0.5122</v>
+        <v>0.443</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>-0.1778</v>
+        <v>-0.247</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0.8537</v>
+        <v>0.8329</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>0</v>
@@ -54900,32 +54900,32 @@
       <c r="B67" s="5" t="inlineStr"/>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
@@ -54935,7 +54935,7 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
@@ -54944,31 +54944,31 @@
         </is>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.75</v>
+        <v>-0.15</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0.75</v>
+        <v>0.15</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>14.25</v>
+        <v>11.35</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>0.4076</v>
+        <v>0.5359</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>-0.2708</v>
+        <v>-0.0015</v>
       </c>
       <c r="Q67" s="5" t="n">
-        <v>0.6522</v>
+        <v>0.6742</v>
       </c>
       <c r="R67" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="S67" s="5" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="T67" s="5" t="n">
-        <v>14.4</v>
+        <v>11.5</v>
       </c>
       <c r="U67" s="5" t="n">
         <v>1</v>
@@ -54978,12 +54978,12 @@
       </c>
       <c r="W67" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="X67" s="5" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y67" s="5" t="inlineStr">
@@ -55004,70 +55004,66 @@
       <c r="AB67" s="5" t="inlineStr"/>
       <c r="AC67" s="5" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AD67" s="5" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AE67" s="5" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AF67" s="5" t="inlineStr"/>
       <c r="AG67" s="5" t="inlineStr"/>
       <c r="AH67" s="5" t="n">
-        <v>43.02091283643649</v>
+        <v>25.47593598731441</v>
       </c>
       <c r="AI67" s="5" t="inlineStr"/>
       <c r="AJ67" s="5" t="n">
-        <v>-2.229000000000001</v>
+        <v>-0.3000000000000007</v>
       </c>
       <c r="AK67" s="5" t="inlineStr"/>
       <c r="AL67" s="5" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AM67" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AN67" s="5" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AM67" s="5" t="inlineStr">
+      <c r="AO67" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AP67" s="5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ67" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AN67" s="5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AO67" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AP67" s="5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AQ67" s="5" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AR67" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="AR67" s="5" t="inlineStr"/>
       <c r="AS67" s="5" t="inlineStr"/>
       <c r="AT67" s="5" t="inlineStr"/>
       <c r="AU67" s="5" t="inlineStr"/>
       <c r="AV67" s="5" t="inlineStr">
         <is>
-          <t>14.429</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AW67" s="5" t="inlineStr"/>
@@ -55080,12 +55076,12 @@
       <c r="BD67" s="5" t="inlineStr"/>
       <c r="BE67" s="5" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BF67" s="5" t="inlineStr">
         <is>
-          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
+          <t>MIL +6.5 pt margin vs MEM, pts: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -55098,32 +55094,32 @@
       <c r="B68" s="3" t="inlineStr"/>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G-F</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -55133,7 +55129,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -55142,31 +55138,31 @@
         </is>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>11.35</v>
+        <v>14.25</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.4537</v>
+        <v>0.4077</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>-0.0837</v>
+        <v>-0.2708</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.6496</v>
+        <v>0.6522</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>11.5</v>
+        <v>14.4</v>
       </c>
       <c r="U68" s="3" t="n">
         <v>1</v>
@@ -55176,12 +55172,12 @@
       </c>
       <c r="W68" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
@@ -55202,66 +55198,70 @@
       <c r="AB68" s="3" t="inlineStr"/>
       <c r="AC68" s="3" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AD68" s="3" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AE68" s="3" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AF68" s="3" t="inlineStr"/>
       <c r="AG68" s="3" t="inlineStr"/>
       <c r="AH68" s="3" t="n">
-        <v>25.47593598731441</v>
+        <v>43.02091283643649</v>
       </c>
       <c r="AI68" s="3" t="inlineStr"/>
       <c r="AJ68" s="3" t="n">
-        <v>-0.3000000000000007</v>
+        <v>-2.229000000000001</v>
       </c>
       <c r="AK68" s="3" t="inlineStr"/>
       <c r="AL68" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM68" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AN68" s="3" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AP68" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AQ68" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AR68" s="3" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AO68" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AP68" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AQ68" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AR68" s="3" t="inlineStr"/>
       <c r="AS68" s="3" t="inlineStr"/>
       <c r="AT68" s="3" t="inlineStr"/>
       <c r="AU68" s="3" t="inlineStr"/>
       <c r="AV68" s="3" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>14.429</t>
         </is>
       </c>
       <c r="AW68" s="3" t="inlineStr"/>
@@ -55274,12 +55274,12 @@
       <c r="BD68" s="3" t="inlineStr"/>
       <c r="BE68" s="3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="BF68" s="3" t="inlineStr">
         <is>
-          <t>MIL +6.5 pt margin vs MEM, pts: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
+          <t>NOP -4.5 pt margin vs ?, pra: 0.95x game script (dog; spread_risk 0.93, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -55292,32 +55292,32 @@
       <c r="B69" s="5" t="inlineStr"/>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Oso Ighodaro</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
@@ -55327,7 +55327,7 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
@@ -55336,46 +55336,46 @@
         </is>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-1.42</v>
+        <v>-0.06</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>1.42</v>
+        <v>0.06</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>17.92</v>
+        <v>3.94</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>0.3537</v>
+        <v>0.6328</v>
       </c>
       <c r="P69" s="5" t="n">
-        <v>-0.452</v>
+        <v>0.1171</v>
       </c>
       <c r="Q69" s="5" t="n">
-        <v>0.6311</v>
+        <v>0.6332</v>
       </c>
       <c r="R69" s="5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="S69" s="5" t="n">
-        <v>16.8</v>
+        <v>4</v>
       </c>
       <c r="T69" s="5" t="n">
-        <v>16.8</v>
+        <v>3.9</v>
       </c>
       <c r="U69" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V69" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W69" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>28</t>
         </is>
       </c>
       <c r="X69" s="5" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y69" s="5" t="inlineStr">
@@ -55390,64 +55390,80 @@
       </c>
       <c r="AA69" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AB69" s="5" t="inlineStr"/>
       <c r="AC69" s="5" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AD69" s="5" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE69" s="5" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AF69" s="5" t="inlineStr"/>
       <c r="AG69" s="5" t="inlineStr"/>
       <c r="AH69" s="5" t="n">
-        <v>51.42218858791706</v>
+        <v>55.4050452816699</v>
       </c>
       <c r="AI69" s="5" t="inlineStr"/>
       <c r="AJ69" s="5" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AK69" s="5" t="inlineStr"/>
       <c r="AL69" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM69" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN69" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AO69" s="5" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AP69" s="5" t="inlineStr"/>
-      <c r="AQ69" s="5" t="inlineStr"/>
-      <c r="AR69" s="5" t="inlineStr"/>
-      <c r="AS69" s="5" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP69" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ69" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AR69" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS69" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AT69" s="5" t="inlineStr"/>
       <c r="AU69" s="5" t="inlineStr"/>
       <c r="AV69" s="5" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>3.875</t>
         </is>
       </c>
       <c r="AW69" s="5" t="inlineStr"/>
@@ -55460,12 +55476,12 @@
       <c r="BD69" s="5" t="inlineStr"/>
       <c r="BE69" s="5" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BF69" s="5" t="inlineStr">
         <is>
-          <t>MIN -2.5 pt margin vs CHA, pra: 0.99x game script (pick; spread_risk 0.98, total_risk 1.02)</t>
+          <t>PHX +10.5 pt margin vs ?, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -55478,32 +55494,32 @@
       <c r="B70" s="3" t="inlineStr"/>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Oso Ighodaro</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -55513,7 +55529,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -55522,46 +55538,46 @@
         </is>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.06</v>
+        <v>1.42</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0.06</v>
+        <v>1.42</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>3.94</v>
+        <v>17.92</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0.6019</v>
+        <v>0.3528</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0.0863</v>
+        <v>-0.453</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0.6239</v>
+        <v>0.6308</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>4</v>
+        <v>16.8</v>
       </c>
       <c r="T70" s="3" t="n">
-        <v>3.9</v>
+        <v>16.8</v>
       </c>
       <c r="U70" s="3" t="n">
         <v>1</v>
       </c>
       <c r="V70" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
@@ -55576,80 +55592,64 @@
       </c>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr"/>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AD70" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AE70" s="3" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AF70" s="3" t="inlineStr"/>
       <c r="AG70" s="3" t="inlineStr"/>
       <c r="AH70" s="3" t="n">
-        <v>55.4050452816699</v>
+        <v>51.42218858791706</v>
       </c>
       <c r="AI70" s="3" t="inlineStr"/>
       <c r="AJ70" s="3" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AK70" s="3" t="inlineStr"/>
       <c r="AL70" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AM70" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AN70" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AP70" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AQ70" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AR70" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AS70" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AP70" s="3" t="inlineStr"/>
+      <c r="AQ70" s="3" t="inlineStr"/>
+      <c r="AR70" s="3" t="inlineStr"/>
+      <c r="AS70" s="3" t="inlineStr"/>
       <c r="AT70" s="3" t="inlineStr"/>
       <c r="AU70" s="3" t="inlineStr"/>
       <c r="AV70" s="3" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="AW70" s="3" t="inlineStr"/>
@@ -55662,12 +55662,12 @@
       <c r="BD70" s="3" t="inlineStr"/>
       <c r="BE70" s="3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.991</t>
         </is>
       </c>
       <c r="BF70" s="3" t="inlineStr">
         <is>
-          <t>PHX +10.5 pt margin vs ?, pts: 1.06x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>MIN -2.5 pt margin vs CHA, pra: 0.99x game script (pick; spread_risk 0.98, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -56100,22 +56100,22 @@
       <c r="B74" s="3" t="inlineStr"/>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NOP</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -56125,7 +56125,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -56135,7 +56135,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -56143,33 +56143,47 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="L74" s="3" t="inlineStr"/>
-      <c r="M74" s="3" t="inlineStr"/>
+      <c r="L74" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="N74" s="3" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>0.703</v>
+        <v>0.6364</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>0.203</v>
+        <v>0.1114</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>0.5609</v>
-      </c>
-      <c r="R74" s="3" t="inlineStr"/>
-      <c r="S74" s="3" t="inlineStr"/>
-      <c r="T74" s="3" t="inlineStr"/>
-      <c r="U74" s="3" t="inlineStr"/>
-      <c r="V74" s="3" t="inlineStr"/>
+        <v>0.5658</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S74" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="T74" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="U74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V74" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="W74" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
@@ -56184,34 +56198,82 @@
       </c>
       <c r="AA74" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="AB74" s="3" t="inlineStr">
-        <is>
-          <t>NO_PROJECTION_OR_LINE</t>
-        </is>
-      </c>
-      <c r="AC74" s="3" t="inlineStr"/>
-      <c r="AD74" s="3" t="inlineStr"/>
-      <c r="AE74" s="3" t="inlineStr"/>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="AB74" s="3" t="inlineStr"/>
+      <c r="AC74" s="3" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
+      <c r="AD74" s="3" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="AE74" s="3" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
       <c r="AF74" s="3" t="inlineStr"/>
       <c r="AG74" s="3" t="inlineStr"/>
-      <c r="AH74" s="3" t="inlineStr"/>
+      <c r="AH74" s="3" t="n">
+        <v>30.33616923822909</v>
+      </c>
       <c r="AI74" s="3" t="inlineStr"/>
-      <c r="AJ74" s="3" t="inlineStr"/>
+      <c r="AJ74" s="3" t="n">
+        <v>-0.6500000000000004</v>
+      </c>
       <c r="AK74" s="3" t="inlineStr"/>
-      <c r="AL74" s="3" t="inlineStr"/>
-      <c r="AM74" s="3" t="inlineStr"/>
-      <c r="AN74" s="3" t="inlineStr"/>
-      <c r="AO74" s="3" t="inlineStr"/>
-      <c r="AP74" s="3" t="inlineStr"/>
-      <c r="AQ74" s="3" t="inlineStr"/>
-      <c r="AR74" s="3" t="inlineStr"/>
-      <c r="AS74" s="3" t="inlineStr"/>
+      <c r="AL74" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AM74" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AN74" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AO74" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AP74" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ74" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AR74" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AS74" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="AT74" s="3" t="inlineStr"/>
       <c r="AU74" s="3" t="inlineStr"/>
-      <c r="AV74" s="3" t="inlineStr"/>
+      <c r="AV74" s="3" t="inlineStr">
+        <is>
+          <t>14.25</t>
+        </is>
+      </c>
       <c r="AW74" s="3" t="inlineStr"/>
       <c r="AX74" s="3" t="inlineStr"/>
       <c r="AY74" s="3" t="inlineStr"/>
@@ -56222,12 +56284,12 @@
       <c r="BD74" s="3" t="inlineStr"/>
       <c r="BE74" s="3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.027</t>
         </is>
       </c>
       <c r="BF74" s="3" t="inlineStr">
         <is>
-          <t>CHA +2.5 pt margin vs MIN, pts: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
+          <t>ORL +4.5 pt margin vs NO, pra: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -56240,32 +56302,32 @@
       <c r="B75" s="5" t="inlineStr"/>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 15:30:00-04:00</t>
+          <t>2026-04-05 19:00:00-04:00</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>Fantasy Score</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
@@ -56275,7 +56337,7 @@
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
@@ -56289,13 +56351,13 @@
         <v>0</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>0.6866</v>
+        <v>0.703</v>
       </c>
       <c r="P75" s="5" t="n">
-        <v>0.1866</v>
+        <v>0.203</v>
       </c>
       <c r="Q75" s="5" t="n">
-        <v>0.556</v>
+        <v>0.5609</v>
       </c>
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="5" t="inlineStr"/>
@@ -56304,12 +56366,12 @@
       <c r="V75" s="5" t="inlineStr"/>
       <c r="W75" s="5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>11</t>
         </is>
       </c>
       <c r="X75" s="5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Y75" s="5" t="inlineStr">
@@ -56362,12 +56424,12 @@
       <c r="BD75" s="5" t="inlineStr"/>
       <c r="BE75" s="5" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BF75" s="5" t="inlineStr">
         <is>
-          <t>PHX +10.5 pt margin vs ?, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
+          <t>CHA +2.5 pt margin vs MIN, pts: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -56380,27 +56442,27 @@
       <c r="B76" s="3" t="inlineStr"/>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-04-05 19:30:00-04:00</t>
+          <t>2026-04-05 15:30:00-04:00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
@@ -56444,7 +56506,7 @@
       <c r="V76" s="3" t="inlineStr"/>
       <c r="W76" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="X76" s="3" t="inlineStr">
@@ -56502,12 +56564,12 @@
       <c r="BD76" s="3" t="inlineStr"/>
       <c r="BE76" s="3" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>1.054</t>
         </is>
       </c>
       <c r="BF76" s="3" t="inlineStr">
         <is>
-          <t>LAL +1.5 pt margin vs DAL, fantasy: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
+          <t>PHX +10.5 pt margin vs ?, fantasy: 1.05x game script (fav; spread_risk 1.05, total_risk 1.02)</t>
         </is>
       </c>
     </row>
@@ -56520,32 +56582,32 @@
       <c r="B77" s="5" t="inlineStr"/>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>2026-04-05 19:00:00-04:00</t>
+          <t>2026-04-05 19:30:00-04:00</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Fantasy Score</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -56555,50 +56617,36 @@
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M77" s="5" t="n">
-        <v>0.1</v>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr"/>
+      <c r="M77" s="5" t="inlineStr"/>
       <c r="N77" s="5" t="n">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>0.6018</v>
+        <v>0.6866</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.1866</v>
       </c>
       <c r="Q77" s="5" t="n">
-        <v>0.5554</v>
-      </c>
-      <c r="R77" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S77" s="5" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="T77" s="5" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U77" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V77" s="5" t="n">
-        <v>2</v>
-      </c>
+        <v>0.556</v>
+      </c>
+      <c r="R77" s="5" t="inlineStr"/>
+      <c r="S77" s="5" t="inlineStr"/>
+      <c r="T77" s="5" t="inlineStr"/>
+      <c r="U77" s="5" t="inlineStr"/>
+      <c r="V77" s="5" t="inlineStr"/>
       <c r="W77" s="5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="X77" s="5" t="inlineStr">
@@ -56618,82 +56666,34 @@
       </c>
       <c r="AA77" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AB77" s="5" t="inlineStr"/>
-      <c r="AC77" s="5" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
-      <c r="AD77" s="5" t="inlineStr">
-        <is>
-          <t>13.6</t>
-        </is>
-      </c>
-      <c r="AE77" s="5" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AB77" s="5" t="inlineStr">
+        <is>
+          <t>NO_PROJECTION_OR_LINE</t>
+        </is>
+      </c>
+      <c r="AC77" s="5" t="inlineStr"/>
+      <c r="AD77" s="5" t="inlineStr"/>
+      <c r="AE77" s="5" t="inlineStr"/>
       <c r="AF77" s="5" t="inlineStr"/>
       <c r="AG77" s="5" t="inlineStr"/>
-      <c r="AH77" s="5" t="n">
-        <v>30.33616923822909</v>
-      </c>
+      <c r="AH77" s="5" t="inlineStr"/>
       <c r="AI77" s="5" t="inlineStr"/>
-      <c r="AJ77" s="5" t="n">
-        <v>-0.6500000000000004</v>
-      </c>
+      <c r="AJ77" s="5" t="inlineStr"/>
       <c r="AK77" s="5" t="inlineStr"/>
-      <c r="AL77" s="5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AM77" s="5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AN77" s="5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AO77" s="5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AP77" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ77" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AR77" s="5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AS77" s="5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="AL77" s="5" t="inlineStr"/>
+      <c r="AM77" s="5" t="inlineStr"/>
+      <c r="AN77" s="5" t="inlineStr"/>
+      <c r="AO77" s="5" t="inlineStr"/>
+      <c r="AP77" s="5" t="inlineStr"/>
+      <c r="AQ77" s="5" t="inlineStr"/>
+      <c r="AR77" s="5" t="inlineStr"/>
+      <c r="AS77" s="5" t="inlineStr"/>
       <c r="AT77" s="5" t="inlineStr"/>
       <c r="AU77" s="5" t="inlineStr"/>
-      <c r="AV77" s="5" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
-      </c>
+      <c r="AV77" s="5" t="inlineStr"/>
       <c r="AW77" s="5" t="inlineStr"/>
       <c r="AX77" s="5" t="inlineStr"/>
       <c r="AY77" s="5" t="inlineStr"/>
@@ -56704,12 +56704,12 @@
       <c r="BD77" s="5" t="inlineStr"/>
       <c r="BE77" s="5" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1.009</t>
         </is>
       </c>
       <c r="BF77" s="5" t="inlineStr">
         <is>
-          <t>ORL +4.5 pt margin vs NO, pra: 1.03x game script (fav; spread_risk 1.02, total_risk 1.02)</t>
+          <t>LAL +1.5 pt margin vs DAL, fantasy: 1.01x game script (pick; spread_risk 1.00, total_risk 1.02)</t>
         </is>
       </c>
     </row>

--- a/NBA/step8_nba1h_direction_clean.xlsx
+++ b/NBA/step8_nba1h_direction_clean.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier D" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ALL'!$A$1:$BG$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tier B'!$A$1:$BG$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tier C'!$A$1:$BG$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tier D'!$A$1:$BG$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ALL'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tier B'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tier C'!$A$1:$BJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tier D'!$A$1:$BJ$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG90"/>
+  <dimension ref="A1:BJ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -566,6 +566,9 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -836,30 +839,45 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>H2H Over% (L5)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>L5 vs Opp Hit%</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Days Rest</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Game Total</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Playoff Game</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Game Script Mult</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Game Script Note</t>
         </is>
@@ -1049,12 +1067,19 @@
       <c r="BC2" s="3" t="inlineStr"/>
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr"/>
-      <c r="BF2" s="3" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG2" s="3" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -1260,12 +1285,19 @@
       <c r="BC3" s="5" t="inlineStr"/>
       <c r="BD3" s="5" t="inlineStr"/>
       <c r="BE3" s="5" t="inlineStr"/>
-      <c r="BF3" s="5" t="inlineStr">
+      <c r="BF3" s="5" t="inlineStr"/>
+      <c r="BG3" s="5" t="inlineStr"/>
+      <c r="BH3" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI3" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG3" s="5" t="inlineStr">
+      <c r="BJ3" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -1475,12 +1507,19 @@
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr"/>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI4" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BJ4" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -1666,12 +1705,19 @@
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr"/>
-      <c r="BF5" s="5" t="inlineStr">
+      <c r="BF5" s="5" t="inlineStr"/>
+      <c r="BG5" s="5" t="inlineStr"/>
+      <c r="BH5" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI5" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG5" s="5" t="inlineStr">
+      <c r="BJ5" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -1881,12 +1927,19 @@
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
       <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI6" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BJ6" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -2080,12 +2133,19 @@
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
       <c r="BE7" s="5" t="inlineStr"/>
-      <c r="BF7" s="5" t="inlineStr">
+      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BG7" s="5" t="inlineStr"/>
+      <c r="BH7" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI7" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG7" s="5" t="inlineStr">
+      <c r="BJ7" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -2279,12 +2339,19 @@
       <c r="BC8" s="3" t="inlineStr"/>
       <c r="BD8" s="3" t="inlineStr"/>
       <c r="BE8" s="3" t="inlineStr"/>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI8" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BJ8" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -2490,12 +2557,19 @@
       <c r="BC9" s="5" t="inlineStr"/>
       <c r="BD9" s="5" t="inlineStr"/>
       <c r="BE9" s="5" t="inlineStr"/>
-      <c r="BF9" s="5" t="inlineStr">
+      <c r="BF9" s="5" t="inlineStr"/>
+      <c r="BG9" s="5" t="inlineStr"/>
+      <c r="BH9" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI9" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG9" s="5" t="inlineStr">
+      <c r="BJ9" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -2705,12 +2779,19 @@
       <c r="BC10" s="3" t="inlineStr"/>
       <c r="BD10" s="3" t="inlineStr"/>
       <c r="BE10" s="3" t="inlineStr"/>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI10" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BJ10" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -2920,12 +3001,19 @@
       <c r="BC11" s="5" t="inlineStr"/>
       <c r="BD11" s="5" t="inlineStr"/>
       <c r="BE11" s="5" t="inlineStr"/>
-      <c r="BF11" s="5" t="inlineStr">
+      <c r="BF11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="inlineStr"/>
+      <c r="BH11" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI11" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG11" s="5" t="inlineStr">
+      <c r="BJ11" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -3123,12 +3211,19 @@
       <c r="BC12" s="3" t="inlineStr"/>
       <c r="BD12" s="3" t="inlineStr"/>
       <c r="BE12" s="3" t="inlineStr"/>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="3" t="inlineStr"/>
+      <c r="BG12" s="3" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI12" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BJ12" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -3338,12 +3433,19 @@
       <c r="BC13" s="5" t="inlineStr"/>
       <c r="BD13" s="5" t="inlineStr"/>
       <c r="BE13" s="5" t="inlineStr"/>
-      <c r="BF13" s="5" t="inlineStr">
+      <c r="BF13" s="5" t="inlineStr"/>
+      <c r="BG13" s="5" t="inlineStr"/>
+      <c r="BH13" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI13" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG13" s="5" t="inlineStr">
+      <c r="BJ13" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -3521,12 +3623,19 @@
       <c r="BC14" s="3" t="inlineStr"/>
       <c r="BD14" s="3" t="inlineStr"/>
       <c r="BE14" s="3" t="inlineStr"/>
-      <c r="BF14" s="3" t="inlineStr">
+      <c r="BF14" s="3" t="inlineStr"/>
+      <c r="BG14" s="3" t="inlineStr"/>
+      <c r="BH14" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI14" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BJ14" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -3728,12 +3837,19 @@
       <c r="BC15" s="5" t="inlineStr"/>
       <c r="BD15" s="5" t="inlineStr"/>
       <c r="BE15" s="5" t="inlineStr"/>
-      <c r="BF15" s="5" t="inlineStr">
+      <c r="BF15" s="5" t="inlineStr"/>
+      <c r="BG15" s="5" t="inlineStr"/>
+      <c r="BH15" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI15" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG15" s="5" t="inlineStr">
+      <c r="BJ15" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -3939,12 +4055,19 @@
       <c r="BC16" s="3" t="inlineStr"/>
       <c r="BD16" s="3" t="inlineStr"/>
       <c r="BE16" s="3" t="inlineStr"/>
-      <c r="BF16" s="3" t="inlineStr">
+      <c r="BF16" s="3" t="inlineStr"/>
+      <c r="BG16" s="3" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI16" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG16" s="3" t="inlineStr">
+      <c r="BJ16" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -4154,12 +4277,19 @@
       <c r="BC17" s="5" t="inlineStr"/>
       <c r="BD17" s="5" t="inlineStr"/>
       <c r="BE17" s="5" t="inlineStr"/>
-      <c r="BF17" s="5" t="inlineStr">
+      <c r="BF17" s="5" t="inlineStr"/>
+      <c r="BG17" s="5" t="inlineStr"/>
+      <c r="BH17" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI17" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG17" s="5" t="inlineStr">
+      <c r="BJ17" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -4365,12 +4495,19 @@
       <c r="BC18" s="3" t="inlineStr"/>
       <c r="BD18" s="3" t="inlineStr"/>
       <c r="BE18" s="3" t="inlineStr"/>
-      <c r="BF18" s="3" t="inlineStr">
+      <c r="BF18" s="3" t="inlineStr"/>
+      <c r="BG18" s="3" t="inlineStr"/>
+      <c r="BH18" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI18" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG18" s="3" t="inlineStr">
+      <c r="BJ18" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -4560,12 +4697,19 @@
       <c r="BC19" s="5" t="inlineStr"/>
       <c r="BD19" s="5" t="inlineStr"/>
       <c r="BE19" s="5" t="inlineStr"/>
-      <c r="BF19" s="5" t="inlineStr">
+      <c r="BF19" s="5" t="inlineStr"/>
+      <c r="BG19" s="5" t="inlineStr"/>
+      <c r="BH19" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI19" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG19" s="5" t="inlineStr">
+      <c r="BJ19" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -4775,12 +4919,19 @@
       <c r="BC20" s="3" t="inlineStr"/>
       <c r="BD20" s="3" t="inlineStr"/>
       <c r="BE20" s="3" t="inlineStr"/>
-      <c r="BF20" s="3" t="inlineStr">
+      <c r="BF20" s="3" t="inlineStr"/>
+      <c r="BG20" s="3" t="inlineStr"/>
+      <c r="BH20" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI20" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG20" s="3" t="inlineStr">
+      <c r="BJ20" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -4990,12 +5141,19 @@
       <c r="BC21" s="5" t="inlineStr"/>
       <c r="BD21" s="5" t="inlineStr"/>
       <c r="BE21" s="5" t="inlineStr"/>
-      <c r="BF21" s="5" t="inlineStr">
+      <c r="BF21" s="5" t="inlineStr"/>
+      <c r="BG21" s="5" t="inlineStr"/>
+      <c r="BH21" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI21" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG21" s="5" t="inlineStr">
+      <c r="BJ21" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -5201,12 +5359,19 @@
       <c r="BC22" s="3" t="inlineStr"/>
       <c r="BD22" s="3" t="inlineStr"/>
       <c r="BE22" s="3" t="inlineStr"/>
-      <c r="BF22" s="3" t="inlineStr">
+      <c r="BF22" s="3" t="inlineStr"/>
+      <c r="BG22" s="3" t="inlineStr"/>
+      <c r="BH22" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI22" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG22" s="3" t="inlineStr">
+      <c r="BJ22" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -5408,12 +5573,19 @@
       <c r="BC23" s="5" t="inlineStr"/>
       <c r="BD23" s="5" t="inlineStr"/>
       <c r="BE23" s="5" t="inlineStr"/>
-      <c r="BF23" s="5" t="inlineStr">
+      <c r="BF23" s="5" t="inlineStr"/>
+      <c r="BG23" s="5" t="inlineStr"/>
+      <c r="BH23" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI23" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG23" s="5" t="inlineStr">
+      <c r="BJ23" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -5619,12 +5791,19 @@
       <c r="BC24" s="3" t="inlineStr"/>
       <c r="BD24" s="3" t="inlineStr"/>
       <c r="BE24" s="3" t="inlineStr"/>
-      <c r="BF24" s="3" t="inlineStr">
+      <c r="BF24" s="3" t="inlineStr"/>
+      <c r="BG24" s="3" t="inlineStr"/>
+      <c r="BH24" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI24" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG24" s="3" t="inlineStr">
+      <c r="BJ24" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -5826,12 +6005,19 @@
       <c r="BC25" s="5" t="inlineStr"/>
       <c r="BD25" s="5" t="inlineStr"/>
       <c r="BE25" s="5" t="inlineStr"/>
-      <c r="BF25" s="5" t="inlineStr">
+      <c r="BF25" s="5" t="inlineStr"/>
+      <c r="BG25" s="5" t="inlineStr"/>
+      <c r="BH25" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI25" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG25" s="5" t="inlineStr">
+      <c r="BJ25" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -6021,12 +6207,19 @@
       <c r="BC26" s="3" t="inlineStr"/>
       <c r="BD26" s="3" t="inlineStr"/>
       <c r="BE26" s="3" t="inlineStr"/>
-      <c r="BF26" s="3" t="inlineStr">
+      <c r="BF26" s="3" t="inlineStr"/>
+      <c r="BG26" s="3" t="inlineStr"/>
+      <c r="BH26" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI26" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG26" s="3" t="inlineStr">
+      <c r="BJ26" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -6236,12 +6429,19 @@
       <c r="BC27" s="5" t="inlineStr"/>
       <c r="BD27" s="5" t="inlineStr"/>
       <c r="BE27" s="5" t="inlineStr"/>
-      <c r="BF27" s="5" t="inlineStr">
+      <c r="BF27" s="5" t="inlineStr"/>
+      <c r="BG27" s="5" t="inlineStr"/>
+      <c r="BH27" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI27" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG27" s="5" t="inlineStr">
+      <c r="BJ27" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -6451,12 +6651,19 @@
       <c r="BC28" s="3" t="inlineStr"/>
       <c r="BD28" s="3" t="inlineStr"/>
       <c r="BE28" s="3" t="inlineStr"/>
-      <c r="BF28" s="3" t="inlineStr">
+      <c r="BF28" s="3" t="inlineStr"/>
+      <c r="BG28" s="3" t="inlineStr"/>
+      <c r="BH28" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI28" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG28" s="3" t="inlineStr">
+      <c r="BJ28" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -6662,12 +6869,19 @@
       <c r="BC29" s="5" t="inlineStr"/>
       <c r="BD29" s="5" t="inlineStr"/>
       <c r="BE29" s="5" t="inlineStr"/>
-      <c r="BF29" s="5" t="inlineStr">
+      <c r="BF29" s="5" t="inlineStr"/>
+      <c r="BG29" s="5" t="inlineStr"/>
+      <c r="BH29" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI29" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG29" s="5" t="inlineStr">
+      <c r="BJ29" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -6873,12 +7087,19 @@
       <c r="BC30" s="3" t="inlineStr"/>
       <c r="BD30" s="3" t="inlineStr"/>
       <c r="BE30" s="3" t="inlineStr"/>
-      <c r="BF30" s="3" t="inlineStr">
+      <c r="BF30" s="3" t="inlineStr"/>
+      <c r="BG30" s="3" t="inlineStr"/>
+      <c r="BH30" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI30" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG30" s="3" t="inlineStr">
+      <c r="BJ30" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -7088,12 +7309,19 @@
       <c r="BC31" s="5" t="inlineStr"/>
       <c r="BD31" s="5" t="inlineStr"/>
       <c r="BE31" s="5" t="inlineStr"/>
-      <c r="BF31" s="5" t="inlineStr">
+      <c r="BF31" s="5" t="inlineStr"/>
+      <c r="BG31" s="5" t="inlineStr"/>
+      <c r="BH31" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI31" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG31" s="5" t="inlineStr">
+      <c r="BJ31" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -7299,12 +7527,19 @@
       <c r="BC32" s="3" t="inlineStr"/>
       <c r="BD32" s="3" t="inlineStr"/>
       <c r="BE32" s="3" t="inlineStr"/>
-      <c r="BF32" s="3" t="inlineStr">
+      <c r="BF32" s="3" t="inlineStr"/>
+      <c r="BG32" s="3" t="inlineStr"/>
+      <c r="BH32" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI32" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG32" s="3" t="inlineStr">
+      <c r="BJ32" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -7506,12 +7741,19 @@
       <c r="BC33" s="5" t="inlineStr"/>
       <c r="BD33" s="5" t="inlineStr"/>
       <c r="BE33" s="5" t="inlineStr"/>
-      <c r="BF33" s="5" t="inlineStr">
+      <c r="BF33" s="5" t="inlineStr"/>
+      <c r="BG33" s="5" t="inlineStr"/>
+      <c r="BH33" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI33" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG33" s="5" t="inlineStr">
+      <c r="BJ33" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -7643,12 +7885,19 @@
       <c r="BC34" s="3" t="inlineStr"/>
       <c r="BD34" s="3" t="inlineStr"/>
       <c r="BE34" s="3" t="inlineStr"/>
-      <c r="BF34" s="3" t="inlineStr">
+      <c r="BF34" s="3" t="inlineStr"/>
+      <c r="BG34" s="3" t="inlineStr"/>
+      <c r="BH34" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI34" s="3" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG34" s="3" t="inlineStr">
+      <c r="BJ34" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -7780,12 +8029,19 @@
       <c r="BC35" s="5" t="inlineStr"/>
       <c r="BD35" s="5" t="inlineStr"/>
       <c r="BE35" s="5" t="inlineStr"/>
-      <c r="BF35" s="5" t="inlineStr">
+      <c r="BF35" s="5" t="inlineStr"/>
+      <c r="BG35" s="5" t="inlineStr"/>
+      <c r="BH35" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI35" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG35" s="5" t="inlineStr">
+      <c r="BJ35" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -7917,12 +8173,19 @@
       <c r="BC36" s="3" t="inlineStr"/>
       <c r="BD36" s="3" t="inlineStr"/>
       <c r="BE36" s="3" t="inlineStr"/>
-      <c r="BF36" s="3" t="inlineStr">
+      <c r="BF36" s="3" t="inlineStr"/>
+      <c r="BG36" s="3" t="inlineStr"/>
+      <c r="BH36" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI36" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG36" s="3" t="inlineStr">
+      <c r="BJ36" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -8054,12 +8317,19 @@
       <c r="BC37" s="5" t="inlineStr"/>
       <c r="BD37" s="5" t="inlineStr"/>
       <c r="BE37" s="5" t="inlineStr"/>
-      <c r="BF37" s="5" t="inlineStr">
+      <c r="BF37" s="5" t="inlineStr"/>
+      <c r="BG37" s="5" t="inlineStr"/>
+      <c r="BH37" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI37" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG37" s="5" t="inlineStr">
+      <c r="BJ37" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -8191,12 +8461,19 @@
       <c r="BC38" s="3" t="inlineStr"/>
       <c r="BD38" s="3" t="inlineStr"/>
       <c r="BE38" s="3" t="inlineStr"/>
-      <c r="BF38" s="3" t="inlineStr">
+      <c r="BF38" s="3" t="inlineStr"/>
+      <c r="BG38" s="3" t="inlineStr"/>
+      <c r="BH38" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI38" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG38" s="3" t="inlineStr">
+      <c r="BJ38" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -8328,12 +8605,19 @@
       <c r="BC39" s="5" t="inlineStr"/>
       <c r="BD39" s="5" t="inlineStr"/>
       <c r="BE39" s="5" t="inlineStr"/>
-      <c r="BF39" s="5" t="inlineStr">
+      <c r="BF39" s="5" t="inlineStr"/>
+      <c r="BG39" s="5" t="inlineStr"/>
+      <c r="BH39" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI39" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG39" s="5" t="inlineStr">
+      <c r="BJ39" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -8465,12 +8749,19 @@
       <c r="BC40" s="3" t="inlineStr"/>
       <c r="BD40" s="3" t="inlineStr"/>
       <c r="BE40" s="3" t="inlineStr"/>
-      <c r="BF40" s="3" t="inlineStr">
+      <c r="BF40" s="3" t="inlineStr"/>
+      <c r="BG40" s="3" t="inlineStr"/>
+      <c r="BH40" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI40" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG40" s="3" t="inlineStr">
+      <c r="BJ40" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -8602,12 +8893,19 @@
       <c r="BC41" s="5" t="inlineStr"/>
       <c r="BD41" s="5" t="inlineStr"/>
       <c r="BE41" s="5" t="inlineStr"/>
-      <c r="BF41" s="5" t="inlineStr">
+      <c r="BF41" s="5" t="inlineStr"/>
+      <c r="BG41" s="5" t="inlineStr"/>
+      <c r="BH41" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI41" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG41" s="5" t="inlineStr">
+      <c r="BJ41" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -8739,12 +9037,19 @@
       <c r="BC42" s="3" t="inlineStr"/>
       <c r="BD42" s="3" t="inlineStr"/>
       <c r="BE42" s="3" t="inlineStr"/>
-      <c r="BF42" s="3" t="inlineStr">
+      <c r="BF42" s="3" t="inlineStr"/>
+      <c r="BG42" s="3" t="inlineStr"/>
+      <c r="BH42" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI42" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG42" s="3" t="inlineStr">
+      <c r="BJ42" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -8876,12 +9181,19 @@
       <c r="BC43" s="5" t="inlineStr"/>
       <c r="BD43" s="5" t="inlineStr"/>
       <c r="BE43" s="5" t="inlineStr"/>
-      <c r="BF43" s="5" t="inlineStr">
+      <c r="BF43" s="5" t="inlineStr"/>
+      <c r="BG43" s="5" t="inlineStr"/>
+      <c r="BH43" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI43" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG43" s="5" t="inlineStr">
+      <c r="BJ43" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -9013,12 +9325,19 @@
       <c r="BC44" s="3" t="inlineStr"/>
       <c r="BD44" s="3" t="inlineStr"/>
       <c r="BE44" s="3" t="inlineStr"/>
-      <c r="BF44" s="3" t="inlineStr">
+      <c r="BF44" s="3" t="inlineStr"/>
+      <c r="BG44" s="3" t="inlineStr"/>
+      <c r="BH44" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI44" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG44" s="3" t="inlineStr">
+      <c r="BJ44" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -9210,12 +9529,19 @@
       <c r="BC45" s="5" t="inlineStr"/>
       <c r="BD45" s="5" t="inlineStr"/>
       <c r="BE45" s="5" t="inlineStr"/>
-      <c r="BF45" s="5" t="inlineStr">
+      <c r="BF45" s="5" t="inlineStr"/>
+      <c r="BG45" s="5" t="inlineStr"/>
+      <c r="BH45" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI45" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG45" s="5" t="inlineStr">
+      <c r="BJ45" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -9347,12 +9673,19 @@
       <c r="BC46" s="3" t="inlineStr"/>
       <c r="BD46" s="3" t="inlineStr"/>
       <c r="BE46" s="3" t="inlineStr"/>
-      <c r="BF46" s="3" t="inlineStr">
+      <c r="BF46" s="3" t="inlineStr"/>
+      <c r="BG46" s="3" t="inlineStr"/>
+      <c r="BH46" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI46" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG46" s="3" t="inlineStr">
+      <c r="BJ46" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -9560,12 +9893,19 @@
       <c r="BC47" s="5" t="inlineStr"/>
       <c r="BD47" s="5" t="inlineStr"/>
       <c r="BE47" s="5" t="inlineStr"/>
-      <c r="BF47" s="5" t="inlineStr">
+      <c r="BF47" s="5" t="inlineStr"/>
+      <c r="BG47" s="5" t="inlineStr"/>
+      <c r="BH47" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI47" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG47" s="5" t="inlineStr">
+      <c r="BJ47" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -9697,12 +10037,19 @@
       <c r="BC48" s="3" t="inlineStr"/>
       <c r="BD48" s="3" t="inlineStr"/>
       <c r="BE48" s="3" t="inlineStr"/>
-      <c r="BF48" s="3" t="inlineStr">
+      <c r="BF48" s="3" t="inlineStr"/>
+      <c r="BG48" s="3" t="inlineStr"/>
+      <c r="BH48" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI48" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG48" s="3" t="inlineStr">
+      <c r="BJ48" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -9834,12 +10181,19 @@
       <c r="BC49" s="5" t="inlineStr"/>
       <c r="BD49" s="5" t="inlineStr"/>
       <c r="BE49" s="5" t="inlineStr"/>
-      <c r="BF49" s="5" t="inlineStr">
+      <c r="BF49" s="5" t="inlineStr"/>
+      <c r="BG49" s="5" t="inlineStr"/>
+      <c r="BH49" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI49" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG49" s="5" t="inlineStr">
+      <c r="BJ49" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -10035,12 +10389,19 @@
       <c r="BC50" s="3" t="inlineStr"/>
       <c r="BD50" s="3" t="inlineStr"/>
       <c r="BE50" s="3" t="inlineStr"/>
-      <c r="BF50" s="3" t="inlineStr">
+      <c r="BF50" s="3" t="inlineStr"/>
+      <c r="BG50" s="3" t="inlineStr"/>
+      <c r="BH50" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI50" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG50" s="3" t="inlineStr">
+      <c r="BJ50" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -10172,12 +10533,19 @@
       <c r="BC51" s="5" t="inlineStr"/>
       <c r="BD51" s="5" t="inlineStr"/>
       <c r="BE51" s="5" t="inlineStr"/>
-      <c r="BF51" s="5" t="inlineStr">
+      <c r="BF51" s="5" t="inlineStr"/>
+      <c r="BG51" s="5" t="inlineStr"/>
+      <c r="BH51" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI51" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG51" s="5" t="inlineStr">
+      <c r="BJ51" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -10309,12 +10677,19 @@
       <c r="BC52" s="3" t="inlineStr"/>
       <c r="BD52" s="3" t="inlineStr"/>
       <c r="BE52" s="3" t="inlineStr"/>
-      <c r="BF52" s="3" t="inlineStr">
+      <c r="BF52" s="3" t="inlineStr"/>
+      <c r="BG52" s="3" t="inlineStr"/>
+      <c r="BH52" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI52" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG52" s="3" t="inlineStr">
+      <c r="BJ52" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -10446,12 +10821,19 @@
       <c r="BC53" s="5" t="inlineStr"/>
       <c r="BD53" s="5" t="inlineStr"/>
       <c r="BE53" s="5" t="inlineStr"/>
-      <c r="BF53" s="5" t="inlineStr">
+      <c r="BF53" s="5" t="inlineStr"/>
+      <c r="BG53" s="5" t="inlineStr"/>
+      <c r="BH53" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI53" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG53" s="5" t="inlineStr">
+      <c r="BJ53" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -10583,12 +10965,19 @@
       <c r="BC54" s="3" t="inlineStr"/>
       <c r="BD54" s="3" t="inlineStr"/>
       <c r="BE54" s="3" t="inlineStr"/>
-      <c r="BF54" s="3" t="inlineStr">
+      <c r="BF54" s="3" t="inlineStr"/>
+      <c r="BG54" s="3" t="inlineStr"/>
+      <c r="BH54" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI54" s="3" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG54" s="3" t="inlineStr">
+      <c r="BJ54" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -10720,12 +11109,19 @@
       <c r="BC55" s="5" t="inlineStr"/>
       <c r="BD55" s="5" t="inlineStr"/>
       <c r="BE55" s="5" t="inlineStr"/>
-      <c r="BF55" s="5" t="inlineStr">
+      <c r="BF55" s="5" t="inlineStr"/>
+      <c r="BG55" s="5" t="inlineStr"/>
+      <c r="BH55" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI55" s="5" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG55" s="5" t="inlineStr">
+      <c r="BJ55" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -10857,12 +11253,19 @@
       <c r="BC56" s="3" t="inlineStr"/>
       <c r="BD56" s="3" t="inlineStr"/>
       <c r="BE56" s="3" t="inlineStr"/>
-      <c r="BF56" s="3" t="inlineStr">
+      <c r="BF56" s="3" t="inlineStr"/>
+      <c r="BG56" s="3" t="inlineStr"/>
+      <c r="BH56" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI56" s="3" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG56" s="3" t="inlineStr">
+      <c r="BJ56" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -10994,12 +11397,19 @@
       <c r="BC57" s="5" t="inlineStr"/>
       <c r="BD57" s="5" t="inlineStr"/>
       <c r="BE57" s="5" t="inlineStr"/>
-      <c r="BF57" s="5" t="inlineStr">
+      <c r="BF57" s="5" t="inlineStr"/>
+      <c r="BG57" s="5" t="inlineStr"/>
+      <c r="BH57" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI57" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG57" s="5" t="inlineStr">
+      <c r="BJ57" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -11131,12 +11541,19 @@
       <c r="BC58" s="3" t="inlineStr"/>
       <c r="BD58" s="3" t="inlineStr"/>
       <c r="BE58" s="3" t="inlineStr"/>
-      <c r="BF58" s="3" t="inlineStr">
+      <c r="BF58" s="3" t="inlineStr"/>
+      <c r="BG58" s="3" t="inlineStr"/>
+      <c r="BH58" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI58" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG58" s="3" t="inlineStr">
+      <c r="BJ58" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -11268,12 +11685,19 @@
       <c r="BC59" s="5" t="inlineStr"/>
       <c r="BD59" s="5" t="inlineStr"/>
       <c r="BE59" s="5" t="inlineStr"/>
-      <c r="BF59" s="5" t="inlineStr">
+      <c r="BF59" s="5" t="inlineStr"/>
+      <c r="BG59" s="5" t="inlineStr"/>
+      <c r="BH59" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI59" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG59" s="5" t="inlineStr">
+      <c r="BJ59" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -11405,12 +11829,19 @@
       <c r="BC60" s="3" t="inlineStr"/>
       <c r="BD60" s="3" t="inlineStr"/>
       <c r="BE60" s="3" t="inlineStr"/>
-      <c r="BF60" s="3" t="inlineStr">
+      <c r="BF60" s="3" t="inlineStr"/>
+      <c r="BG60" s="3" t="inlineStr"/>
+      <c r="BH60" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI60" s="3" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG60" s="3" t="inlineStr">
+      <c r="BJ60" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -11542,12 +11973,19 @@
       <c r="BC61" s="5" t="inlineStr"/>
       <c r="BD61" s="5" t="inlineStr"/>
       <c r="BE61" s="5" t="inlineStr"/>
-      <c r="BF61" s="5" t="inlineStr">
+      <c r="BF61" s="5" t="inlineStr"/>
+      <c r="BG61" s="5" t="inlineStr"/>
+      <c r="BH61" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI61" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG61" s="5" t="inlineStr">
+      <c r="BJ61" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -11679,12 +12117,19 @@
       <c r="BC62" s="3" t="inlineStr"/>
       <c r="BD62" s="3" t="inlineStr"/>
       <c r="BE62" s="3" t="inlineStr"/>
-      <c r="BF62" s="3" t="inlineStr">
+      <c r="BF62" s="3" t="inlineStr"/>
+      <c r="BG62" s="3" t="inlineStr"/>
+      <c r="BH62" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI62" s="3" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG62" s="3" t="inlineStr">
+      <c r="BJ62" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -11816,12 +12261,19 @@
       <c r="BC63" s="5" t="inlineStr"/>
       <c r="BD63" s="5" t="inlineStr"/>
       <c r="BE63" s="5" t="inlineStr"/>
-      <c r="BF63" s="5" t="inlineStr">
+      <c r="BF63" s="5" t="inlineStr"/>
+      <c r="BG63" s="5" t="inlineStr"/>
+      <c r="BH63" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI63" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG63" s="5" t="inlineStr">
+      <c r="BJ63" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -11953,12 +12405,19 @@
       <c r="BC64" s="3" t="inlineStr"/>
       <c r="BD64" s="3" t="inlineStr"/>
       <c r="BE64" s="3" t="inlineStr"/>
-      <c r="BF64" s="3" t="inlineStr">
+      <c r="BF64" s="3" t="inlineStr"/>
+      <c r="BG64" s="3" t="inlineStr"/>
+      <c r="BH64" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI64" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG64" s="3" t="inlineStr">
+      <c r="BJ64" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -12090,12 +12549,19 @@
       <c r="BC65" s="5" t="inlineStr"/>
       <c r="BD65" s="5" t="inlineStr"/>
       <c r="BE65" s="5" t="inlineStr"/>
-      <c r="BF65" s="5" t="inlineStr">
+      <c r="BF65" s="5" t="inlineStr"/>
+      <c r="BG65" s="5" t="inlineStr"/>
+      <c r="BH65" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI65" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG65" s="5" t="inlineStr">
+      <c r="BJ65" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -12227,12 +12693,19 @@
       <c r="BC66" s="3" t="inlineStr"/>
       <c r="BD66" s="3" t="inlineStr"/>
       <c r="BE66" s="3" t="inlineStr"/>
-      <c r="BF66" s="3" t="inlineStr">
+      <c r="BF66" s="3" t="inlineStr"/>
+      <c r="BG66" s="3" t="inlineStr"/>
+      <c r="BH66" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI66" s="3" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG66" s="3" t="inlineStr">
+      <c r="BJ66" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -12364,12 +12837,19 @@
       <c r="BC67" s="5" t="inlineStr"/>
       <c r="BD67" s="5" t="inlineStr"/>
       <c r="BE67" s="5" t="inlineStr"/>
-      <c r="BF67" s="5" t="inlineStr">
+      <c r="BF67" s="5" t="inlineStr"/>
+      <c r="BG67" s="5" t="inlineStr"/>
+      <c r="BH67" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI67" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG67" s="5" t="inlineStr">
+      <c r="BJ67" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -12501,12 +12981,19 @@
       <c r="BC68" s="3" t="inlineStr"/>
       <c r="BD68" s="3" t="inlineStr"/>
       <c r="BE68" s="3" t="inlineStr"/>
-      <c r="BF68" s="3" t="inlineStr">
+      <c r="BF68" s="3" t="inlineStr"/>
+      <c r="BG68" s="3" t="inlineStr"/>
+      <c r="BH68" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI68" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG68" s="3" t="inlineStr">
+      <c r="BJ68" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -12638,12 +13125,19 @@
       <c r="BC69" s="5" t="inlineStr"/>
       <c r="BD69" s="5" t="inlineStr"/>
       <c r="BE69" s="5" t="inlineStr"/>
-      <c r="BF69" s="5" t="inlineStr">
+      <c r="BF69" s="5" t="inlineStr"/>
+      <c r="BG69" s="5" t="inlineStr"/>
+      <c r="BH69" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI69" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG69" s="5" t="inlineStr">
+      <c r="BJ69" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -12775,12 +13269,19 @@
       <c r="BC70" s="3" t="inlineStr"/>
       <c r="BD70" s="3" t="inlineStr"/>
       <c r="BE70" s="3" t="inlineStr"/>
-      <c r="BF70" s="3" t="inlineStr">
+      <c r="BF70" s="3" t="inlineStr"/>
+      <c r="BG70" s="3" t="inlineStr"/>
+      <c r="BH70" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI70" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG70" s="3" t="inlineStr">
+      <c r="BJ70" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -12912,12 +13413,19 @@
       <c r="BC71" s="5" t="inlineStr"/>
       <c r="BD71" s="5" t="inlineStr"/>
       <c r="BE71" s="5" t="inlineStr"/>
-      <c r="BF71" s="5" t="inlineStr">
+      <c r="BF71" s="5" t="inlineStr"/>
+      <c r="BG71" s="5" t="inlineStr"/>
+      <c r="BH71" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI71" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG71" s="5" t="inlineStr">
+      <c r="BJ71" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -13049,12 +13557,19 @@
       <c r="BC72" s="3" t="inlineStr"/>
       <c r="BD72" s="3" t="inlineStr"/>
       <c r="BE72" s="3" t="inlineStr"/>
-      <c r="BF72" s="3" t="inlineStr">
+      <c r="BF72" s="3" t="inlineStr"/>
+      <c r="BG72" s="3" t="inlineStr"/>
+      <c r="BH72" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI72" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG72" s="3" t="inlineStr">
+      <c r="BJ72" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -13186,12 +13701,19 @@
       <c r="BC73" s="5" t="inlineStr"/>
       <c r="BD73" s="5" t="inlineStr"/>
       <c r="BE73" s="5" t="inlineStr"/>
-      <c r="BF73" s="5" t="inlineStr">
+      <c r="BF73" s="5" t="inlineStr"/>
+      <c r="BG73" s="5" t="inlineStr"/>
+      <c r="BH73" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI73" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG73" s="5" t="inlineStr">
+      <c r="BJ73" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -13323,12 +13845,19 @@
       <c r="BC74" s="3" t="inlineStr"/>
       <c r="BD74" s="3" t="inlineStr"/>
       <c r="BE74" s="3" t="inlineStr"/>
-      <c r="BF74" s="3" t="inlineStr">
+      <c r="BF74" s="3" t="inlineStr"/>
+      <c r="BG74" s="3" t="inlineStr"/>
+      <c r="BH74" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI74" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG74" s="3" t="inlineStr">
+      <c r="BJ74" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -13460,12 +13989,19 @@
       <c r="BC75" s="5" t="inlineStr"/>
       <c r="BD75" s="5" t="inlineStr"/>
       <c r="BE75" s="5" t="inlineStr"/>
-      <c r="BF75" s="5" t="inlineStr">
+      <c r="BF75" s="5" t="inlineStr"/>
+      <c r="BG75" s="5" t="inlineStr"/>
+      <c r="BH75" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI75" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG75" s="5" t="inlineStr">
+      <c r="BJ75" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -13597,12 +14133,19 @@
       <c r="BC76" s="3" t="inlineStr"/>
       <c r="BD76" s="3" t="inlineStr"/>
       <c r="BE76" s="3" t="inlineStr"/>
-      <c r="BF76" s="3" t="inlineStr">
+      <c r="BF76" s="3" t="inlineStr"/>
+      <c r="BG76" s="3" t="inlineStr"/>
+      <c r="BH76" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI76" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG76" s="3" t="inlineStr">
+      <c r="BJ76" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -13734,12 +14277,19 @@
       <c r="BC77" s="5" t="inlineStr"/>
       <c r="BD77" s="5" t="inlineStr"/>
       <c r="BE77" s="5" t="inlineStr"/>
-      <c r="BF77" s="5" t="inlineStr">
+      <c r="BF77" s="5" t="inlineStr"/>
+      <c r="BG77" s="5" t="inlineStr"/>
+      <c r="BH77" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI77" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG77" s="5" t="inlineStr">
+      <c r="BJ77" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -13871,12 +14421,19 @@
       <c r="BC78" s="3" t="inlineStr"/>
       <c r="BD78" s="3" t="inlineStr"/>
       <c r="BE78" s="3" t="inlineStr"/>
-      <c r="BF78" s="3" t="inlineStr">
+      <c r="BF78" s="3" t="inlineStr"/>
+      <c r="BG78" s="3" t="inlineStr"/>
+      <c r="BH78" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI78" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG78" s="3" t="inlineStr">
+      <c r="BJ78" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -14056,12 +14613,19 @@
       <c r="BC79" s="5" t="inlineStr"/>
       <c r="BD79" s="5" t="inlineStr"/>
       <c r="BE79" s="5" t="inlineStr"/>
-      <c r="BF79" s="5" t="inlineStr">
+      <c r="BF79" s="5" t="inlineStr"/>
+      <c r="BG79" s="5" t="inlineStr"/>
+      <c r="BH79" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI79" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG79" s="5" t="inlineStr">
+      <c r="BJ79" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -14193,12 +14757,19 @@
       <c r="BC80" s="3" t="inlineStr"/>
       <c r="BD80" s="3" t="inlineStr"/>
       <c r="BE80" s="3" t="inlineStr"/>
-      <c r="BF80" s="3" t="inlineStr">
+      <c r="BF80" s="3" t="inlineStr"/>
+      <c r="BG80" s="3" t="inlineStr"/>
+      <c r="BH80" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI80" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG80" s="3" t="inlineStr">
+      <c r="BJ80" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -14330,12 +14901,19 @@
       <c r="BC81" s="5" t="inlineStr"/>
       <c r="BD81" s="5" t="inlineStr"/>
       <c r="BE81" s="5" t="inlineStr"/>
-      <c r="BF81" s="5" t="inlineStr">
+      <c r="BF81" s="5" t="inlineStr"/>
+      <c r="BG81" s="5" t="inlineStr"/>
+      <c r="BH81" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI81" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG81" s="5" t="inlineStr">
+      <c r="BJ81" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -14467,12 +15045,19 @@
       <c r="BC82" s="3" t="inlineStr"/>
       <c r="BD82" s="3" t="inlineStr"/>
       <c r="BE82" s="3" t="inlineStr"/>
-      <c r="BF82" s="3" t="inlineStr">
+      <c r="BF82" s="3" t="inlineStr"/>
+      <c r="BG82" s="3" t="inlineStr"/>
+      <c r="BH82" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI82" s="3" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG82" s="3" t="inlineStr">
+      <c r="BJ82" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -14604,12 +15189,19 @@
       <c r="BC83" s="5" t="inlineStr"/>
       <c r="BD83" s="5" t="inlineStr"/>
       <c r="BE83" s="5" t="inlineStr"/>
-      <c r="BF83" s="5" t="inlineStr">
+      <c r="BF83" s="5" t="inlineStr"/>
+      <c r="BG83" s="5" t="inlineStr"/>
+      <c r="BH83" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI83" s="5" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG83" s="5" t="inlineStr">
+      <c r="BJ83" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -14741,12 +15333,19 @@
       <c r="BC84" s="3" t="inlineStr"/>
       <c r="BD84" s="3" t="inlineStr"/>
       <c r="BE84" s="3" t="inlineStr"/>
-      <c r="BF84" s="3" t="inlineStr">
+      <c r="BF84" s="3" t="inlineStr"/>
+      <c r="BG84" s="3" t="inlineStr"/>
+      <c r="BH84" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI84" s="3" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG84" s="3" t="inlineStr">
+      <c r="BJ84" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -14878,12 +15477,19 @@
       <c r="BC85" s="5" t="inlineStr"/>
       <c r="BD85" s="5" t="inlineStr"/>
       <c r="BE85" s="5" t="inlineStr"/>
-      <c r="BF85" s="5" t="inlineStr">
+      <c r="BF85" s="5" t="inlineStr"/>
+      <c r="BG85" s="5" t="inlineStr"/>
+      <c r="BH85" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI85" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG85" s="5" t="inlineStr">
+      <c r="BJ85" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -15015,12 +15621,19 @@
       <c r="BC86" s="3" t="inlineStr"/>
       <c r="BD86" s="3" t="inlineStr"/>
       <c r="BE86" s="3" t="inlineStr"/>
-      <c r="BF86" s="3" t="inlineStr">
+      <c r="BF86" s="3" t="inlineStr"/>
+      <c r="BG86" s="3" t="inlineStr"/>
+      <c r="BH86" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI86" s="3" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG86" s="3" t="inlineStr">
+      <c r="BJ86" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -15152,12 +15765,19 @@
       <c r="BC87" s="5" t="inlineStr"/>
       <c r="BD87" s="5" t="inlineStr"/>
       <c r="BE87" s="5" t="inlineStr"/>
-      <c r="BF87" s="5" t="inlineStr">
+      <c r="BF87" s="5" t="inlineStr"/>
+      <c r="BG87" s="5" t="inlineStr"/>
+      <c r="BH87" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI87" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG87" s="5" t="inlineStr">
+      <c r="BJ87" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -15289,12 +15909,19 @@
       <c r="BC88" s="3" t="inlineStr"/>
       <c r="BD88" s="3" t="inlineStr"/>
       <c r="BE88" s="3" t="inlineStr"/>
-      <c r="BF88" s="3" t="inlineStr">
+      <c r="BF88" s="3" t="inlineStr"/>
+      <c r="BG88" s="3" t="inlineStr"/>
+      <c r="BH88" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI88" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG88" s="3" t="inlineStr">
+      <c r="BJ88" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -15426,12 +16053,19 @@
       <c r="BC89" s="5" t="inlineStr"/>
       <c r="BD89" s="5" t="inlineStr"/>
       <c r="BE89" s="5" t="inlineStr"/>
-      <c r="BF89" s="5" t="inlineStr">
+      <c r="BF89" s="5" t="inlineStr"/>
+      <c r="BG89" s="5" t="inlineStr"/>
+      <c r="BH89" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI89" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG89" s="5" t="inlineStr">
+      <c r="BJ89" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -15563,19 +16197,26 @@
       <c r="BC90" s="3" t="inlineStr"/>
       <c r="BD90" s="3" t="inlineStr"/>
       <c r="BE90" s="3" t="inlineStr"/>
-      <c r="BF90" s="3" t="inlineStr">
+      <c r="BF90" s="3" t="inlineStr"/>
+      <c r="BG90" s="3" t="inlineStr"/>
+      <c r="BH90" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI90" s="3" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG90" s="3" t="inlineStr">
+      <c r="BJ90" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15586,7 +16227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG4"/>
+  <dimension ref="A1:BJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15648,6 +16289,9 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -15918,30 +16562,45 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>H2H Over% (L5)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>L5 vs Opp Hit%</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Days Rest</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Game Total</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Playoff Game</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Game Script Mult</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Game Script Note</t>
         </is>
@@ -16131,12 +16790,19 @@
       <c r="BC2" s="3" t="inlineStr"/>
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr"/>
-      <c r="BF2" s="3" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG2" s="3" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -16342,12 +17008,19 @@
       <c r="BC3" s="5" t="inlineStr"/>
       <c r="BD3" s="5" t="inlineStr"/>
       <c r="BE3" s="5" t="inlineStr"/>
-      <c r="BF3" s="5" t="inlineStr">
+      <c r="BF3" s="5" t="inlineStr"/>
+      <c r="BG3" s="5" t="inlineStr"/>
+      <c r="BH3" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI3" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG3" s="5" t="inlineStr">
+      <c r="BJ3" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -16557,19 +17230,26 @@
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr"/>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI4" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BJ4" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16580,7 +17260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG11"/>
+  <dimension ref="A1:BJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -16642,6 +17322,9 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -16912,30 +17595,45 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>H2H Over% (L5)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>L5 vs Opp Hit%</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Days Rest</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Game Total</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Playoff Game</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Game Script Mult</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Game Script Note</t>
         </is>
@@ -17121,12 +17819,19 @@
       <c r="BC2" s="3" t="inlineStr"/>
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr"/>
-      <c r="BF2" s="3" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG2" s="3" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -17336,12 +18041,19 @@
       <c r="BC3" s="5" t="inlineStr"/>
       <c r="BD3" s="5" t="inlineStr"/>
       <c r="BE3" s="5" t="inlineStr"/>
-      <c r="BF3" s="5" t="inlineStr">
+      <c r="BF3" s="5" t="inlineStr"/>
+      <c r="BG3" s="5" t="inlineStr"/>
+      <c r="BH3" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI3" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG3" s="5" t="inlineStr">
+      <c r="BJ3" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -17535,12 +18247,19 @@
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr"/>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI4" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BJ4" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -17734,12 +18453,19 @@
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr"/>
-      <c r="BF5" s="5" t="inlineStr">
+      <c r="BF5" s="5" t="inlineStr"/>
+      <c r="BG5" s="5" t="inlineStr"/>
+      <c r="BH5" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI5" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG5" s="5" t="inlineStr">
+      <c r="BJ5" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -17945,12 +18671,19 @@
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
       <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI6" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BJ6" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -18160,12 +18893,19 @@
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
       <c r="BE7" s="5" t="inlineStr"/>
-      <c r="BF7" s="5" t="inlineStr">
+      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BG7" s="5" t="inlineStr"/>
+      <c r="BH7" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI7" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG7" s="5" t="inlineStr">
+      <c r="BJ7" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -18375,12 +19115,19 @@
       <c r="BC8" s="3" t="inlineStr"/>
       <c r="BD8" s="3" t="inlineStr"/>
       <c r="BE8" s="3" t="inlineStr"/>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI8" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BJ8" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -18578,12 +19325,19 @@
       <c r="BC9" s="5" t="inlineStr"/>
       <c r="BD9" s="5" t="inlineStr"/>
       <c r="BE9" s="5" t="inlineStr"/>
-      <c r="BF9" s="5" t="inlineStr">
+      <c r="BF9" s="5" t="inlineStr"/>
+      <c r="BG9" s="5" t="inlineStr"/>
+      <c r="BH9" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI9" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG9" s="5" t="inlineStr">
+      <c r="BJ9" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -18793,12 +19547,19 @@
       <c r="BC10" s="3" t="inlineStr"/>
       <c r="BD10" s="3" t="inlineStr"/>
       <c r="BE10" s="3" t="inlineStr"/>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI10" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BJ10" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -18976,19 +19737,26 @@
       <c r="BC11" s="5" t="inlineStr"/>
       <c r="BD11" s="5" t="inlineStr"/>
       <c r="BE11" s="5" t="inlineStr"/>
-      <c r="BF11" s="5" t="inlineStr">
+      <c r="BF11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="inlineStr"/>
+      <c r="BH11" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI11" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG11" s="5" t="inlineStr">
+      <c r="BJ11" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18999,7 +19767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG77"/>
+  <dimension ref="A1:BJ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -19061,6 +19829,9 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -19331,30 +20102,45 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>H2H Over% (L5)</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>L5 vs Opp Hit%</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Days Rest</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Game Total</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Playoff Game</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Game Script Mult</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Game Script Note</t>
         </is>
@@ -19556,12 +20342,19 @@
       <c r="BC2" s="3" t="inlineStr"/>
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr"/>
-      <c r="BF2" s="3" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI2" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG2" s="3" t="inlineStr">
+      <c r="BJ2" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -19767,12 +20560,19 @@
       <c r="BC3" s="5" t="inlineStr"/>
       <c r="BD3" s="5" t="inlineStr"/>
       <c r="BE3" s="5" t="inlineStr"/>
-      <c r="BF3" s="5" t="inlineStr">
+      <c r="BF3" s="5" t="inlineStr"/>
+      <c r="BG3" s="5" t="inlineStr"/>
+      <c r="BH3" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI3" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG3" s="5" t="inlineStr">
+      <c r="BJ3" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -19982,12 +20782,19 @@
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr"/>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI4" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BJ4" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -20193,12 +21000,19 @@
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr"/>
-      <c r="BF5" s="5" t="inlineStr">
+      <c r="BF5" s="5" t="inlineStr"/>
+      <c r="BG5" s="5" t="inlineStr"/>
+      <c r="BH5" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI5" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG5" s="5" t="inlineStr">
+      <c r="BJ5" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -20388,12 +21202,19 @@
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
       <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI6" s="3" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BJ6" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -20603,12 +21424,19 @@
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
       <c r="BE7" s="5" t="inlineStr"/>
-      <c r="BF7" s="5" t="inlineStr">
+      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BG7" s="5" t="inlineStr"/>
+      <c r="BH7" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI7" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG7" s="5" t="inlineStr">
+      <c r="BJ7" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -20818,12 +21646,19 @@
       <c r="BC8" s="3" t="inlineStr"/>
       <c r="BD8" s="3" t="inlineStr"/>
       <c r="BE8" s="3" t="inlineStr"/>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr"/>
+      <c r="BH8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI8" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BJ8" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -21029,12 +21864,19 @@
       <c r="BC9" s="5" t="inlineStr"/>
       <c r="BD9" s="5" t="inlineStr"/>
       <c r="BE9" s="5" t="inlineStr"/>
-      <c r="BF9" s="5" t="inlineStr">
+      <c r="BF9" s="5" t="inlineStr"/>
+      <c r="BG9" s="5" t="inlineStr"/>
+      <c r="BH9" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI9" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG9" s="5" t="inlineStr">
+      <c r="BJ9" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -21236,12 +22078,19 @@
       <c r="BC10" s="3" t="inlineStr"/>
       <c r="BD10" s="3" t="inlineStr"/>
       <c r="BE10" s="3" t="inlineStr"/>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI10" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BJ10" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -21447,12 +22296,19 @@
       <c r="BC11" s="5" t="inlineStr"/>
       <c r="BD11" s="5" t="inlineStr"/>
       <c r="BE11" s="5" t="inlineStr"/>
-      <c r="BF11" s="5" t="inlineStr">
+      <c r="BF11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="inlineStr"/>
+      <c r="BH11" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI11" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG11" s="5" t="inlineStr">
+      <c r="BJ11" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -21654,12 +22510,19 @@
       <c r="BC12" s="3" t="inlineStr"/>
       <c r="BD12" s="3" t="inlineStr"/>
       <c r="BE12" s="3" t="inlineStr"/>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="3" t="inlineStr"/>
+      <c r="BG12" s="3" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI12" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BJ12" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -21849,12 +22712,19 @@
       <c r="BC13" s="5" t="inlineStr"/>
       <c r="BD13" s="5" t="inlineStr"/>
       <c r="BE13" s="5" t="inlineStr"/>
-      <c r="BF13" s="5" t="inlineStr">
+      <c r="BF13" s="5" t="inlineStr"/>
+      <c r="BG13" s="5" t="inlineStr"/>
+      <c r="BH13" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI13" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG13" s="5" t="inlineStr">
+      <c r="BJ13" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -22064,12 +22934,19 @@
       <c r="BC14" s="3" t="inlineStr"/>
       <c r="BD14" s="3" t="inlineStr"/>
       <c r="BE14" s="3" t="inlineStr"/>
-      <c r="BF14" s="3" t="inlineStr">
+      <c r="BF14" s="3" t="inlineStr"/>
+      <c r="BG14" s="3" t="inlineStr"/>
+      <c r="BH14" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI14" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BJ14" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -22279,12 +23156,19 @@
       <c r="BC15" s="5" t="inlineStr"/>
       <c r="BD15" s="5" t="inlineStr"/>
       <c r="BE15" s="5" t="inlineStr"/>
-      <c r="BF15" s="5" t="inlineStr">
+      <c r="BF15" s="5" t="inlineStr"/>
+      <c r="BG15" s="5" t="inlineStr"/>
+      <c r="BH15" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI15" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG15" s="5" t="inlineStr">
+      <c r="BJ15" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -22490,12 +23374,19 @@
       <c r="BC16" s="3" t="inlineStr"/>
       <c r="BD16" s="3" t="inlineStr"/>
       <c r="BE16" s="3" t="inlineStr"/>
-      <c r="BF16" s="3" t="inlineStr">
+      <c r="BF16" s="3" t="inlineStr"/>
+      <c r="BG16" s="3" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI16" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG16" s="3" t="inlineStr">
+      <c r="BJ16" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -22701,12 +23592,19 @@
       <c r="BC17" s="5" t="inlineStr"/>
       <c r="BD17" s="5" t="inlineStr"/>
       <c r="BE17" s="5" t="inlineStr"/>
-      <c r="BF17" s="5" t="inlineStr">
+      <c r="BF17" s="5" t="inlineStr"/>
+      <c r="BG17" s="5" t="inlineStr"/>
+      <c r="BH17" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI17" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG17" s="5" t="inlineStr">
+      <c r="BJ17" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -22916,12 +23814,19 @@
       <c r="BC18" s="3" t="inlineStr"/>
       <c r="BD18" s="3" t="inlineStr"/>
       <c r="BE18" s="3" t="inlineStr"/>
-      <c r="BF18" s="3" t="inlineStr">
+      <c r="BF18" s="3" t="inlineStr"/>
+      <c r="BG18" s="3" t="inlineStr"/>
+      <c r="BH18" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI18" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG18" s="3" t="inlineStr">
+      <c r="BJ18" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -23127,12 +24032,19 @@
       <c r="BC19" s="5" t="inlineStr"/>
       <c r="BD19" s="5" t="inlineStr"/>
       <c r="BE19" s="5" t="inlineStr"/>
-      <c r="BF19" s="5" t="inlineStr">
+      <c r="BF19" s="5" t="inlineStr"/>
+      <c r="BG19" s="5" t="inlineStr"/>
+      <c r="BH19" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI19" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG19" s="5" t="inlineStr">
+      <c r="BJ19" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -23334,12 +24246,19 @@
       <c r="BC20" s="3" t="inlineStr"/>
       <c r="BD20" s="3" t="inlineStr"/>
       <c r="BE20" s="3" t="inlineStr"/>
-      <c r="BF20" s="3" t="inlineStr">
+      <c r="BF20" s="3" t="inlineStr"/>
+      <c r="BG20" s="3" t="inlineStr"/>
+      <c r="BH20" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI20" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG20" s="3" t="inlineStr">
+      <c r="BJ20" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -23471,12 +24390,19 @@
       <c r="BC21" s="5" t="inlineStr"/>
       <c r="BD21" s="5" t="inlineStr"/>
       <c r="BE21" s="5" t="inlineStr"/>
-      <c r="BF21" s="5" t="inlineStr">
+      <c r="BF21" s="5" t="inlineStr"/>
+      <c r="BG21" s="5" t="inlineStr"/>
+      <c r="BH21" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI21" s="5" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG21" s="5" t="inlineStr">
+      <c r="BJ21" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -23608,12 +24534,19 @@
       <c r="BC22" s="3" t="inlineStr"/>
       <c r="BD22" s="3" t="inlineStr"/>
       <c r="BE22" s="3" t="inlineStr"/>
-      <c r="BF22" s="3" t="inlineStr">
+      <c r="BF22" s="3" t="inlineStr"/>
+      <c r="BG22" s="3" t="inlineStr"/>
+      <c r="BH22" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI22" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG22" s="3" t="inlineStr">
+      <c r="BJ22" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -23745,12 +24678,19 @@
       <c r="BC23" s="5" t="inlineStr"/>
       <c r="BD23" s="5" t="inlineStr"/>
       <c r="BE23" s="5" t="inlineStr"/>
-      <c r="BF23" s="5" t="inlineStr">
+      <c r="BF23" s="5" t="inlineStr"/>
+      <c r="BG23" s="5" t="inlineStr"/>
+      <c r="BH23" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI23" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG23" s="5" t="inlineStr">
+      <c r="BJ23" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -23882,12 +24822,19 @@
       <c r="BC24" s="3" t="inlineStr"/>
       <c r="BD24" s="3" t="inlineStr"/>
       <c r="BE24" s="3" t="inlineStr"/>
-      <c r="BF24" s="3" t="inlineStr">
+      <c r="BF24" s="3" t="inlineStr"/>
+      <c r="BG24" s="3" t="inlineStr"/>
+      <c r="BH24" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI24" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG24" s="3" t="inlineStr">
+      <c r="BJ24" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -24019,12 +24966,19 @@
       <c r="BC25" s="5" t="inlineStr"/>
       <c r="BD25" s="5" t="inlineStr"/>
       <c r="BE25" s="5" t="inlineStr"/>
-      <c r="BF25" s="5" t="inlineStr">
+      <c r="BF25" s="5" t="inlineStr"/>
+      <c r="BG25" s="5" t="inlineStr"/>
+      <c r="BH25" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI25" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG25" s="5" t="inlineStr">
+      <c r="BJ25" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -24156,12 +25110,19 @@
       <c r="BC26" s="3" t="inlineStr"/>
       <c r="BD26" s="3" t="inlineStr"/>
       <c r="BE26" s="3" t="inlineStr"/>
-      <c r="BF26" s="3" t="inlineStr">
+      <c r="BF26" s="3" t="inlineStr"/>
+      <c r="BG26" s="3" t="inlineStr"/>
+      <c r="BH26" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI26" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG26" s="3" t="inlineStr">
+      <c r="BJ26" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -24293,12 +25254,19 @@
       <c r="BC27" s="5" t="inlineStr"/>
       <c r="BD27" s="5" t="inlineStr"/>
       <c r="BE27" s="5" t="inlineStr"/>
-      <c r="BF27" s="5" t="inlineStr">
+      <c r="BF27" s="5" t="inlineStr"/>
+      <c r="BG27" s="5" t="inlineStr"/>
+      <c r="BH27" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI27" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG27" s="5" t="inlineStr">
+      <c r="BJ27" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -24430,12 +25398,19 @@
       <c r="BC28" s="3" t="inlineStr"/>
       <c r="BD28" s="3" t="inlineStr"/>
       <c r="BE28" s="3" t="inlineStr"/>
-      <c r="BF28" s="3" t="inlineStr">
+      <c r="BF28" s="3" t="inlineStr"/>
+      <c r="BG28" s="3" t="inlineStr"/>
+      <c r="BH28" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI28" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG28" s="3" t="inlineStr">
+      <c r="BJ28" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -24567,12 +25542,19 @@
       <c r="BC29" s="5" t="inlineStr"/>
       <c r="BD29" s="5" t="inlineStr"/>
       <c r="BE29" s="5" t="inlineStr"/>
-      <c r="BF29" s="5" t="inlineStr">
+      <c r="BF29" s="5" t="inlineStr"/>
+      <c r="BG29" s="5" t="inlineStr"/>
+      <c r="BH29" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI29" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG29" s="5" t="inlineStr">
+      <c r="BJ29" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -24704,12 +25686,19 @@
       <c r="BC30" s="3" t="inlineStr"/>
       <c r="BD30" s="3" t="inlineStr"/>
       <c r="BE30" s="3" t="inlineStr"/>
-      <c r="BF30" s="3" t="inlineStr">
+      <c r="BF30" s="3" t="inlineStr"/>
+      <c r="BG30" s="3" t="inlineStr"/>
+      <c r="BH30" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI30" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG30" s="3" t="inlineStr">
+      <c r="BJ30" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -24841,12 +25830,19 @@
       <c r="BC31" s="5" t="inlineStr"/>
       <c r="BD31" s="5" t="inlineStr"/>
       <c r="BE31" s="5" t="inlineStr"/>
-      <c r="BF31" s="5" t="inlineStr">
+      <c r="BF31" s="5" t="inlineStr"/>
+      <c r="BG31" s="5" t="inlineStr"/>
+      <c r="BH31" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI31" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG31" s="5" t="inlineStr">
+      <c r="BJ31" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -25038,12 +26034,19 @@
       <c r="BC32" s="3" t="inlineStr"/>
       <c r="BD32" s="3" t="inlineStr"/>
       <c r="BE32" s="3" t="inlineStr"/>
-      <c r="BF32" s="3" t="inlineStr">
+      <c r="BF32" s="3" t="inlineStr"/>
+      <c r="BG32" s="3" t="inlineStr"/>
+      <c r="BH32" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI32" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG32" s="3" t="inlineStr">
+      <c r="BJ32" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -25175,12 +26178,19 @@
       <c r="BC33" s="5" t="inlineStr"/>
       <c r="BD33" s="5" t="inlineStr"/>
       <c r="BE33" s="5" t="inlineStr"/>
-      <c r="BF33" s="5" t="inlineStr">
+      <c r="BF33" s="5" t="inlineStr"/>
+      <c r="BG33" s="5" t="inlineStr"/>
+      <c r="BH33" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI33" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG33" s="5" t="inlineStr">
+      <c r="BJ33" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -25388,12 +26398,19 @@
       <c r="BC34" s="3" t="inlineStr"/>
       <c r="BD34" s="3" t="inlineStr"/>
       <c r="BE34" s="3" t="inlineStr"/>
-      <c r="BF34" s="3" t="inlineStr">
+      <c r="BF34" s="3" t="inlineStr"/>
+      <c r="BG34" s="3" t="inlineStr"/>
+      <c r="BH34" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI34" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG34" s="3" t="inlineStr">
+      <c r="BJ34" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -25525,12 +26542,19 @@
       <c r="BC35" s="5" t="inlineStr"/>
       <c r="BD35" s="5" t="inlineStr"/>
       <c r="BE35" s="5" t="inlineStr"/>
-      <c r="BF35" s="5" t="inlineStr">
+      <c r="BF35" s="5" t="inlineStr"/>
+      <c r="BG35" s="5" t="inlineStr"/>
+      <c r="BH35" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI35" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG35" s="5" t="inlineStr">
+      <c r="BJ35" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -25662,12 +26686,19 @@
       <c r="BC36" s="3" t="inlineStr"/>
       <c r="BD36" s="3" t="inlineStr"/>
       <c r="BE36" s="3" t="inlineStr"/>
-      <c r="BF36" s="3" t="inlineStr">
+      <c r="BF36" s="3" t="inlineStr"/>
+      <c r="BG36" s="3" t="inlineStr"/>
+      <c r="BH36" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI36" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG36" s="3" t="inlineStr">
+      <c r="BJ36" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -25863,12 +26894,19 @@
       <c r="BC37" s="5" t="inlineStr"/>
       <c r="BD37" s="5" t="inlineStr"/>
       <c r="BE37" s="5" t="inlineStr"/>
-      <c r="BF37" s="5" t="inlineStr">
+      <c r="BF37" s="5" t="inlineStr"/>
+      <c r="BG37" s="5" t="inlineStr"/>
+      <c r="BH37" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI37" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG37" s="5" t="inlineStr">
+      <c r="BJ37" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -26000,12 +27038,19 @@
       <c r="BC38" s="3" t="inlineStr"/>
       <c r="BD38" s="3" t="inlineStr"/>
       <c r="BE38" s="3" t="inlineStr"/>
-      <c r="BF38" s="3" t="inlineStr">
+      <c r="BF38" s="3" t="inlineStr"/>
+      <c r="BG38" s="3" t="inlineStr"/>
+      <c r="BH38" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI38" s="3" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG38" s="3" t="inlineStr">
+      <c r="BJ38" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -26137,12 +27182,19 @@
       <c r="BC39" s="5" t="inlineStr"/>
       <c r="BD39" s="5" t="inlineStr"/>
       <c r="BE39" s="5" t="inlineStr"/>
-      <c r="BF39" s="5" t="inlineStr">
+      <c r="BF39" s="5" t="inlineStr"/>
+      <c r="BG39" s="5" t="inlineStr"/>
+      <c r="BH39" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI39" s="5" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="BG39" s="5" t="inlineStr">
+      <c r="BJ39" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, pts: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -26274,12 +27326,19 @@
       <c r="BC40" s="3" t="inlineStr"/>
       <c r="BD40" s="3" t="inlineStr"/>
       <c r="BE40" s="3" t="inlineStr"/>
-      <c r="BF40" s="3" t="inlineStr">
+      <c r="BF40" s="3" t="inlineStr"/>
+      <c r="BG40" s="3" t="inlineStr"/>
+      <c r="BH40" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI40" s="3" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG40" s="3" t="inlineStr">
+      <c r="BJ40" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -26411,12 +27470,19 @@
       <c r="BC41" s="5" t="inlineStr"/>
       <c r="BD41" s="5" t="inlineStr"/>
       <c r="BE41" s="5" t="inlineStr"/>
-      <c r="BF41" s="5" t="inlineStr">
+      <c r="BF41" s="5" t="inlineStr"/>
+      <c r="BG41" s="5" t="inlineStr"/>
+      <c r="BH41" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI41" s="5" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG41" s="5" t="inlineStr">
+      <c r="BJ41" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -26548,12 +27614,19 @@
       <c r="BC42" s="3" t="inlineStr"/>
       <c r="BD42" s="3" t="inlineStr"/>
       <c r="BE42" s="3" t="inlineStr"/>
-      <c r="BF42" s="3" t="inlineStr">
+      <c r="BF42" s="3" t="inlineStr"/>
+      <c r="BG42" s="3" t="inlineStr"/>
+      <c r="BH42" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI42" s="3" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG42" s="3" t="inlineStr">
+      <c r="BJ42" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -26685,12 +27758,19 @@
       <c r="BC43" s="5" t="inlineStr"/>
       <c r="BD43" s="5" t="inlineStr"/>
       <c r="BE43" s="5" t="inlineStr"/>
-      <c r="BF43" s="5" t="inlineStr">
+      <c r="BF43" s="5" t="inlineStr"/>
+      <c r="BG43" s="5" t="inlineStr"/>
+      <c r="BH43" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI43" s="5" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG43" s="5" t="inlineStr">
+      <c r="BJ43" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -26822,12 +27902,19 @@
       <c r="BC44" s="3" t="inlineStr"/>
       <c r="BD44" s="3" t="inlineStr"/>
       <c r="BE44" s="3" t="inlineStr"/>
-      <c r="BF44" s="3" t="inlineStr">
+      <c r="BF44" s="3" t="inlineStr"/>
+      <c r="BG44" s="3" t="inlineStr"/>
+      <c r="BH44" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI44" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG44" s="3" t="inlineStr">
+      <c r="BJ44" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -26959,12 +28046,19 @@
       <c r="BC45" s="5" t="inlineStr"/>
       <c r="BD45" s="5" t="inlineStr"/>
       <c r="BE45" s="5" t="inlineStr"/>
-      <c r="BF45" s="5" t="inlineStr">
+      <c r="BF45" s="5" t="inlineStr"/>
+      <c r="BG45" s="5" t="inlineStr"/>
+      <c r="BH45" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI45" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG45" s="5" t="inlineStr">
+      <c r="BJ45" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -27096,12 +28190,19 @@
       <c r="BC46" s="3" t="inlineStr"/>
       <c r="BD46" s="3" t="inlineStr"/>
       <c r="BE46" s="3" t="inlineStr"/>
-      <c r="BF46" s="3" t="inlineStr">
+      <c r="BF46" s="3" t="inlineStr"/>
+      <c r="BG46" s="3" t="inlineStr"/>
+      <c r="BH46" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI46" s="3" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG46" s="3" t="inlineStr">
+      <c r="BJ46" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -27233,12 +28334,19 @@
       <c r="BC47" s="5" t="inlineStr"/>
       <c r="BD47" s="5" t="inlineStr"/>
       <c r="BE47" s="5" t="inlineStr"/>
-      <c r="BF47" s="5" t="inlineStr">
+      <c r="BF47" s="5" t="inlineStr"/>
+      <c r="BG47" s="5" t="inlineStr"/>
+      <c r="BH47" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI47" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG47" s="5" t="inlineStr">
+      <c r="BJ47" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -27370,12 +28478,19 @@
       <c r="BC48" s="3" t="inlineStr"/>
       <c r="BD48" s="3" t="inlineStr"/>
       <c r="BE48" s="3" t="inlineStr"/>
-      <c r="BF48" s="3" t="inlineStr">
+      <c r="BF48" s="3" t="inlineStr"/>
+      <c r="BG48" s="3" t="inlineStr"/>
+      <c r="BH48" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI48" s="3" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG48" s="3" t="inlineStr">
+      <c r="BJ48" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -27507,12 +28622,19 @@
       <c r="BC49" s="5" t="inlineStr"/>
       <c r="BD49" s="5" t="inlineStr"/>
       <c r="BE49" s="5" t="inlineStr"/>
-      <c r="BF49" s="5" t="inlineStr">
+      <c r="BF49" s="5" t="inlineStr"/>
+      <c r="BG49" s="5" t="inlineStr"/>
+      <c r="BH49" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI49" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG49" s="5" t="inlineStr">
+      <c r="BJ49" s="5" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -27644,12 +28766,19 @@
       <c r="BC50" s="3" t="inlineStr"/>
       <c r="BD50" s="3" t="inlineStr"/>
       <c r="BE50" s="3" t="inlineStr"/>
-      <c r="BF50" s="3" t="inlineStr">
+      <c r="BF50" s="3" t="inlineStr"/>
+      <c r="BG50" s="3" t="inlineStr"/>
+      <c r="BH50" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI50" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG50" s="3" t="inlineStr">
+      <c r="BJ50" s="3" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -27781,12 +28910,19 @@
       <c r="BC51" s="5" t="inlineStr"/>
       <c r="BD51" s="5" t="inlineStr"/>
       <c r="BE51" s="5" t="inlineStr"/>
-      <c r="BF51" s="5" t="inlineStr">
+      <c r="BF51" s="5" t="inlineStr"/>
+      <c r="BG51" s="5" t="inlineStr"/>
+      <c r="BH51" s="5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI51" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG51" s="5" t="inlineStr">
+      <c r="BJ51" s="5" t="inlineStr">
         <is>
           <t>CHA +3.5 pt margin vs ORL, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -27918,12 +29054,19 @@
       <c r="BC52" s="3" t="inlineStr"/>
       <c r="BD52" s="3" t="inlineStr"/>
       <c r="BE52" s="3" t="inlineStr"/>
-      <c r="BF52" s="3" t="inlineStr">
+      <c r="BF52" s="3" t="inlineStr"/>
+      <c r="BG52" s="3" t="inlineStr"/>
+      <c r="BH52" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI52" s="3" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG52" s="3" t="inlineStr">
+      <c r="BJ52" s="3" t="inlineStr">
         <is>
           <t>ORL -3.5 pt margin vs CHA, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -28055,12 +29198,19 @@
       <c r="BC53" s="5" t="inlineStr"/>
       <c r="BD53" s="5" t="inlineStr"/>
       <c r="BE53" s="5" t="inlineStr"/>
-      <c r="BF53" s="5" t="inlineStr">
+      <c r="BF53" s="5" t="inlineStr"/>
+      <c r="BG53" s="5" t="inlineStr"/>
+      <c r="BH53" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI53" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG53" s="5" t="inlineStr">
+      <c r="BJ53" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -28192,12 +29342,19 @@
       <c r="BC54" s="3" t="inlineStr"/>
       <c r="BD54" s="3" t="inlineStr"/>
       <c r="BE54" s="3" t="inlineStr"/>
-      <c r="BF54" s="3" t="inlineStr">
+      <c r="BF54" s="3" t="inlineStr"/>
+      <c r="BG54" s="3" t="inlineStr"/>
+      <c r="BH54" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI54" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG54" s="3" t="inlineStr">
+      <c r="BJ54" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -28329,12 +29486,19 @@
       <c r="BC55" s="5" t="inlineStr"/>
       <c r="BD55" s="5" t="inlineStr"/>
       <c r="BE55" s="5" t="inlineStr"/>
-      <c r="BF55" s="5" t="inlineStr">
+      <c r="BF55" s="5" t="inlineStr"/>
+      <c r="BG55" s="5" t="inlineStr"/>
+      <c r="BH55" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI55" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG55" s="5" t="inlineStr">
+      <c r="BJ55" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -28466,12 +29630,19 @@
       <c r="BC56" s="3" t="inlineStr"/>
       <c r="BD56" s="3" t="inlineStr"/>
       <c r="BE56" s="3" t="inlineStr"/>
-      <c r="BF56" s="3" t="inlineStr">
+      <c r="BF56" s="3" t="inlineStr"/>
+      <c r="BG56" s="3" t="inlineStr"/>
+      <c r="BH56" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI56" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG56" s="3" t="inlineStr">
+      <c r="BJ56" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -28603,12 +29774,19 @@
       <c r="BC57" s="5" t="inlineStr"/>
       <c r="BD57" s="5" t="inlineStr"/>
       <c r="BE57" s="5" t="inlineStr"/>
-      <c r="BF57" s="5" t="inlineStr">
+      <c r="BF57" s="5" t="inlineStr"/>
+      <c r="BG57" s="5" t="inlineStr"/>
+      <c r="BH57" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI57" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG57" s="5" t="inlineStr">
+      <c r="BJ57" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -28740,12 +29918,19 @@
       <c r="BC58" s="3" t="inlineStr"/>
       <c r="BD58" s="3" t="inlineStr"/>
       <c r="BE58" s="3" t="inlineStr"/>
-      <c r="BF58" s="3" t="inlineStr">
+      <c r="BF58" s="3" t="inlineStr"/>
+      <c r="BG58" s="3" t="inlineStr"/>
+      <c r="BH58" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI58" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG58" s="3" t="inlineStr">
+      <c r="BJ58" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -28877,12 +30062,19 @@
       <c r="BC59" s="5" t="inlineStr"/>
       <c r="BD59" s="5" t="inlineStr"/>
       <c r="BE59" s="5" t="inlineStr"/>
-      <c r="BF59" s="5" t="inlineStr">
+      <c r="BF59" s="5" t="inlineStr"/>
+      <c r="BG59" s="5" t="inlineStr"/>
+      <c r="BH59" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI59" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG59" s="5" t="inlineStr">
+      <c r="BJ59" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -29014,12 +30206,19 @@
       <c r="BC60" s="3" t="inlineStr"/>
       <c r="BD60" s="3" t="inlineStr"/>
       <c r="BE60" s="3" t="inlineStr"/>
-      <c r="BF60" s="3" t="inlineStr">
+      <c r="BF60" s="3" t="inlineStr"/>
+      <c r="BG60" s="3" t="inlineStr"/>
+      <c r="BH60" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI60" s="3" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG60" s="3" t="inlineStr">
+      <c r="BJ60" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pra: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -29151,12 +30350,19 @@
       <c r="BC61" s="5" t="inlineStr"/>
       <c r="BD61" s="5" t="inlineStr"/>
       <c r="BE61" s="5" t="inlineStr"/>
-      <c r="BF61" s="5" t="inlineStr">
+      <c r="BF61" s="5" t="inlineStr"/>
+      <c r="BG61" s="5" t="inlineStr"/>
+      <c r="BH61" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI61" s="5" t="inlineStr">
         <is>
           <t>0.937</t>
         </is>
       </c>
-      <c r="BG61" s="5" t="inlineStr">
+      <c r="BJ61" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, fantasy: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -29288,12 +30494,19 @@
       <c r="BC62" s="3" t="inlineStr"/>
       <c r="BD62" s="3" t="inlineStr"/>
       <c r="BE62" s="3" t="inlineStr"/>
-      <c r="BF62" s="3" t="inlineStr">
+      <c r="BF62" s="3" t="inlineStr"/>
+      <c r="BG62" s="3" t="inlineStr"/>
+      <c r="BH62" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI62" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG62" s="3" t="inlineStr">
+      <c r="BJ62" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -29425,12 +30638,19 @@
       <c r="BC63" s="5" t="inlineStr"/>
       <c r="BD63" s="5" t="inlineStr"/>
       <c r="BE63" s="5" t="inlineStr"/>
-      <c r="BF63" s="5" t="inlineStr">
+      <c r="BF63" s="5" t="inlineStr"/>
+      <c r="BG63" s="5" t="inlineStr"/>
+      <c r="BH63" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI63" s="5" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG63" s="5" t="inlineStr">
+      <c r="BJ63" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -29562,12 +30782,19 @@
       <c r="BC64" s="3" t="inlineStr"/>
       <c r="BD64" s="3" t="inlineStr"/>
       <c r="BE64" s="3" t="inlineStr"/>
-      <c r="BF64" s="3" t="inlineStr">
+      <c r="BF64" s="3" t="inlineStr"/>
+      <c r="BG64" s="3" t="inlineStr"/>
+      <c r="BH64" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI64" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG64" s="3" t="inlineStr">
+      <c r="BJ64" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, fantasy: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -29699,12 +30926,19 @@
       <c r="BC65" s="5" t="inlineStr"/>
       <c r="BD65" s="5" t="inlineStr"/>
       <c r="BE65" s="5" t="inlineStr"/>
-      <c r="BF65" s="5" t="inlineStr">
+      <c r="BF65" s="5" t="inlineStr"/>
+      <c r="BG65" s="5" t="inlineStr"/>
+      <c r="BH65" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI65" s="5" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="BG65" s="5" t="inlineStr">
+      <c r="BJ65" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, pts: 0.93x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -29884,12 +31118,19 @@
       <c r="BC66" s="3" t="inlineStr"/>
       <c r="BD66" s="3" t="inlineStr"/>
       <c r="BE66" s="3" t="inlineStr"/>
-      <c r="BF66" s="3" t="inlineStr">
+      <c r="BF66" s="3" t="inlineStr"/>
+      <c r="BG66" s="3" t="inlineStr"/>
+      <c r="BH66" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI66" s="3" t="inlineStr">
         <is>
           <t>1.018</t>
         </is>
       </c>
-      <c r="BG66" s="3" t="inlineStr">
+      <c r="BJ66" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, pra: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -30021,12 +31262,19 @@
       <c r="BC67" s="5" t="inlineStr"/>
       <c r="BD67" s="5" t="inlineStr"/>
       <c r="BE67" s="5" t="inlineStr"/>
-      <c r="BF67" s="5" t="inlineStr">
+      <c r="BF67" s="5" t="inlineStr"/>
+      <c r="BG67" s="5" t="inlineStr"/>
+      <c r="BH67" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI67" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG67" s="5" t="inlineStr">
+      <c r="BJ67" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -30158,12 +31406,19 @@
       <c r="BC68" s="3" t="inlineStr"/>
       <c r="BD68" s="3" t="inlineStr"/>
       <c r="BE68" s="3" t="inlineStr"/>
-      <c r="BF68" s="3" t="inlineStr">
+      <c r="BF68" s="3" t="inlineStr"/>
+      <c r="BG68" s="3" t="inlineStr"/>
+      <c r="BH68" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI68" s="3" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG68" s="3" t="inlineStr">
+      <c r="BJ68" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -30295,12 +31550,19 @@
       <c r="BC69" s="5" t="inlineStr"/>
       <c r="BD69" s="5" t="inlineStr"/>
       <c r="BE69" s="5" t="inlineStr"/>
-      <c r="BF69" s="5" t="inlineStr">
+      <c r="BF69" s="5" t="inlineStr"/>
+      <c r="BG69" s="5" t="inlineStr"/>
+      <c r="BH69" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI69" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG69" s="5" t="inlineStr">
+      <c r="BJ69" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -30432,12 +31694,19 @@
       <c r="BC70" s="3" t="inlineStr"/>
       <c r="BD70" s="3" t="inlineStr"/>
       <c r="BE70" s="3" t="inlineStr"/>
-      <c r="BF70" s="3" t="inlineStr">
+      <c r="BF70" s="3" t="inlineStr"/>
+      <c r="BG70" s="3" t="inlineStr"/>
+      <c r="BH70" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI70" s="3" t="inlineStr">
         <is>
           <t>1.016</t>
         </is>
       </c>
-      <c r="BG70" s="3" t="inlineStr">
+      <c r="BJ70" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, 3ptmade: 1.02x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -30569,12 +31838,19 @@
       <c r="BC71" s="5" t="inlineStr"/>
       <c r="BD71" s="5" t="inlineStr"/>
       <c r="BE71" s="5" t="inlineStr"/>
-      <c r="BF71" s="5" t="inlineStr">
+      <c r="BF71" s="5" t="inlineStr"/>
+      <c r="BG71" s="5" t="inlineStr"/>
+      <c r="BH71" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI71" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG71" s="5" t="inlineStr">
+      <c r="BJ71" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -30706,12 +31982,19 @@
       <c r="BC72" s="3" t="inlineStr"/>
       <c r="BD72" s="3" t="inlineStr"/>
       <c r="BE72" s="3" t="inlineStr"/>
-      <c r="BF72" s="3" t="inlineStr">
+      <c r="BF72" s="3" t="inlineStr"/>
+      <c r="BG72" s="3" t="inlineStr"/>
+      <c r="BH72" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI72" s="3" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG72" s="3" t="inlineStr">
+      <c r="BJ72" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -30843,12 +32126,19 @@
       <c r="BC73" s="5" t="inlineStr"/>
       <c r="BD73" s="5" t="inlineStr"/>
       <c r="BE73" s="5" t="inlineStr"/>
-      <c r="BF73" s="5" t="inlineStr">
+      <c r="BF73" s="5" t="inlineStr"/>
+      <c r="BG73" s="5" t="inlineStr"/>
+      <c r="BH73" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI73" s="5" t="inlineStr">
         <is>
           <t>0.944</t>
         </is>
       </c>
-      <c r="BG73" s="5" t="inlineStr">
+      <c r="BJ73" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, 3ptmade: 0.94x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -30980,12 +32270,19 @@
       <c r="BC74" s="3" t="inlineStr"/>
       <c r="BD74" s="3" t="inlineStr"/>
       <c r="BE74" s="3" t="inlineStr"/>
-      <c r="BF74" s="3" t="inlineStr">
+      <c r="BF74" s="3" t="inlineStr"/>
+      <c r="BG74" s="3" t="inlineStr"/>
+      <c r="BH74" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI74" s="3" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG74" s="3" t="inlineStr">
+      <c r="BJ74" s="3" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -31117,12 +32414,19 @@
       <c r="BC75" s="5" t="inlineStr"/>
       <c r="BD75" s="5" t="inlineStr"/>
       <c r="BE75" s="5" t="inlineStr"/>
-      <c r="BF75" s="5" t="inlineStr">
+      <c r="BF75" s="5" t="inlineStr"/>
+      <c r="BG75" s="5" t="inlineStr"/>
+      <c r="BH75" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI75" s="5" t="inlineStr">
         <is>
           <t>1.014</t>
         </is>
       </c>
-      <c r="BG75" s="5" t="inlineStr">
+      <c r="BJ75" s="5" t="inlineStr">
         <is>
           <t>PHX +3.5 pt margin vs ?, ftm: 1.01x game script (fav; spread_risk 1.02, total_risk 1.00)</t>
         </is>
@@ -31254,12 +32558,19 @@
       <c r="BC76" s="3" t="inlineStr"/>
       <c r="BD76" s="3" t="inlineStr"/>
       <c r="BE76" s="3" t="inlineStr"/>
-      <c r="BF76" s="3" t="inlineStr">
+      <c r="BF76" s="3" t="inlineStr"/>
+      <c r="BG76" s="3" t="inlineStr"/>
+      <c r="BH76" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI76" s="3" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG76" s="3" t="inlineStr">
+      <c r="BJ76" s="3" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
@@ -31391,19 +32702,26 @@
       <c r="BC77" s="5" t="inlineStr"/>
       <c r="BD77" s="5" t="inlineStr"/>
       <c r="BE77" s="5" t="inlineStr"/>
-      <c r="BF77" s="5" t="inlineStr">
+      <c r="BF77" s="5" t="inlineStr"/>
+      <c r="BG77" s="5" t="inlineStr"/>
+      <c r="BH77" s="5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BI77" s="5" t="inlineStr">
         <is>
           <t>0.951</t>
         </is>
       </c>
-      <c r="BG77" s="5" t="inlineStr">
+      <c r="BJ77" s="5" t="inlineStr">
         <is>
           <t>GSW -3.5 pt margin vs ?, ftm: 0.95x game script (dog; spread_risk 0.93, total_risk 1.00)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG1"/>
+  <autoFilter ref="A1:BJ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NBA/step8_nba1h_direction_clean.xlsx
+++ b/NBA/step8_nba1h_direction_clean.xlsx
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -3656,32 +3656,32 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27 21:30:00-04:00</t>
+          <t>2026-04-27 22:30:00-04:00</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -3700,16 +3700,16 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>4.34</v>
+        <v>1.44</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>4.34</v>
+        <v>1.44</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>9.84</v>
+        <v>6.94</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>0.951</v>
+        <v>0.9587</v>
       </c>
       <c r="P15" s="5" t="inlineStr"/>
       <c r="Q15" s="5" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         <v>0.6</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="U15" s="5" t="n">
         <v>3</v>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="X15" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y15" s="5" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z15" s="5" t="inlineStr">
@@ -3763,62 +3763,70 @@
       </c>
       <c r="AD15" s="5" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>7.286</t>
         </is>
       </c>
       <c r="AE15" s="5" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AF15" s="5" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>7.286</t>
         </is>
       </c>
       <c r="AG15" s="5" t="inlineStr"/>
       <c r="AH15" s="5" t="inlineStr"/>
       <c r="AI15" s="5" t="n">
-        <v>47.82608695652173</v>
+        <v>36.47269654458486</v>
       </c>
       <c r="AJ15" s="5" t="inlineStr"/>
       <c r="AK15" s="5" t="n">
-        <v>0</v>
+        <v>-0.6859999999999999</v>
       </c>
       <c r="AL15" s="5" t="inlineStr"/>
       <c r="AM15" s="5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AN15" s="5" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO15" s="5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AP15" s="5" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AQ15" s="5" t="inlineStr">
         <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AR15" s="5" t="inlineStr"/>
-      <c r="AS15" s="5" t="inlineStr"/>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AR15" s="5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AS15" s="5" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="AT15" s="5" t="inlineStr"/>
       <c r="AU15" s="5" t="inlineStr"/>
       <c r="AV15" s="5" t="inlineStr"/>
       <c r="AW15" s="5" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>7.286</t>
         </is>
       </c>
       <c r="AX15" s="5" t="inlineStr"/>
@@ -3854,36 +3862,36 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Jordan Goodwin</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27 22:30:00-04:00</t>
+          <t>2026-04-27 21:30:00-04:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -3893,7 +3901,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -3902,45 +3910,45 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.44</v>
+        <v>4.95</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.44</v>
+        <v>4.95</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>6.94</v>
+        <v>11.45</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.9587</v>
+        <v>0.9585</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="3" t="inlineStr"/>
       <c r="R16" s="3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>6.6</v>
+        <v>11.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>7.3</v>
+        <v>10</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>5</v>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -3955,7 +3963,7 @@
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
@@ -3965,62 +3973,62 @@
       </c>
       <c r="AD16" s="3" t="inlineStr">
         <is>
-          <t>7.286</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>7.286</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr"/>
       <c r="AH16" s="3" t="inlineStr"/>
       <c r="AI16" s="3" t="n">
-        <v>36.47269654458486</v>
+        <v>38.54496446637727</v>
       </c>
       <c r="AJ16" s="3" t="inlineStr"/>
       <c r="AK16" s="3" t="n">
-        <v>-0.6859999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="AL16" s="3" t="inlineStr"/>
       <c r="AM16" s="3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AN16" s="3" t="inlineStr">
         <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
           <t>5.0</t>
-        </is>
-      </c>
-      <c r="AO16" s="3" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ16" s="3" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AR16" s="3" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AS16" s="3" t="inlineStr">
-        <is>
-          <t>8.0</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr"/>
@@ -4028,7 +4036,7 @@
       <c r="AV16" s="3" t="inlineStr"/>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>7.286</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr"/>
@@ -4068,7 +4076,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Jordan Goodwin</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -4078,22 +4086,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27 21:30:00-04:00</t>
+          <t>2026-04-27 22:30:00-04:00</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -4103,7 +4111,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -4112,45 +4120,45 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>4.95</v>
+        <v>2.35</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>4.95</v>
+        <v>2.35</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>11.45</v>
+        <v>7.85</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.9585</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="P17" s="5" t="inlineStr"/>
       <c r="Q17" s="5" t="inlineStr"/>
       <c r="R17" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="S17" s="5" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="T17" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="U17" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="W17" s="5" t="n">
         <v>5</v>
       </c>
       <c r="X17" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Y17" s="5" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Z17" s="5" t="inlineStr">
@@ -4165,7 +4173,7 @@
       </c>
       <c r="AB17" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AC17" s="5" t="inlineStr">
@@ -4175,70 +4183,82 @@
       </c>
       <c r="AD17" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AE17" s="5" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AF17" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AG17" s="5" t="inlineStr"/>
       <c r="AH17" s="5" t="inlineStr"/>
       <c r="AI17" s="5" t="n">
-        <v>38.54496446637727</v>
+        <v>40.19561849622249</v>
       </c>
       <c r="AJ17" s="5" t="inlineStr"/>
       <c r="AK17" s="5" t="n">
-        <v>1.4</v>
+        <v>1.100000000000001</v>
       </c>
       <c r="AL17" s="5" t="inlineStr"/>
       <c r="AM17" s="5" t="inlineStr">
         <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AN17" s="5" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AO17" s="5" t="inlineStr">
+        <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="AN17" s="5" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="AO17" s="5" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
       <c r="AP17" s="5" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ17" s="5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AR17" s="5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AS17" s="5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT17" s="5" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AQ17" s="5" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AR17" s="5" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AS17" s="5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT17" s="5" t="inlineStr"/>
-      <c r="AU17" s="5" t="inlineStr"/>
-      <c r="AV17" s="5" t="inlineStr"/>
+      <c r="AU17" s="5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AV17" s="5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="AW17" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AX17" s="5" t="inlineStr"/>
@@ -4274,16 +4294,16 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -4322,16 +4342,16 @@
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>7.85</v>
+        <v>7.79</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9394</v>
       </c>
       <c r="P18" s="3" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr"/>
@@ -4339,10 +4359,10 @@
         <v>0.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>4</v>
@@ -4385,82 +4405,78 @@
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.778</t>
         </is>
       </c>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.778</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr"/>
       <c r="AH18" s="3" t="inlineStr"/>
       <c r="AI18" s="3" t="n">
-        <v>40.19561849622249</v>
+        <v>42.7617987059879</v>
       </c>
       <c r="AJ18" s="3" t="inlineStr"/>
       <c r="AK18" s="3" t="n">
-        <v>1.100000000000001</v>
+        <v>0.02200000000000024</v>
       </c>
       <c r="AL18" s="3" t="inlineStr"/>
       <c r="AM18" s="3" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AQ18" s="3" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AR18" s="3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
+      <c r="AV18" s="3" t="inlineStr"/>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.778</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr"/>
@@ -4496,31 +4512,31 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27 22:30:00-04:00</t>
+          <t>2026-04-27 20:00:00-04:00</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -4535,7 +4551,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -4544,45 +4560,45 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>2.29</v>
+        <v>1.14</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>2.29</v>
+        <v>1.14</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>7.79</v>
+        <v>3.36</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.9394</v>
+        <v>0.9606</v>
       </c>
       <c r="P19" s="5" t="inlineStr"/>
       <c r="Q19" s="5" t="inlineStr"/>
       <c r="R19" s="5" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>7.8</v>
+        <v>3</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
       <c r="U19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="V19" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="W19" s="5" t="n">
         <v>5</v>
       </c>
       <c r="X19" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y19" s="5" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Z19" s="5" t="inlineStr">
@@ -4600,85 +4616,73 @@
           <t>SUPPORT</t>
         </is>
       </c>
-      <c r="AC19" s="5" t="inlineStr">
-        <is>
-          <t>VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+      <c r="AC19" s="5" t="inlineStr"/>
       <c r="AD19" s="5" t="inlineStr">
         <is>
-          <t>7.778</t>
+          <t>3.714</t>
         </is>
       </c>
       <c r="AE19" s="5" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AF19" s="5" t="inlineStr">
         <is>
-          <t>7.778</t>
+          <t>3.714</t>
         </is>
       </c>
       <c r="AG19" s="5" t="inlineStr"/>
       <c r="AH19" s="5" t="inlineStr"/>
       <c r="AI19" s="5" t="n">
-        <v>42.7617987059879</v>
+        <v>63.89710663783134</v>
       </c>
       <c r="AJ19" s="5" t="inlineStr"/>
       <c r="AK19" s="5" t="n">
-        <v>0.02200000000000024</v>
+        <v>-0.714</v>
       </c>
       <c r="AL19" s="5" t="inlineStr"/>
       <c r="AM19" s="5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN19" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AO19" s="5" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AP19" s="5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AQ19" s="5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AR19" s="5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS19" s="5" t="inlineStr">
+        <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="AP19" s="5" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AQ19" s="5" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AR19" s="5" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AS19" s="5" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT19" s="5" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU19" s="5" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
+      <c r="AT19" s="5" t="inlineStr"/>
+      <c r="AU19" s="5" t="inlineStr"/>
       <c r="AV19" s="5" t="inlineStr"/>
       <c r="AW19" s="5" t="inlineStr">
         <is>
-          <t>7.778</t>
+          <t>3.714</t>
         </is>
       </c>
       <c r="AX19" s="5" t="inlineStr"/>
@@ -4693,7 +4697,7 @@
       <c r="BG19" s="5" t="inlineStr"/>
       <c r="BH19" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="BI19" s="5" t="inlineStr">
@@ -4714,36 +4718,36 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27 20:00:00-04:00</t>
+          <t>2026-04-27 22:30:00-04:00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -4753,7 +4757,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -4762,45 +4766,45 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.14</v>
+        <v>3.82</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.14</v>
+        <v>3.82</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>3.36</v>
+        <v>16.32</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.9606</v>
+        <v>0.9423</v>
       </c>
       <c r="P20" s="3" t="inlineStr"/>
       <c r="Q20" s="3" t="inlineStr"/>
       <c r="R20" s="3" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="S20" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U20" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="T20" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U20" s="3" t="n">
+      <c r="V20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="W20" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="W20" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -4815,76 +4819,64 @@
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr"/>
       <c r="AD20" s="3" t="inlineStr">
         <is>
-          <t>3.714</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>3.714</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr"/>
       <c r="AH20" s="3" t="inlineStr"/>
       <c r="AI20" s="3" t="n">
-        <v>63.89710663783134</v>
+        <v>12.59204220962067</v>
       </c>
       <c r="AJ20" s="3" t="inlineStr"/>
       <c r="AK20" s="3" t="n">
-        <v>-0.714</v>
+        <v>0</v>
       </c>
       <c r="AL20" s="3" t="inlineStr"/>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AQ20" s="3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AR20" s="3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr"/>
+      <c r="AS20" s="3" t="inlineStr"/>
       <c r="AT20" s="3" t="inlineStr"/>
       <c r="AU20" s="3" t="inlineStr"/>
       <c r="AV20" s="3" t="inlineStr"/>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>3.714</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr"/>
@@ -4899,7 +4891,7 @@
       <c r="BG20" s="3" t="inlineStr"/>
       <c r="BH20" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="BI20" s="3" t="inlineStr">
@@ -4920,28 +4912,28 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
           <t>2026-04-27 22:30:00-04:00</t>
@@ -4959,7 +4951,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -4968,45 +4960,45 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.82</v>
+        <v>4.43</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>3.82</v>
+        <v>4.43</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>16.32</v>
+        <v>13.43</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.9423</v>
+        <v>0.951</v>
       </c>
       <c r="P21" s="5" t="inlineStr"/>
       <c r="Q21" s="5" t="inlineStr"/>
       <c r="R21" s="5" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>15.2</v>
+        <v>12.6</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>15.2</v>
+        <v>12.5</v>
       </c>
       <c r="U21" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="W21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X21" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Y21" s="5" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Z21" s="5" t="inlineStr">
@@ -5024,61 +5016,73 @@
           <t>SECONDARY</t>
         </is>
       </c>
-      <c r="AC21" s="5" t="inlineStr"/>
+      <c r="AC21" s="5" t="inlineStr">
+        <is>
+          <t>VOID_LOW_MINUTES_NON_A</t>
+        </is>
+      </c>
       <c r="AD21" s="5" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AE21" s="5" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AF21" s="5" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG21" s="5" t="inlineStr"/>
       <c r="AH21" s="5" t="inlineStr"/>
       <c r="AI21" s="5" t="n">
-        <v>12.59204220962067</v>
+        <v>26.43230346879868</v>
       </c>
       <c r="AJ21" s="5" t="inlineStr"/>
       <c r="AK21" s="5" t="n">
-        <v>0</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="AL21" s="5" t="inlineStr"/>
       <c r="AM21" s="5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AN21" s="5" t="inlineStr">
         <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AO21" s="5" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AP21" s="5" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AQ21" s="5" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="AR21" s="5" t="inlineStr">
+        <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="AO21" s="5" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="AP21" s="5" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="AQ21" s="5" t="inlineStr"/>
-      <c r="AR21" s="5" t="inlineStr"/>
       <c r="AS21" s="5" t="inlineStr"/>
       <c r="AT21" s="5" t="inlineStr"/>
       <c r="AU21" s="5" t="inlineStr"/>
       <c r="AV21" s="5" t="inlineStr"/>
       <c r="AW21" s="5" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AX21" s="5" t="inlineStr"/>
@@ -5114,31 +5118,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27 22:30:00-04:00</t>
+          <t>2026-04-27 21:30:00-04:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5153,7 +5157,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -5162,45 +5166,45 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>4.43</v>
+        <v>3.84</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>4.43</v>
+        <v>3.84</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>13.43</v>
+        <v>9.84</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.951</v>
+        <v>0.9496</v>
       </c>
       <c r="P22" s="3" t="inlineStr"/>
       <c r="Q22" s="3" t="inlineStr"/>
       <c r="R22" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>12.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>5</v>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
@@ -5215,7 +5219,7 @@
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
@@ -5225,66 +5229,62 @@
       </c>
       <c r="AD22" s="3" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr"/>
       <c r="AH22" s="3" t="inlineStr"/>
       <c r="AI22" s="3" t="n">
-        <v>26.43230346879868</v>
+        <v>47.82608695652173</v>
       </c>
       <c r="AJ22" s="3" t="inlineStr"/>
       <c r="AK22" s="3" t="n">
-        <v>0.09999999999999964</v>
+        <v>0</v>
       </c>
       <c r="AL22" s="3" t="inlineStr"/>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
         <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
           <t>14.0</t>
         </is>
       </c>
-      <c r="AO22" s="3" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AR22" s="3" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AR22" s="3" t="inlineStr"/>
       <c r="AS22" s="3" t="inlineStr"/>
       <c r="AT22" s="3" t="inlineStr"/>
       <c r="AU22" s="3" t="inlineStr"/>
       <c r="AV22" s="3" t="inlineStr"/>
       <c r="AW22" s="3" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AX22" s="3" t="inlineStr"/>
@@ -5518,24 +5518,24 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
           <t>ORL</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
           <t>2026-04-27 20:00:00-04:00</t>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -5562,45 +5562,45 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1.9</v>
+        <v>4.89</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>1.9</v>
+        <v>4.89</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>8.1</v>
+        <v>19.39</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.9506</v>
+        <v>0.9431</v>
       </c>
       <c r="P24" s="3" t="inlineStr"/>
       <c r="Q24" s="3" t="inlineStr"/>
       <c r="R24" s="3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>7.4</v>
+        <v>17.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>5</v>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -5615,88 +5615,84 @@
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr"/>
       <c r="AD24" s="3" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>18.444</t>
         </is>
       </c>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>18.444</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr"/>
       <c r="AH24" s="3" t="inlineStr"/>
       <c r="AI24" s="3" t="n">
-        <v>58.12141751156554</v>
+        <v>25.57227141782064</v>
       </c>
       <c r="AJ24" s="3" t="inlineStr"/>
       <c r="AK24" s="3" t="n">
-        <v>-1.4</v>
+        <v>-0.6439999999999984</v>
       </c>
       <c r="AL24" s="3" t="inlineStr"/>
       <c r="AM24" s="3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AV24" s="3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr"/>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>18.444</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr"/>
@@ -5736,24 +5732,24 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>ORL</t>
-        </is>
-      </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
           <t>2026-04-27 20:00:00-04:00</t>
@@ -5761,7 +5757,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -5771,7 +5767,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -5780,45 +5776,45 @@
         </is>
       </c>
       <c r="L25" s="5" t="n">
-        <v>4.89</v>
+        <v>1.9</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>4.89</v>
+        <v>1.9</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>19.39</v>
+        <v>8.1</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>0.9431</v>
+        <v>0.9506</v>
       </c>
       <c r="P25" s="5" t="inlineStr"/>
       <c r="Q25" s="5" t="inlineStr"/>
       <c r="R25" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S25" s="5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T25" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="U25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="S25" s="5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="T25" s="5" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="U25" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="V25" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W25" s="5" t="n">
         <v>5</v>
       </c>
       <c r="X25" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y25" s="5" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Z25" s="5" t="inlineStr">
@@ -5833,84 +5829,88 @@
       </c>
       <c r="AB25" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AC25" s="5" t="inlineStr"/>
       <c r="AD25" s="5" t="inlineStr">
         <is>
-          <t>18.444</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AE25" s="5" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AF25" s="5" t="inlineStr">
         <is>
-          <t>18.444</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AG25" s="5" t="inlineStr"/>
       <c r="AH25" s="5" t="inlineStr"/>
       <c r="AI25" s="5" t="n">
-        <v>25.57227141782064</v>
+        <v>58.12141751156554</v>
       </c>
       <c r="AJ25" s="5" t="inlineStr"/>
       <c r="AK25" s="5" t="n">
-        <v>-0.6439999999999984</v>
+        <v>-1.4</v>
       </c>
       <c r="AL25" s="5" t="inlineStr"/>
       <c r="AM25" s="5" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AN25" s="5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AO25" s="5" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AP25" s="5" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AQ25" s="5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AR25" s="5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AS25" s="5" t="inlineStr">
         <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="AT25" s="5" t="inlineStr">
+        <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AT25" s="5" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
       <c r="AU25" s="5" t="inlineStr">
         <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="AV25" s="5" t="inlineStr"/>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AV25" s="5" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
       <c r="AW25" s="5" t="inlineStr">
         <is>
-          <t>18.444</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AX25" s="5" t="inlineStr"/>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -10634,36 +10634,36 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.16</v>
+        <v>0.85</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>5.16</v>
+        <v>0.85</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>18.66</v>
+        <v>4.85</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.9368</v>
+        <v>0.9555</v>
       </c>
       <c r="P48" s="3" t="inlineStr"/>
       <c r="Q48" s="3" t="inlineStr"/>
       <c r="R48" s="3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>18.9</v>
+        <v>5.9</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V48" s="3" t="n">
         <v>2</v>
       </c>
       <c r="W48" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
@@ -10687,84 +10687,92 @@
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
         </is>
       </c>
       <c r="AD48" s="3" t="inlineStr">
         <is>
-          <t>18.875</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
         <is>
-          <t>18.875</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AG48" s="3" t="inlineStr"/>
       <c r="AH48" s="3" t="inlineStr"/>
       <c r="AI48" s="3" t="n">
-        <v>35.48457834336109</v>
+        <v>43.83904120805953</v>
       </c>
       <c r="AJ48" s="3" t="inlineStr"/>
       <c r="AK48" s="3" t="n">
-        <v>-2.875</v>
+        <v>-2.100000000000001</v>
       </c>
       <c r="AL48" s="3" t="inlineStr"/>
       <c r="AM48" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AN48" s="3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AQ48" s="3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AR48" s="3" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr"/>
-      <c r="AV48" s="3" t="inlineStr"/>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>18.875</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr"/>
@@ -10800,36 +10808,36 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27 21:30:00-04:00</t>
+          <t>2026-04-27 20:00:00-04:00</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -10839,7 +10847,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -10848,45 +10856,45 @@
         </is>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.85</v>
+        <v>1.52</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>0.85</v>
+        <v>1.52</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>4.85</v>
+        <v>14.02</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>0.9555</v>
+        <v>0.9532</v>
       </c>
       <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr"/>
       <c r="R49" s="5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="S49" s="5" t="n">
-        <v>3.8</v>
+        <v>13.2</v>
       </c>
       <c r="T49" s="5" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="U49" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V49" s="5" t="n">
         <v>2</v>
       </c>
       <c r="W49" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X49" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y49" s="5" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z49" s="5" t="inlineStr">
@@ -10901,7 +10909,7 @@
       </c>
       <c r="AB49" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AC49" s="5" t="inlineStr">
@@ -10911,82 +10919,66 @@
       </c>
       <c r="AD49" s="5" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AE49" s="5" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AF49" s="5" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AG49" s="5" t="inlineStr"/>
       <c r="AH49" s="5" t="inlineStr"/>
       <c r="AI49" s="5" t="n">
-        <v>43.83904120805953</v>
+        <v>18.31135494498167</v>
       </c>
       <c r="AJ49" s="5" t="inlineStr"/>
       <c r="AK49" s="5" t="n">
-        <v>-2.100000000000001</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="AL49" s="5" t="inlineStr"/>
       <c r="AM49" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AN49" s="5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO49" s="5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AP49" s="5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AQ49" s="5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AR49" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AS49" s="5" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AT49" s="5" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU49" s="5" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AV49" s="5" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AS49" s="5" t="inlineStr"/>
+      <c r="AT49" s="5" t="inlineStr"/>
+      <c r="AU49" s="5" t="inlineStr"/>
+      <c r="AV49" s="5" t="inlineStr"/>
       <c r="AW49" s="5" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AX49" s="5" t="inlineStr"/>
@@ -11001,7 +10993,7 @@
       <c r="BG49" s="5" t="inlineStr"/>
       <c r="BH49" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="BI49" s="5" t="inlineStr">
@@ -11022,31 +11014,31 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F-C</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27 20:00:00-04:00</t>
+          <t>2026-04-27 22:30:00-04:00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -11061,7 +11053,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -11070,16 +11062,16 @@
         </is>
       </c>
       <c r="L50" s="3" t="n">
-        <v>1.52</v>
+        <v>0.52</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>1.52</v>
+        <v>0.52</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>14.02</v>
+        <v>17.52</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>0.9532</v>
+        <v>0.951</v>
       </c>
       <c r="P50" s="3" t="inlineStr"/>
       <c r="Q50" s="3" t="inlineStr"/>
@@ -11087,10 +11079,10 @@
         <v>0.6</v>
       </c>
       <c r="S50" s="3" t="n">
-        <v>13.2</v>
+        <v>16.6</v>
       </c>
       <c r="T50" s="3" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="U50" s="3" t="n">
         <v>3</v>
@@ -11103,7 +11095,7 @@
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
@@ -11128,71 +11120,75 @@
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D</t>
         </is>
       </c>
       <c r="AD50" s="3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.143</t>
         </is>
       </c>
       <c r="AE50" s="3" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AF50" s="3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.143</t>
         </is>
       </c>
       <c r="AG50" s="3" t="inlineStr"/>
       <c r="AH50" s="3" t="inlineStr"/>
       <c r="AI50" s="3" t="n">
-        <v>18.31135494498167</v>
+        <v>18.85599624129426</v>
       </c>
       <c r="AJ50" s="3" t="inlineStr"/>
       <c r="AK50" s="3" t="n">
-        <v>0.1999999999999993</v>
+        <v>0.4570000000000007</v>
       </c>
       <c r="AL50" s="3" t="inlineStr"/>
       <c r="AM50" s="3" t="inlineStr">
         <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AO50" s="3" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="AQ50" s="3" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AR50" s="3" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AS50" s="3" t="inlineStr"/>
       <c r="AT50" s="3" t="inlineStr"/>
       <c r="AU50" s="3" t="inlineStr"/>
       <c r="AV50" s="3" t="inlineStr"/>
       <c r="AW50" s="3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.143</t>
         </is>
       </c>
       <c r="AX50" s="3" t="inlineStr"/>
@@ -11207,7 +11203,7 @@
       <c r="BG50" s="3" t="inlineStr"/>
       <c r="BH50" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="BI50" s="3" t="inlineStr">
@@ -11228,11 +11224,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -11242,22 +11238,22 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27 20:00:00-04:00</t>
+          <t>2026-04-27 21:30:00-04:00</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -11267,7 +11263,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -11276,40 +11272,40 @@
         </is>
       </c>
       <c r="L51" s="5" t="n">
-        <v>4.44</v>
+        <v>0.05</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>4.44</v>
+        <v>0.05</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>15.94</v>
+        <v>7.45</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9563</v>
       </c>
       <c r="P51" s="5" t="inlineStr"/>
       <c r="Q51" s="5" t="inlineStr"/>
       <c r="R51" s="5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="S51" s="5" t="n">
-        <v>14.6</v>
+        <v>7</v>
       </c>
       <c r="T51" s="5" t="n">
-        <v>15.2</v>
+        <v>7.9</v>
       </c>
       <c r="U51" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V51" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="V51" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="W51" s="5" t="n">
         <v>5</v>
       </c>
       <c r="X51" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y51" s="5" t="inlineStr">
@@ -11329,92 +11325,88 @@
       </c>
       <c r="AB51" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AC51" s="5" t="inlineStr">
-        <is>
-          <t>VOID_TIER_D</t>
-        </is>
-      </c>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AC51" s="5" t="inlineStr"/>
       <c r="AD51" s="5" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AE51" s="5" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AF51" s="5" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AG51" s="5" t="inlineStr"/>
       <c r="AH51" s="5" t="inlineStr"/>
       <c r="AI51" s="5" t="n">
-        <v>32.73646132795981</v>
+        <v>36.00370291981745</v>
       </c>
       <c r="AJ51" s="5" t="inlineStr"/>
       <c r="AK51" s="5" t="n">
-        <v>-0.5999999999999996</v>
+        <v>-0.9000000000000004</v>
       </c>
       <c r="AL51" s="5" t="inlineStr"/>
       <c r="AM51" s="5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AN51" s="5" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO51" s="5" t="inlineStr">
         <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AP51" s="5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ51" s="5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AR51" s="5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AS51" s="5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AT51" s="5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AU51" s="5" t="inlineStr">
+        <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AP51" s="5" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="AQ51" s="5" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AR51" s="5" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AS51" s="5" t="inlineStr">
+      <c r="AV51" s="5" t="inlineStr">
         <is>
           <t>14.0</t>
         </is>
       </c>
-      <c r="AT51" s="5" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AU51" s="5" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="AV51" s="5" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
       <c r="AW51" s="5" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AX51" s="5" t="inlineStr"/>
@@ -11429,7 +11421,7 @@
       <c r="BG51" s="5" t="inlineStr"/>
       <c r="BH51" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="BI51" s="5" t="inlineStr">
@@ -11454,24 +11446,24 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G-F</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
+          <t>PHX</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
           <t>OKC</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>PHX</t>
-        </is>
-      </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
           <t>2026-04-27 21:30:00-04:00</t>
@@ -11479,7 +11471,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -11489,7 +11481,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -11498,40 +11490,40 @@
         </is>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.05</v>
+        <v>1.16</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>0.05</v>
+        <v>1.16</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>7.45</v>
+        <v>11.34</v>
       </c>
       <c r="O52" s="3" t="n">
-        <v>0.9563</v>
+        <v>0.9506</v>
       </c>
       <c r="P52" s="3" t="inlineStr"/>
       <c r="Q52" s="3" t="inlineStr"/>
       <c r="R52" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="S52" s="3" t="n">
-        <v>7</v>
+        <v>10.6</v>
       </c>
       <c r="T52" s="3" t="n">
-        <v>7.9</v>
+        <v>10.6</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W52" s="3" t="n">
         <v>5</v>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
@@ -11551,88 +11543,68 @@
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr"/>
       <c r="AD52" s="3" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AE52" s="3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AF52" s="3" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AG52" s="3" t="inlineStr"/>
       <c r="AH52" s="3" t="inlineStr"/>
       <c r="AI52" s="3" t="n">
-        <v>36.00370291981745</v>
+        <v>28.98545565233437</v>
       </c>
       <c r="AJ52" s="3" t="inlineStr"/>
       <c r="AK52" s="3" t="n">
-        <v>-0.9000000000000004</v>
+        <v>0</v>
       </c>
       <c r="AL52" s="3" t="inlineStr"/>
       <c r="AM52" s="3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AN52" s="3" t="inlineStr">
         <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO52" s="3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AR52" s="3" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AS52" s="3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT52" s="3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AU52" s="3" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AV52" s="3" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
+      <c r="AR52" s="3" t="inlineStr"/>
+      <c r="AS52" s="3" t="inlineStr"/>
+      <c r="AT52" s="3" t="inlineStr"/>
+      <c r="AU52" s="3" t="inlineStr"/>
+      <c r="AV52" s="3" t="inlineStr"/>
       <c r="AW52" s="3" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AX52" s="3" t="inlineStr"/>
@@ -11668,16 +11640,16 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -11707,7 +11679,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -11716,33 +11688,33 @@
         </is>
       </c>
       <c r="L53" s="5" t="n">
-        <v>1.16</v>
+        <v>4.66</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>1.16</v>
+        <v>4.66</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>11.34</v>
+        <v>18.66</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0.9506</v>
+        <v>0.9439</v>
       </c>
       <c r="P53" s="5" t="inlineStr"/>
       <c r="Q53" s="5" t="inlineStr"/>
       <c r="R53" s="5" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="S53" s="5" t="n">
-        <v>10.6</v>
+        <v>16</v>
       </c>
       <c r="T53" s="5" t="n">
-        <v>10.6</v>
+        <v>18.9</v>
       </c>
       <c r="U53" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V53" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W53" s="5" t="n">
         <v>5</v>
@@ -11772,65 +11744,81 @@
           <t>SECONDARY</t>
         </is>
       </c>
-      <c r="AC53" s="5" t="inlineStr"/>
+      <c r="AC53" s="5" t="inlineStr">
+        <is>
+          <t>VOID_TIER_D</t>
+        </is>
+      </c>
       <c r="AD53" s="5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>18.875</t>
         </is>
       </c>
       <c r="AE53" s="5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AF53" s="5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>18.875</t>
         </is>
       </c>
       <c r="AG53" s="5" t="inlineStr"/>
       <c r="AH53" s="5" t="inlineStr"/>
       <c r="AI53" s="5" t="n">
-        <v>28.98545565233437</v>
+        <v>35.48457834336109</v>
       </c>
       <c r="AJ53" s="5" t="inlineStr"/>
       <c r="AK53" s="5" t="n">
-        <v>0</v>
+        <v>-2.875</v>
       </c>
       <c r="AL53" s="5" t="inlineStr"/>
       <c r="AM53" s="5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AN53" s="5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AO53" s="5" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AP53" s="5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AQ53" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AR53" s="5" t="inlineStr"/>
-      <c r="AS53" s="5" t="inlineStr"/>
-      <c r="AT53" s="5" t="inlineStr"/>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AR53" s="5" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="AS53" s="5" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="AT53" s="5" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
       <c r="AU53" s="5" t="inlineStr"/>
       <c r="AV53" s="5" t="inlineStr"/>
       <c r="AW53" s="5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>18.875</t>
         </is>
       </c>
       <c r="AX53" s="5" t="inlineStr"/>
@@ -12080,31 +12068,31 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>F-C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27 22:30:00-04:00</t>
+          <t>2026-04-27 20:00:00-04:00</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -12119,7 +12107,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -12128,16 +12116,16 @@
         </is>
       </c>
       <c r="L55" s="5" t="n">
-        <v>0.02</v>
+        <v>3.94</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>0.02</v>
+        <v>3.94</v>
       </c>
       <c r="N55" s="5" t="n">
-        <v>17.52</v>
+        <v>15.94</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>0.9628</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="P55" s="5" t="inlineStr"/>
       <c r="Q55" s="5" t="inlineStr"/>
@@ -12145,10 +12133,10 @@
         <v>0.6</v>
       </c>
       <c r="S55" s="5" t="n">
-        <v>16.6</v>
+        <v>14.6</v>
       </c>
       <c r="T55" s="5" t="n">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="U55" s="5" t="n">
         <v>3</v>
@@ -12161,12 +12149,12 @@
       </c>
       <c r="X55" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y55" s="5" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Z55" s="5" t="inlineStr">
@@ -12191,70 +12179,82 @@
       </c>
       <c r="AD55" s="5" t="inlineStr">
         <is>
-          <t>16.143</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AE55" s="5" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AF55" s="5" t="inlineStr">
         <is>
-          <t>16.143</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AG55" s="5" t="inlineStr"/>
       <c r="AH55" s="5" t="inlineStr"/>
       <c r="AI55" s="5" t="n">
-        <v>18.85599624129426</v>
+        <v>32.73646132795981</v>
       </c>
       <c r="AJ55" s="5" t="inlineStr"/>
       <c r="AK55" s="5" t="n">
-        <v>0.4570000000000007</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="AL55" s="5" t="inlineStr"/>
       <c r="AM55" s="5" t="inlineStr">
         <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AN55" s="5" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="AO55" s="5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AP55" s="5" t="inlineStr">
+        <is>
           <t>19.0</t>
         </is>
       </c>
-      <c r="AN55" s="5" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AO55" s="5" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AP55" s="5" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
       <c r="AQ55" s="5" t="inlineStr">
         <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AR55" s="5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AS55" s="5" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AT55" s="5" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="AR55" s="5" t="inlineStr">
+      <c r="AU55" s="5" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="AV55" s="5" t="inlineStr">
         <is>
           <t>17.0</t>
         </is>
       </c>
-      <c r="AS55" s="5" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="AT55" s="5" t="inlineStr"/>
-      <c r="AU55" s="5" t="inlineStr"/>
-      <c r="AV55" s="5" t="inlineStr"/>
       <c r="AW55" s="5" t="inlineStr">
         <is>
-          <t>16.143</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AX55" s="5" t="inlineStr"/>
@@ -12269,7 +12269,7 @@
       <c r="BG55" s="5" t="inlineStr"/>
       <c r="BH55" s="5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="BI55" s="5" t="inlineStr">
@@ -12924,16 +12924,16 @@
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -12972,33 +12972,33 @@
         </is>
       </c>
       <c r="L59" s="5" t="n">
-        <v>5.27</v>
+        <v>0.85</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>5.27</v>
+        <v>0.85</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>23.27</v>
+        <v>7.85</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>0.9368</v>
+        <v>0.9492</v>
       </c>
       <c r="P59" s="5" t="inlineStr"/>
       <c r="Q59" s="5" t="inlineStr"/>
       <c r="R59" s="5" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="S59" s="5" t="n">
-        <v>22.6</v>
+        <v>8.6</v>
       </c>
       <c r="T59" s="5" t="n">
-        <v>20.9</v>
+        <v>7.1</v>
       </c>
       <c r="U59" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V59" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W59" s="5" t="n">
         <v>5</v>
@@ -13025,92 +13025,92 @@
       </c>
       <c r="AB59" s="5" t="inlineStr">
         <is>
-          <t>PRIMARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AC59" s="5" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
         </is>
       </c>
       <c r="AD59" s="5" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AE59" s="5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AF59" s="5" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AG59" s="5" t="inlineStr"/>
       <c r="AH59" s="5" t="inlineStr"/>
       <c r="AI59" s="5" t="n">
-        <v>19.3114220771393</v>
+        <v>64.98744785948917</v>
       </c>
       <c r="AJ59" s="5" t="inlineStr"/>
       <c r="AK59" s="5" t="n">
-        <v>1.700000000000003</v>
+        <v>1.5</v>
       </c>
       <c r="AL59" s="5" t="inlineStr"/>
       <c r="AM59" s="5" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AN59" s="5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AO59" s="5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AP59" s="5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AQ59" s="5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AR59" s="5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS59" s="5" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT59" s="5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AU59" s="5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AV59" s="5" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AW59" s="5" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AX59" s="5" t="inlineStr"/>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -13194,33 +13194,33 @@
         </is>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.85</v>
+        <v>0.05</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>0.85</v>
+        <v>0.05</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>7.85</v>
+        <v>7.45</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>0.9492</v>
+        <v>0.9621</v>
       </c>
       <c r="P60" s="3" t="inlineStr"/>
       <c r="Q60" s="3" t="inlineStr"/>
       <c r="R60" s="3" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="S60" s="3" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="T60" s="3" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="U60" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V60" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W60" s="3" t="n">
         <v>5</v>
@@ -13250,89 +13250,69 @@
           <t>SUPPORT</t>
         </is>
       </c>
-      <c r="AC60" s="3" t="inlineStr">
-        <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+      <c r="AC60" s="3" t="inlineStr"/>
       <c r="AD60" s="3" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.333</t>
         </is>
       </c>
       <c r="AE60" s="3" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AF60" s="3" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.333</t>
         </is>
       </c>
       <c r="AG60" s="3" t="inlineStr"/>
       <c r="AH60" s="3" t="inlineStr"/>
       <c r="AI60" s="3" t="n">
-        <v>64.98744785948917</v>
+        <v>28.02006364985899</v>
       </c>
       <c r="AJ60" s="3" t="inlineStr"/>
       <c r="AK60" s="3" t="n">
-        <v>1.5</v>
+        <v>-0.7330000000000005</v>
       </c>
       <c r="AL60" s="3" t="inlineStr"/>
       <c r="AM60" s="3" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AO60" s="3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AP60" s="3" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AQ60" s="3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AR60" s="3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS60" s="3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT60" s="3" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU60" s="3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AV60" s="3" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
+      <c r="AS60" s="3" t="inlineStr"/>
+      <c r="AT60" s="3" t="inlineStr"/>
+      <c r="AU60" s="3" t="inlineStr"/>
+      <c r="AV60" s="3" t="inlineStr"/>
       <c r="AW60" s="3" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.333</t>
         </is>
       </c>
       <c r="AX60" s="3" t="inlineStr"/>
@@ -13368,16 +13348,16 @@
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -13407,7 +13387,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -13416,33 +13396,33 @@
         </is>
       </c>
       <c r="L61" s="5" t="n">
-        <v>0.05</v>
+        <v>4.77</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>0.05</v>
+        <v>4.77</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>7.45</v>
+        <v>23.27</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>0.9621</v>
+        <v>0.9415</v>
       </c>
       <c r="P61" s="5" t="inlineStr"/>
       <c r="Q61" s="5" t="inlineStr"/>
       <c r="R61" s="5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S61" s="5" t="n">
-        <v>6.6</v>
+        <v>22.6</v>
       </c>
       <c r="T61" s="5" t="n">
-        <v>7.3</v>
+        <v>20.9</v>
       </c>
       <c r="U61" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V61" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W61" s="5" t="n">
         <v>5</v>
@@ -13469,72 +13449,92 @@
       </c>
       <c r="AB61" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="AC61" s="5" t="inlineStr"/>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="AC61" s="5" t="inlineStr">
+        <is>
+          <t>VOID_TIER_D</t>
+        </is>
+      </c>
       <c r="AD61" s="5" t="inlineStr">
         <is>
-          <t>7.333</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AE61" s="5" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="AF61" s="5" t="inlineStr">
         <is>
-          <t>7.333</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AG61" s="5" t="inlineStr"/>
       <c r="AH61" s="5" t="inlineStr"/>
       <c r="AI61" s="5" t="n">
-        <v>28.02006364985899</v>
+        <v>19.3114220771393</v>
       </c>
       <c r="AJ61" s="5" t="inlineStr"/>
       <c r="AK61" s="5" t="n">
-        <v>-0.7330000000000005</v>
+        <v>1.700000000000003</v>
       </c>
       <c r="AL61" s="5" t="inlineStr"/>
       <c r="AM61" s="5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AN61" s="5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AO61" s="5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AP61" s="5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AQ61" s="5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AR61" s="5" t="inlineStr">
         <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AS61" s="5" t="inlineStr"/>
-      <c r="AT61" s="5" t="inlineStr"/>
-      <c r="AU61" s="5" t="inlineStr"/>
-      <c r="AV61" s="5" t="inlineStr"/>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AS61" s="5" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="AT61" s="5" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AU61" s="5" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="AV61" s="5" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
       <c r="AW61" s="5" t="inlineStr">
         <is>
-          <t>7.333</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AX61" s="5" t="inlineStr"/>
@@ -15252,12 +15252,12 @@
       <c r="B71" s="5" t="inlineStr"/>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
@@ -15396,12 +15396,12 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -15575,7 +15575,7 @@
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -15719,7 +15719,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
@@ -19967,7 +19967,7 @@
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
@@ -20220,24 +20220,24 @@
       <c r="B105" s="5" t="inlineStr"/>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
           <t>DEN</t>
         </is>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
           <t>2026-04-27 22:30:00-04:00</t>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Fantasy Score</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
@@ -20269,7 +20269,7 @@
         <v>0</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>0.9658</v>
+        <v>0.9628</v>
       </c>
       <c r="P105" s="5" t="inlineStr"/>
       <c r="Q105" s="5" t="inlineStr"/>
@@ -20281,12 +20281,12 @@
       <c r="W105" s="5" t="inlineStr"/>
       <c r="X105" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y105" s="5" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z105" s="5" t="inlineStr">
@@ -20364,24 +20364,24 @@
       <c r="B106" s="3" t="inlineStr"/>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
           <t>2026-04-27 22:30:00-04:00</t>
@@ -20389,7 +20389,7 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>Fantasy Score</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
@@ -20413,7 +20413,7 @@
         <v>0</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.9628</v>
+        <v>0.9658</v>
       </c>
       <c r="P106" s="3" t="inlineStr"/>
       <c r="Q106" s="3" t="inlineStr"/>
@@ -20425,12 +20425,12 @@
       <c r="W106" s="3" t="inlineStr"/>
       <c r="X106" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Y106" s="3" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Z106" s="3" t="inlineStr">
@@ -21084,22 +21084,22 @@
       <c r="B111" s="5" t="inlineStr"/>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Tim Hardaway</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
           <t>DEN</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>MIN</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
@@ -21133,7 +21133,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="5" t="n">
-        <v>0.9626</v>
+        <v>0.9628</v>
       </c>
       <c r="P111" s="5" t="inlineStr"/>
       <c r="Q111" s="5" t="inlineStr"/>
@@ -21145,12 +21145,12 @@
       <c r="W111" s="5" t="inlineStr"/>
       <c r="X111" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y111" s="5" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z111" s="5" t="inlineStr">
@@ -21228,24 +21228,24 @@
       <c r="B112" s="3" t="inlineStr"/>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Tim Hardaway</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G-F</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
           <t>2026-04-27 22:30:00-04:00</t>
@@ -21263,7 +21263,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
@@ -21277,7 +21277,7 @@
         <v>0</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0.9628</v>
+        <v>0.9626</v>
       </c>
       <c r="P112" s="3" t="inlineStr"/>
       <c r="Q112" s="3" t="inlineStr"/>
@@ -21289,12 +21289,12 @@
       <c r="W112" s="3" t="inlineStr"/>
       <c r="X112" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Y112" s="3" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Z112" s="3" t="inlineStr">
@@ -24953,7 +24953,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -25998,32 +25998,32 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27 21:30:00-04:00</t>
+          <t>2026-04-27 22:30:00-04:00</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -26042,16 +26042,16 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>4.34</v>
+        <v>1.44</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>4.34</v>
+        <v>1.44</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>9.84</v>
+        <v>6.94</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.951</v>
+        <v>0.9587</v>
       </c>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr"/>
@@ -26059,10 +26059,10 @@
         <v>0.6</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>3</v>
@@ -26075,12 +26075,12 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -26105,62 +26105,70 @@
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>7.286</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>7.286</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr"/>
       <c r="AH4" s="3" t="inlineStr"/>
       <c r="AI4" s="3" t="n">
-        <v>47.82608695652173</v>
+        <v>36.47269654458486</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="n">
-        <v>0</v>
+        <v>-0.6859999999999999</v>
       </c>
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="AT4" s="3" t="inlineStr"/>
       <c r="AU4" s="3" t="inlineStr"/>
       <c r="AV4" s="3" t="inlineStr"/>
       <c r="AW4" s="3" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>7.286</t>
         </is>
       </c>
       <c r="AX4" s="3" t="inlineStr"/>
@@ -26196,36 +26204,36 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Jordan Goodwin</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27 22:30:00-04:00</t>
+          <t>2026-04-27 21:30:00-04:00</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -26235,7 +26243,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -26244,45 +26252,45 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>1.44</v>
+        <v>4.95</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>1.44</v>
+        <v>4.95</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>6.94</v>
+        <v>11.45</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.9587</v>
+        <v>0.9585</v>
       </c>
       <c r="P5" s="5" t="inlineStr"/>
       <c r="Q5" s="5" t="inlineStr"/>
       <c r="R5" s="5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>6.6</v>
+        <v>11.4</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>7.3</v>
+        <v>10</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W5" s="5" t="n">
         <v>5</v>
       </c>
       <c r="X5" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y5" s="5" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Z5" s="5" t="inlineStr">
@@ -26297,7 +26305,7 @@
       </c>
       <c r="AB5" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AC5" s="5" t="inlineStr">
@@ -26307,62 +26315,62 @@
       </c>
       <c r="AD5" s="5" t="inlineStr">
         <is>
-          <t>7.286</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AE5" s="5" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AF5" s="5" t="inlineStr">
         <is>
-          <t>7.286</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG5" s="5" t="inlineStr"/>
       <c r="AH5" s="5" t="inlineStr"/>
       <c r="AI5" s="5" t="n">
-        <v>36.47269654458486</v>
+        <v>38.54496446637727</v>
       </c>
       <c r="AJ5" s="5" t="inlineStr"/>
       <c r="AK5" s="5" t="n">
-        <v>-0.6859999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="AL5" s="5" t="inlineStr"/>
       <c r="AM5" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AN5" s="5" t="inlineStr">
         <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="AO5" s="5" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AP5" s="5" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AQ5" s="5" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AR5" s="5" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AS5" s="5" t="inlineStr">
+        <is>
           <t>5.0</t>
-        </is>
-      </c>
-      <c r="AO5" s="5" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AP5" s="5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ5" s="5" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AR5" s="5" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AS5" s="5" t="inlineStr">
-        <is>
-          <t>8.0</t>
         </is>
       </c>
       <c r="AT5" s="5" t="inlineStr"/>
@@ -26370,7 +26378,7 @@
       <c r="AV5" s="5" t="inlineStr"/>
       <c r="AW5" s="5" t="inlineStr">
         <is>
-          <t>7.286</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AX5" s="5" t="inlineStr"/>
@@ -26410,7 +26418,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Jordan Goodwin</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -26420,22 +26428,22 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27 21:30:00-04:00</t>
+          <t>2026-04-27 22:30:00-04:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -26445,7 +26453,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -26454,45 +26462,45 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.95</v>
+        <v>2.35</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>4.95</v>
+        <v>2.35</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>11.45</v>
+        <v>7.85</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.9585</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr"/>
       <c r="R6" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -26507,7 +26515,7 @@
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
@@ -26517,70 +26525,82 @@
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AG6" s="3" t="inlineStr"/>
       <c r="AH6" s="3" t="inlineStr"/>
       <c r="AI6" s="3" t="n">
-        <v>38.54496446637727</v>
+        <v>40.19561849622249</v>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
       <c r="AK6" s="3" t="n">
-        <v>1.4</v>
+        <v>1.100000000000001</v>
       </c>
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr">
         <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="AO6" s="3" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AQ6" s="3" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AR6" s="3" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="AW6" s="3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AX6" s="3" t="inlineStr"/>
@@ -26616,16 +26636,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -26664,16 +26684,16 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>7.85</v>
+        <v>7.79</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9394</v>
       </c>
       <c r="P7" s="5" t="inlineStr"/>
       <c r="Q7" s="5" t="inlineStr"/>
@@ -26681,10 +26701,10 @@
         <v>0.8</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>4</v>
@@ -26727,82 +26747,78 @@
       </c>
       <c r="AD7" s="5" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.778</t>
         </is>
       </c>
       <c r="AE7" s="5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AF7" s="5" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.778</t>
         </is>
       </c>
       <c r="AG7" s="5" t="inlineStr"/>
       <c r="AH7" s="5" t="inlineStr"/>
       <c r="AI7" s="5" t="n">
-        <v>40.19561849622249</v>
+        <v>42.7617987059879</v>
       </c>
       <c r="AJ7" s="5" t="inlineStr"/>
       <c r="AK7" s="5" t="n">
-        <v>1.100000000000001</v>
+        <v>0.02200000000000024</v>
       </c>
       <c r="AL7" s="5" t="inlineStr"/>
       <c r="AM7" s="5" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AN7" s="5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AO7" s="5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AP7" s="5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AQ7" s="5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AR7" s="5" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AS7" s="5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT7" s="5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AU7" s="5" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AN7" s="5" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="AO7" s="5" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AP7" s="5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AQ7" s="5" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AR7" s="5" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AS7" s="5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT7" s="5" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU7" s="5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AV7" s="5" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
+      <c r="AV7" s="5" t="inlineStr"/>
       <c r="AW7" s="5" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.778</t>
         </is>
       </c>
       <c r="AX7" s="5" t="inlineStr"/>
@@ -26838,31 +26854,31 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27 22:30:00-04:00</t>
+          <t>2026-04-27 20:00:00-04:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -26877,7 +26893,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -26886,45 +26902,45 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>2.29</v>
+        <v>1.14</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2.29</v>
+        <v>1.14</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>7.79</v>
+        <v>3.36</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.9394</v>
+        <v>0.9606</v>
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>7.8</v>
+        <v>3</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
       <c r="U8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
         <v>4</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>5</v>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
@@ -26942,85 +26958,73 @@
           <t>SUPPORT</t>
         </is>
       </c>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+      <c r="AC8" s="3" t="inlineStr"/>
       <c r="AD8" s="3" t="inlineStr">
         <is>
-          <t>7.778</t>
+          <t>3.714</t>
         </is>
       </c>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>7.778</t>
+          <t>3.714</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr"/>
       <c r="AH8" s="3" t="inlineStr"/>
       <c r="AI8" s="3" t="n">
-        <v>42.7617987059879</v>
+        <v>63.89710663783134</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="n">
-        <v>0.02200000000000024</v>
+        <v>-0.714</v>
       </c>
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN8" s="3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AQ8" s="3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="3" t="inlineStr"/>
       <c r="AV8" s="3" t="inlineStr"/>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>7.778</t>
+          <t>3.714</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr"/>
@@ -27035,7 +27039,7 @@
       <c r="BG8" s="3" t="inlineStr"/>
       <c r="BH8" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="BI8" s="3" t="inlineStr">
@@ -27056,36 +27060,36 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27 20:00:00-04:00</t>
+          <t>2026-04-27 22:30:00-04:00</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -27095,7 +27099,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -27104,45 +27108,45 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>1.14</v>
+        <v>3.82</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>1.14</v>
+        <v>3.82</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>3.36</v>
+        <v>16.32</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.9606</v>
+        <v>0.9423</v>
       </c>
       <c r="P9" s="5" t="inlineStr"/>
       <c r="Q9" s="5" t="inlineStr"/>
       <c r="R9" s="5" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="S9" s="5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="T9" s="5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U9" s="5" t="n">
+      <c r="V9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="V9" s="5" t="n">
+      <c r="W9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W9" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="X9" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y9" s="5" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z9" s="5" t="inlineStr">
@@ -27157,76 +27161,64 @@
       </c>
       <c r="AB9" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AC9" s="5" t="inlineStr"/>
       <c r="AD9" s="5" t="inlineStr">
         <is>
-          <t>3.714</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="AE9" s="5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="AF9" s="5" t="inlineStr">
         <is>
-          <t>3.714</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="AG9" s="5" t="inlineStr"/>
       <c r="AH9" s="5" t="inlineStr"/>
       <c r="AI9" s="5" t="n">
-        <v>63.89710663783134</v>
+        <v>12.59204220962067</v>
       </c>
       <c r="AJ9" s="5" t="inlineStr"/>
       <c r="AK9" s="5" t="n">
-        <v>-0.714</v>
+        <v>0</v>
       </c>
       <c r="AL9" s="5" t="inlineStr"/>
       <c r="AM9" s="5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AN9" s="5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AO9" s="5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AP9" s="5" t="inlineStr">
         <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AQ9" s="5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AR9" s="5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS9" s="5" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AQ9" s="5" t="inlineStr"/>
+      <c r="AR9" s="5" t="inlineStr"/>
+      <c r="AS9" s="5" t="inlineStr"/>
       <c r="AT9" s="5" t="inlineStr"/>
       <c r="AU9" s="5" t="inlineStr"/>
       <c r="AV9" s="5" t="inlineStr"/>
       <c r="AW9" s="5" t="inlineStr">
         <is>
-          <t>3.714</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="AX9" s="5" t="inlineStr"/>
@@ -27241,7 +27233,7 @@
       <c r="BG9" s="5" t="inlineStr"/>
       <c r="BH9" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="BI9" s="5" t="inlineStr">
@@ -27262,28 +27254,28 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
           <t>2026-04-27 22:30:00-04:00</t>
@@ -27301,7 +27293,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -27310,45 +27302,45 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>3.82</v>
+        <v>4.43</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>3.82</v>
+        <v>4.43</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>16.32</v>
+        <v>13.43</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.9423</v>
+        <v>0.951</v>
       </c>
       <c r="P10" s="3" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr"/>
       <c r="R10" s="3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>15.2</v>
+        <v>12.6</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>15.2</v>
+        <v>12.5</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -27366,61 +27358,73 @@
           <t>SECONDARY</t>
         </is>
       </c>
-      <c r="AC10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>VOID_LOW_MINUTES_NON_A</t>
+        </is>
+      </c>
       <c r="AD10" s="3" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr"/>
       <c r="AH10" s="3" t="inlineStr"/>
       <c r="AI10" s="3" t="n">
-        <v>12.59204220962067</v>
+        <v>26.43230346879868</v>
       </c>
       <c r="AJ10" s="3" t="inlineStr"/>
       <c r="AK10" s="3" t="n">
-        <v>0</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="AL10" s="3" t="inlineStr"/>
       <c r="AM10" s="3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AN10" s="3" t="inlineStr">
         <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="AO10" s="3" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
       <c r="AS10" s="3" t="inlineStr"/>
       <c r="AT10" s="3" t="inlineStr"/>
       <c r="AU10" s="3" t="inlineStr"/>
       <c r="AV10" s="3" t="inlineStr"/>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr"/>
@@ -27456,31 +27460,31 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Luguentz Dort</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27 22:30:00-04:00</t>
+          <t>2026-04-27 21:30:00-04:00</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -27495,7 +27499,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -27504,45 +27508,45 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>4.43</v>
+        <v>3.84</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>4.43</v>
+        <v>3.84</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>13.43</v>
+        <v>9.84</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>0.951</v>
+        <v>0.9496</v>
       </c>
       <c r="P11" s="5" t="inlineStr"/>
       <c r="Q11" s="5" t="inlineStr"/>
       <c r="R11" s="5" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>12.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W11" s="5" t="n">
         <v>5</v>
       </c>
       <c r="X11" s="5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y11" s="5" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Z11" s="5" t="inlineStr">
@@ -27557,7 +27561,7 @@
       </c>
       <c r="AB11" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AC11" s="5" t="inlineStr">
@@ -27567,66 +27571,62 @@
       </c>
       <c r="AD11" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AE11" s="5" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AF11" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AG11" s="5" t="inlineStr"/>
       <c r="AH11" s="5" t="inlineStr"/>
       <c r="AI11" s="5" t="n">
-        <v>26.43230346879868</v>
+        <v>47.82608695652173</v>
       </c>
       <c r="AJ11" s="5" t="inlineStr"/>
       <c r="AK11" s="5" t="n">
-        <v>0.09999999999999964</v>
+        <v>0</v>
       </c>
       <c r="AL11" s="5" t="inlineStr"/>
       <c r="AM11" s="5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AN11" s="5" t="inlineStr">
         <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AO11" s="5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AP11" s="5" t="inlineStr">
+        <is>
           <t>14.0</t>
         </is>
       </c>
-      <c r="AO11" s="5" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AP11" s="5" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="AQ11" s="5" t="inlineStr">
         <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AR11" s="5" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AR11" s="5" t="inlineStr"/>
       <c r="AS11" s="5" t="inlineStr"/>
       <c r="AT11" s="5" t="inlineStr"/>
       <c r="AU11" s="5" t="inlineStr"/>
       <c r="AV11" s="5" t="inlineStr"/>
       <c r="AW11" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AX11" s="5" t="inlineStr"/>
@@ -27860,24 +27860,24 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>ORL</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
           <t>2026-04-27 20:00:00-04:00</t>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -27895,7 +27895,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -27904,45 +27904,45 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>1.9</v>
+        <v>4.89</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>1.9</v>
+        <v>4.89</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>8.1</v>
+        <v>19.39</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>0.9506</v>
+        <v>0.9431</v>
       </c>
       <c r="P13" s="5" t="inlineStr"/>
       <c r="Q13" s="5" t="inlineStr"/>
       <c r="R13" s="5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>7.4</v>
+        <v>17.8</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>8.800000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="U13" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W13" s="5" t="n">
         <v>5</v>
       </c>
       <c r="X13" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y13" s="5" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z13" s="5" t="inlineStr">
@@ -27957,88 +27957,84 @@
       </c>
       <c r="AB13" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AC13" s="5" t="inlineStr"/>
       <c r="AD13" s="5" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>18.444</t>
         </is>
       </c>
       <c r="AE13" s="5" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AF13" s="5" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>18.444</t>
         </is>
       </c>
       <c r="AG13" s="5" t="inlineStr"/>
       <c r="AH13" s="5" t="inlineStr"/>
       <c r="AI13" s="5" t="n">
-        <v>58.12141751156554</v>
+        <v>25.57227141782064</v>
       </c>
       <c r="AJ13" s="5" t="inlineStr"/>
       <c r="AK13" s="5" t="n">
-        <v>-1.4</v>
+        <v>-0.6439999999999984</v>
       </c>
       <c r="AL13" s="5" t="inlineStr"/>
       <c r="AM13" s="5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AN13" s="5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AO13" s="5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AP13" s="5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AQ13" s="5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AR13" s="5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AS13" s="5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AT13" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AU13" s="5" t="inlineStr">
         <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AV13" s="5" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AV13" s="5" t="inlineStr"/>
       <c r="AW13" s="5" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>18.444</t>
         </is>
       </c>
       <c r="AX13" s="5" t="inlineStr"/>
@@ -28078,24 +28074,24 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>ORL</t>
-        </is>
-      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t>2026-04-27 20:00:00-04:00</t>
@@ -28103,7 +28099,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -28113,7 +28109,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -28122,45 +28118,45 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>4.89</v>
+        <v>1.9</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>4.89</v>
+        <v>1.9</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>19.39</v>
+        <v>8.1</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.9431</v>
+        <v>0.9506</v>
       </c>
       <c r="P14" s="3" t="inlineStr"/>
       <c r="Q14" s="3" t="inlineStr"/>
       <c r="R14" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S14" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="V14" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>5</v>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -28175,84 +28171,88 @@
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr"/>
       <c r="AD14" s="3" t="inlineStr">
         <is>
-          <t>18.444</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>18.444</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr"/>
       <c r="AH14" s="3" t="inlineStr"/>
       <c r="AI14" s="3" t="n">
-        <v>25.57227141782064</v>
+        <v>58.12141751156554</v>
       </c>
       <c r="AJ14" s="3" t="inlineStr"/>
       <c r="AK14" s="3" t="n">
-        <v>-0.6439999999999984</v>
+        <v>-1.4</v>
       </c>
       <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
       <c r="AU14" s="3" t="inlineStr">
         <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="AV14" s="3" t="inlineStr"/>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>18.444</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr"/>
@@ -33323,7 +33323,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -33348,7 +33348,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -33358,7 +33358,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -33367,36 +33367,36 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>5.16</v>
+        <v>0.85</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>5.16</v>
+        <v>0.85</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>18.66</v>
+        <v>4.85</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.9368</v>
+        <v>0.9555</v>
       </c>
       <c r="P17" s="5" t="inlineStr"/>
       <c r="Q17" s="5" t="inlineStr"/>
       <c r="R17" s="5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>18.9</v>
+        <v>5.9</v>
       </c>
       <c r="U17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V17" s="5" t="n">
         <v>2</v>
       </c>
       <c r="W17" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X17" s="5" t="inlineStr">
         <is>
@@ -33420,84 +33420,92 @@
       </c>
       <c r="AB17" s="5" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AC17" s="5" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
         </is>
       </c>
       <c r="AD17" s="5" t="inlineStr">
         <is>
-          <t>18.875</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AE17" s="5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AF17" s="5" t="inlineStr">
         <is>
-          <t>18.875</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AG17" s="5" t="inlineStr"/>
       <c r="AH17" s="5" t="inlineStr"/>
       <c r="AI17" s="5" t="n">
-        <v>35.48457834336109</v>
+        <v>43.83904120805953</v>
       </c>
       <c r="AJ17" s="5" t="inlineStr"/>
       <c r="AK17" s="5" t="n">
-        <v>-2.875</v>
+        <v>-2.100000000000001</v>
       </c>
       <c r="AL17" s="5" t="inlineStr"/>
       <c r="AM17" s="5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AN17" s="5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AO17" s="5" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP17" s="5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ17" s="5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AR17" s="5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AS17" s="5" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AT17" s="5" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AP17" s="5" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AQ17" s="5" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AR17" s="5" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AS17" s="5" t="inlineStr">
-        <is>
-          <t>26.0</t>
-        </is>
-      </c>
-      <c r="AT17" s="5" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="AU17" s="5" t="inlineStr"/>
-      <c r="AV17" s="5" t="inlineStr"/>
+      <c r="AU17" s="5" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AV17" s="5" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="AW17" s="5" t="inlineStr">
         <is>
-          <t>18.875</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AX17" s="5" t="inlineStr"/>
@@ -33533,36 +33541,36 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>PHX</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27 21:30:00-04:00</t>
+          <t>2026-04-27 20:00:00-04:00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -33572,7 +33580,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -33581,45 +33589,45 @@
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.85</v>
+        <v>1.52</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.85</v>
+        <v>1.52</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>4.85</v>
+        <v>14.02</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.9555</v>
+        <v>0.9532</v>
       </c>
       <c r="P18" s="3" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>3.8</v>
+        <v>13.2</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -33634,7 +33642,7 @@
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
@@ -33644,82 +33652,66 @@
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr"/>
       <c r="AH18" s="3" t="inlineStr"/>
       <c r="AI18" s="3" t="n">
-        <v>43.83904120805953</v>
+        <v>18.31135494498167</v>
       </c>
       <c r="AJ18" s="3" t="inlineStr"/>
       <c r="AK18" s="3" t="n">
-        <v>-2.100000000000001</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="AL18" s="3" t="inlineStr"/>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr"/>
+      <c r="AT18" s="3" t="inlineStr"/>
+      <c r="AU18" s="3" t="inlineStr"/>
+      <c r="AV18" s="3" t="inlineStr"/>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr"/>
@@ -33734,7 +33726,7 @@
       <c r="BG18" s="3" t="inlineStr"/>
       <c r="BH18" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="BI18" s="3" t="inlineStr">
@@ -33755,31 +33747,31 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F-C</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27 20:00:00-04:00</t>
+          <t>2026-04-27 22:30:00-04:00</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -33794,7 +33786,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -33803,16 +33795,16 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>1.52</v>
+        <v>0.52</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>1.52</v>
+        <v>0.52</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>14.02</v>
+        <v>17.52</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.9532</v>
+        <v>0.951</v>
       </c>
       <c r="P19" s="5" t="inlineStr"/>
       <c r="Q19" s="5" t="inlineStr"/>
@@ -33820,10 +33812,10 @@
         <v>0.6</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>13.2</v>
+        <v>16.6</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="U19" s="5" t="n">
         <v>3</v>
@@ -33836,7 +33828,7 @@
       </c>
       <c r="X19" s="5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y19" s="5" t="inlineStr">
@@ -33861,71 +33853,75 @@
       </c>
       <c r="AC19" s="5" t="inlineStr">
         <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
+          <t>VOID_TIER_D</t>
         </is>
       </c>
       <c r="AD19" s="5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.143</t>
         </is>
       </c>
       <c r="AE19" s="5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AF19" s="5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.143</t>
         </is>
       </c>
       <c r="AG19" s="5" t="inlineStr"/>
       <c r="AH19" s="5" t="inlineStr"/>
       <c r="AI19" s="5" t="n">
-        <v>18.31135494498167</v>
+        <v>18.85599624129426</v>
       </c>
       <c r="AJ19" s="5" t="inlineStr"/>
       <c r="AK19" s="5" t="n">
-        <v>0.1999999999999993</v>
+        <v>0.4570000000000007</v>
       </c>
       <c r="AL19" s="5" t="inlineStr"/>
       <c r="AM19" s="5" t="inlineStr">
         <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AN19" s="5" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AO19" s="5" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AP19" s="5" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AQ19" s="5" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="AR19" s="5" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AS19" s="5" t="inlineStr">
+        <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="AN19" s="5" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AO19" s="5" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AP19" s="5" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="AQ19" s="5" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AR19" s="5" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AS19" s="5" t="inlineStr"/>
       <c r="AT19" s="5" t="inlineStr"/>
       <c r="AU19" s="5" t="inlineStr"/>
       <c r="AV19" s="5" t="inlineStr"/>
       <c r="AW19" s="5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.143</t>
         </is>
       </c>
       <c r="AX19" s="5" t="inlineStr"/>
@@ -33940,7 +33936,7 @@
       <c r="BG19" s="5" t="inlineStr"/>
       <c r="BH19" s="5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="BI19" s="5" t="inlineStr">
@@ -33961,11 +33957,11 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -33975,22 +33971,22 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHX</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27 20:00:00-04:00</t>
+          <t>2026-04-27 21:30:00-04:00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -34000,7 +33996,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -34009,40 +34005,40 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>4.44</v>
+        <v>0.05</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>4.44</v>
+        <v>0.05</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>15.94</v>
+        <v>7.45</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9563</v>
       </c>
       <c r="P20" s="3" t="inlineStr"/>
       <c r="Q20" s="3" t="inlineStr"/>
       <c r="R20" s="3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>14.6</v>
+        <v>7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>15.2</v>
+        <v>7.9</v>
       </c>
       <c r="U20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>5</v>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -34062,92 +34058,88 @@
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="AC20" s="3" t="inlineStr">
-        <is>
-          <t>VOID_TIER_D</t>
-        </is>
-      </c>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr"/>
       <c r="AD20" s="3" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr"/>
       <c r="AH20" s="3" t="inlineStr"/>
       <c r="AI20" s="3" t="n">
-        <v>32.73646132795981</v>
+        <v>36.00370291981745</v>
       </c>
       <c r="AJ20" s="3" t="inlineStr"/>
       <c r="AK20" s="3" t="n">
-        <v>-0.5999999999999996</v>
+        <v>-0.9000000000000004</v>
       </c>
       <c r="AL20" s="3" t="inlineStr"/>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="AQ20" s="3" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AR20" s="3" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AS20" s="3" t="inlineStr">
+      <c r="AV20" s="3" t="inlineStr">
         <is>
           <t>14.0</t>
         </is>
       </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr"/>
@@ -34162,7 +34154,7 @@
       <c r="BG20" s="3" t="inlineStr"/>
       <c r="BH20" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="BI20" s="3" t="inlineStr">
@@ -34187,24 +34179,24 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G-F</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>PHX</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>OKC</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>PHX</t>
-        </is>
-      </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
           <t>2026-04-27 21:30:00-04:00</t>
@@ -34212,7 +34204,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -34222,7 +34214,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -34231,40 +34223,40 @@
         </is>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.05</v>
+        <v>1.16</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0.05</v>
+        <v>1.16</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>7.45</v>
+        <v>11.34</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.9563</v>
+        <v>0.9506</v>
       </c>
       <c r="P21" s="5" t="inlineStr"/>
       <c r="Q21" s="5" t="inlineStr"/>
       <c r="R21" s="5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>7</v>
+        <v>10.6</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>7.9</v>
+        <v>10.6</v>
       </c>
       <c r="U21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V21" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W21" s="5" t="n">
         <v>5</v>
       </c>
       <c r="X21" s="5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y21" s="5" t="inlineStr">
@@ -34284,88 +34276,68 @@
       </c>
       <c r="AB21" s="5" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
+          <t>SECONDARY</t>
         </is>
       </c>
       <c r="AC21" s="5" t="inlineStr"/>
       <c r="AD21" s="5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AE21" s="5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AF21" s="5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AG21" s="5" t="inlineStr"/>
       <c r="AH21" s="5" t="inlineStr"/>
       <c r="AI21" s="5" t="n">
-        <v>36.00370291981745</v>
+        <v>28.98545565233437</v>
       </c>
       <c r="AJ21" s="5" t="inlineStr"/>
       <c r="AK21" s="5" t="n">
-        <v>-0.9000000000000004</v>
+        <v>0</v>
       </c>
       <c r="AL21" s="5" t="inlineStr"/>
       <c r="AM21" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AN21" s="5" t="inlineStr">
         <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AO21" s="5" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AP21" s="5" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO21" s="5" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AP21" s="5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="AQ21" s="5" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AR21" s="5" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AS21" s="5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT21" s="5" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AU21" s="5" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AV21" s="5" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
+      <c r="AR21" s="5" t="inlineStr"/>
+      <c r="AS21" s="5" t="inlineStr"/>
+      <c r="AT21" s="5" t="inlineStr"/>
+      <c r="AU21" s="5" t="inlineStr"/>
+      <c r="AV21" s="5" t="inlineStr"/>
       <c r="AW21" s="5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AX21" s="5" t="inlineStr"/>
@@ -34401,16 +34373,16 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -34440,7 +34412,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -34449,33 +34421,33 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>1.16</v>
+        <v>4.66</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>1.16</v>
+        <v>4.66</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.34</v>
+        <v>18.66</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.9506</v>
+        <v>0.9439</v>
       </c>
       <c r="P22" s="3" t="inlineStr"/>
       <c r="Q22" s="3" t="inlineStr"/>
       <c r="R22" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>10.6</v>
+        <v>16</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>10.6</v>
+        <v>18.9</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>5</v>
@@ -34505,65 +34477,81 @@
           <t>SECONDARY</t>
         </is>
       </c>
-      <c r="AC22" s="3" t="inlineStr"/>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>VOID_TIER_D</t>
+        </is>
+      </c>
       <c r="AD22" s="3" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>18.875</t>
         </is>
       </c>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>18.875</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr"/>
       <c r="AH22" s="3" t="inlineStr"/>
       <c r="AI22" s="3" t="n">
-        <v>28.98545565233437</v>
+        <v>35.48457834336109</v>
       </c>
       <c r="AJ22" s="3" t="inlineStr"/>
       <c r="AK22" s="3" t="n">
-        <v>0</v>
+        <v>-2.875</v>
       </c>
       <c r="AL22" s="3" t="inlineStr"/>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr"/>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
       <c r="AU22" s="3" t="inlineStr"/>
       <c r="AV22" s="3" t="inlineStr"/>
       <c r="AW22" s="3" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>18.875</t>
         </is>
       </c>
       <c r="AX22" s="3" t="inlineStr"/>
@@ -34813,31 +34801,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>F-C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27 22:30:00-04:00</t>
+          <t>2026-04-27 20:00:00-04:00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -34852,7 +34840,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -34861,16 +34849,16 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.02</v>
+        <v>3.94</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>0.02</v>
+        <v>3.94</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>17.52</v>
+        <v>15.94</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.9628</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="P24" s="3" t="inlineStr"/>
       <c r="Q24" s="3" t="inlineStr"/>
@@ -34878,10 +34866,10 @@
         <v>0.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>16.6</v>
+        <v>14.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>3</v>
@@ -34894,12 +34882,12 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -34924,70 +34912,82 @@
       </c>
       <c r="AD24" s="3" t="inlineStr">
         <is>
-          <t>16.143</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>16.143</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr"/>
       <c r="AH24" s="3" t="inlineStr"/>
       <c r="AI24" s="3" t="n">
-        <v>18.85599624129426</v>
+        <v>32.73646132795981</v>
       </c>
       <c r="AJ24" s="3" t="inlineStr"/>
       <c r="AK24" s="3" t="n">
-        <v>0.4570000000000007</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="AL24" s="3" t="inlineStr"/>
       <c r="AM24" s="3" t="inlineStr">
         <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
           <t>19.0</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AO24" s="3" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="AR24" s="3" t="inlineStr">
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
         <is>
           <t>17.0</t>
         </is>
       </c>
-      <c r="AS24" s="3" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="AT24" s="3" t="inlineStr"/>
-      <c r="AU24" s="3" t="inlineStr"/>
-      <c r="AV24" s="3" t="inlineStr"/>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>16.143</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr"/>
@@ -35002,7 +35002,7 @@
       <c r="BG24" s="3" t="inlineStr"/>
       <c r="BH24" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="BI24" s="3" t="inlineStr">
@@ -35657,16 +35657,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -35686,7 +35686,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Pts+Rebs+Asts</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -35696,7 +35696,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -35705,33 +35705,33 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>5.27</v>
+        <v>0.85</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>5.27</v>
+        <v>0.85</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>23.27</v>
+        <v>7.85</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.9368</v>
+        <v>0.9492</v>
       </c>
       <c r="P28" s="3" t="inlineStr"/>
       <c r="Q28" s="3" t="inlineStr"/>
       <c r="R28" s="3" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>22.6</v>
+        <v>8.6</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>20.9</v>
+        <v>7.1</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>5</v>
@@ -35758,92 +35758,92 @@
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>PRIMARY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>VOID_TIER_D</t>
+          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
         </is>
       </c>
       <c r="AD28" s="3" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr"/>
       <c r="AH28" s="3" t="inlineStr"/>
       <c r="AI28" s="3" t="n">
-        <v>19.3114220771393</v>
+        <v>64.98744785948917</v>
       </c>
       <c r="AJ28" s="3" t="inlineStr"/>
       <c r="AK28" s="3" t="n">
-        <v>1.700000000000003</v>
+        <v>1.5</v>
       </c>
       <c r="AL28" s="3" t="inlineStr"/>
       <c r="AM28" s="3" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AN28" s="3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr"/>
@@ -35883,7 +35883,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -35908,7 +35908,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Pts+Rebs+Asts</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -35918,7 +35918,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -35927,33 +35927,33 @@
         </is>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.85</v>
+        <v>0.05</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>0.85</v>
+        <v>0.05</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>7.85</v>
+        <v>7.45</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>0.9492</v>
+        <v>0.9621</v>
       </c>
       <c r="P29" s="5" t="inlineStr"/>
       <c r="Q29" s="5" t="inlineStr"/>
       <c r="R29" s="5" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="U29" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V29" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W29" s="5" t="n">
         <v>5</v>
@@ -35983,89 +35983,69 @@
           <t>SUPPORT</t>
         </is>
       </c>
-      <c r="AC29" s="5" t="inlineStr">
-        <is>
-          <t>VOID_TIER_D;VOID_LOW_MINUTES_NON_A</t>
-        </is>
-      </c>
+      <c r="AC29" s="5" t="inlineStr"/>
       <c r="AD29" s="5" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.333</t>
         </is>
       </c>
       <c r="AE29" s="5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AF29" s="5" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.333</t>
         </is>
       </c>
       <c r="AG29" s="5" t="inlineStr"/>
       <c r="AH29" s="5" t="inlineStr"/>
       <c r="AI29" s="5" t="n">
-        <v>64.98744785948917</v>
+        <v>28.02006364985899</v>
       </c>
       <c r="AJ29" s="5" t="inlineStr"/>
       <c r="AK29" s="5" t="n">
-        <v>1.5</v>
+        <v>-0.7330000000000005</v>
       </c>
       <c r="AL29" s="5" t="inlineStr"/>
       <c r="AM29" s="5" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AN29" s="5" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AO29" s="5" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AP29" s="5" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AQ29" s="5" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AR29" s="5" t="inlineStr">
+        <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="AN29" s="5" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AO29" s="5" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AP29" s="5" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AQ29" s="5" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AR29" s="5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS29" s="5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT29" s="5" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU29" s="5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AV29" s="5" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
+      <c r="AS29" s="5" t="inlineStr"/>
+      <c r="AT29" s="5" t="inlineStr"/>
+      <c r="AU29" s="5" t="inlineStr"/>
+      <c r="AV29" s="5" t="inlineStr"/>
       <c r="AW29" s="5" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.333</t>
         </is>
       </c>
       <c r="AX29" s="5" t="inlineStr"/>
@@ -36101,16 +36081,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -36140,7 +36120,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -36149,33 +36129,33 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.05</v>
+        <v>4.77</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.05</v>
+        <v>4.77</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>7.45</v>
+        <v>23.27</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.9621</v>
+        <v>0.9415</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="3" t="inlineStr"/>
       <c r="R30" s="3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>6.6</v>
+        <v>22.6</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>7.3</v>
+        <v>20.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>5</v>
@@ -36202,72 +36182,92 @@
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="AC30" s="3" t="inlineStr"/>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>VOID_TIER_D</t>
+        </is>
+      </c>
       <c r="AD30" s="3" t="inlineStr">
         <is>
-          <t>7.333</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>7.333</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr"/>
       <c r="AH30" s="3" t="inlineStr"/>
       <c r="AI30" s="3" t="n">
-        <v>28.02006364985899</v>
+        <v>19.3114220771393</v>
       </c>
       <c r="AJ30" s="3" t="inlineStr"/>
       <c r="AK30" s="3" t="n">
-        <v>-0.7330000000000005</v>
+        <v>1.700000000000003</v>
       </c>
       <c r="AL30" s="3" t="inlineStr"/>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AS30" s="3" t="inlineStr"/>
-      <c r="AT30" s="3" t="inlineStr"/>
-      <c r="AU30" s="3" t="inlineStr"/>
-      <c r="AV30" s="3" t="inlineStr"/>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>7.333</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr"/>
@@ -37985,12 +37985,12 @@
       <c r="B40" s="3" t="inlineStr"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -38020,7 +38020,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -38129,12 +38129,12 @@
       <c r="B41" s="5" t="inlineStr"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -38452,7 +38452,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -38596,7 +38596,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -40756,7 +40756,7 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
@@ -42700,7 +42700,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -42953,24 +42953,24 @@
       <c r="B74" s="3" t="inlineStr"/>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
           <t>DEN</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
           <t>2026-04-27 22:30:00-04:00</t>
@@ -42978,7 +42978,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Fantasy Score</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -42988,7 +42988,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -43002,7 +43002,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>0.9658</v>
+        <v>0.9628</v>
       </c>
       <c r="P74" s="3" t="inlineStr"/>
       <c r="Q74" s="3" t="inlineStr"/>
@@ -43014,12 +43014,12 @@
       <c r="W74" s="3" t="inlineStr"/>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z74" s="3" t="inlineStr">
@@ -43097,24 +43097,24 @@
       <c r="B75" s="5" t="inlineStr"/>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
           <t>2026-04-27 22:30:00-04:00</t>
@@ -43122,7 +43122,7 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>Fantasy Score</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
@@ -43146,7 +43146,7 @@
         <v>0</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>0.9628</v>
+        <v>0.9658</v>
       </c>
       <c r="P75" s="5" t="inlineStr"/>
       <c r="Q75" s="5" t="inlineStr"/>
@@ -43158,12 +43158,12 @@
       <c r="W75" s="5" t="inlineStr"/>
       <c r="X75" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Y75" s="5" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Z75" s="5" t="inlineStr">
@@ -43817,22 +43817,22 @@
       <c r="B80" s="3" t="inlineStr"/>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Tim Hardaway</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>G-F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
           <t>DEN</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>MIN</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -43866,7 +43866,7 @@
         <v>0</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.9626</v>
+        <v>0.9628</v>
       </c>
       <c r="P80" s="3" t="inlineStr"/>
       <c r="Q80" s="3" t="inlineStr"/>
@@ -43878,12 +43878,12 @@
       <c r="W80" s="3" t="inlineStr"/>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
         <is>
-          <t>Above Avg</t>
+          <t>Avg</t>
         </is>
       </c>
       <c r="Z80" s="3" t="inlineStr">
@@ -43961,24 +43961,24 @@
       <c r="B81" s="5" t="inlineStr"/>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Tim Hardaway</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G-F</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
           <t>2026-04-27 22:30:00-04:00</t>
@@ -43996,7 +43996,7 @@
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
@@ -44010,7 +44010,7 @@
         <v>0</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>0.9628</v>
+        <v>0.9626</v>
       </c>
       <c r="P81" s="5" t="inlineStr"/>
       <c r="Q81" s="5" t="inlineStr"/>
@@ -44022,12 +44022,12 @@
       <c r="W81" s="5" t="inlineStr"/>
       <c r="X81" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Y81" s="5" t="inlineStr">
         <is>
-          <t>Avg</t>
+          <t>Above Avg</t>
         </is>
       </c>
       <c r="Z81" s="5" t="inlineStr">
